--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -15919,11 +15919,7 @@
       </c>
       <c r="H20" s="1080" t="n"/>
       <c r="I20" s="1080" t="n"/>
-      <c r="J20" s="1083" t="inlineStr">
-        <is>
-          <t>% EJECUTADO FINANCIERO</t>
-        </is>
-      </c>
+      <c r="J20" s="1083" t="n"/>
       <c r="K20" s="1080" t="n"/>
       <c r="L20" s="1080" t="n"/>
       <c r="M20" s="1080" t="n"/>
@@ -15948,10 +15944,7 @@
       </c>
       <c r="H21" s="558" t="n"/>
       <c r="I21" s="558" t="n"/>
-      <c r="J21" s="1362">
-        <f>IFERROR(J46/$L$14,0)</f>
-        <v/>
-      </c>
+      <c r="J21" s="1362" t="n"/>
       <c r="K21" s="558" t="n"/>
       <c r="L21" s="558" t="n"/>
       <c r="M21" s="558" t="n"/>
@@ -15994,11 +15987,7 @@
           <t>REAL POND. %</t>
         </is>
       </c>
-      <c r="J22" s="1077" t="inlineStr">
-        <is>
-          <t>VALOR EJECUTADO ($)</t>
-        </is>
-      </c>
+      <c r="J22" s="1077" t="n"/>
       <c r="N22" s="554" t="n"/>
     </row>
     <row r="23">
@@ -16039,10 +16028,7 @@
         <f>D24*F24</f>
         <v/>
       </c>
-      <c r="J24" s="1367">
-        <f>D24*$L$14*G24</f>
-        <v/>
-      </c>
+      <c r="J24" s="1367" t="n"/>
       <c r="K24" s="542" t="n"/>
       <c r="L24" s="542" t="n"/>
       <c r="M24" s="542" t="n"/>
@@ -16073,10 +16059,7 @@
         <f>D25*F25</f>
         <v/>
       </c>
-      <c r="J25" s="1367">
-        <f>D25*$L$14*G25</f>
-        <v/>
-      </c>
+      <c r="J25" s="1367" t="n"/>
       <c r="K25" s="542" t="n"/>
       <c r="L25" s="542" t="n"/>
       <c r="M25" s="542" t="n"/>
@@ -16107,10 +16090,7 @@
         <f>D26*F26</f>
         <v/>
       </c>
-      <c r="J26" s="1367">
-        <f>D26*$L$14*G26</f>
-        <v/>
-      </c>
+      <c r="J26" s="1367" t="n"/>
       <c r="K26" s="542" t="n"/>
       <c r="L26" s="542" t="n"/>
       <c r="M26" s="542" t="n"/>
@@ -16141,10 +16121,7 @@
         <f>D27*F27</f>
         <v/>
       </c>
-      <c r="J27" s="1367">
-        <f>D27*$L$14*G27</f>
-        <v/>
-      </c>
+      <c r="J27" s="1367" t="n"/>
       <c r="K27" s="542" t="n"/>
       <c r="L27" s="542" t="n"/>
       <c r="M27" s="542" t="n"/>
@@ -16175,10 +16152,7 @@
         <f>D28*F28</f>
         <v/>
       </c>
-      <c r="J28" s="1367">
-        <f>D28*$L$14*G28</f>
-        <v/>
-      </c>
+      <c r="J28" s="1367" t="n"/>
       <c r="K28" s="542" t="n"/>
       <c r="L28" s="542" t="n"/>
       <c r="M28" s="542" t="n"/>
@@ -16209,10 +16183,7 @@
         <f>D29*F29</f>
         <v/>
       </c>
-      <c r="J29" s="1367">
-        <f>D29*$L$14*G29</f>
-        <v/>
-      </c>
+      <c r="J29" s="1367" t="n"/>
       <c r="K29" s="542" t="n"/>
       <c r="L29" s="542" t="n"/>
       <c r="M29" s="542" t="n"/>
@@ -16243,10 +16214,7 @@
         <f>D30*F30</f>
         <v/>
       </c>
-      <c r="J30" s="1367">
-        <f>D30*$L$14*G30</f>
-        <v/>
-      </c>
+      <c r="J30" s="1367" t="n"/>
       <c r="K30" s="542" t="n"/>
       <c r="L30" s="542" t="n"/>
       <c r="M30" s="542" t="n"/>
@@ -16277,10 +16245,7 @@
         <f>D31*F31</f>
         <v/>
       </c>
-      <c r="J31" s="1367">
-        <f>D31*$L$14*G31</f>
-        <v/>
-      </c>
+      <c r="J31" s="1367" t="n"/>
       <c r="K31" s="542" t="n"/>
       <c r="L31" s="542" t="n"/>
       <c r="M31" s="542" t="n"/>
@@ -16311,10 +16276,7 @@
         <f>D32*F32</f>
         <v/>
       </c>
-      <c r="J32" s="1367">
-        <f>D32*$L$14*G32</f>
-        <v/>
-      </c>
+      <c r="J32" s="1367" t="n"/>
       <c r="K32" s="542" t="n"/>
       <c r="L32" s="542" t="n"/>
       <c r="M32" s="542" t="n"/>
@@ -16345,10 +16307,7 @@
         <f>D33*F33</f>
         <v/>
       </c>
-      <c r="J33" s="1367">
-        <f>D33*$L$14*G33</f>
-        <v/>
-      </c>
+      <c r="J33" s="1367" t="n"/>
       <c r="K33" s="542" t="n"/>
       <c r="L33" s="542" t="n"/>
       <c r="M33" s="542" t="n"/>
@@ -16379,10 +16338,7 @@
         <f>D34*F34</f>
         <v/>
       </c>
-      <c r="J34" s="1367">
-        <f>D34*$L$14*G34</f>
-        <v/>
-      </c>
+      <c r="J34" s="1367" t="n"/>
       <c r="K34" s="542" t="n"/>
       <c r="L34" s="542" t="n"/>
       <c r="M34" s="542" t="n"/>
@@ -16413,10 +16369,7 @@
         <f>D35*F35</f>
         <v/>
       </c>
-      <c r="J35" s="1367">
-        <f>D35*$L$14*G35</f>
-        <v/>
-      </c>
+      <c r="J35" s="1367" t="n"/>
       <c r="K35" s="542" t="n"/>
       <c r="L35" s="542" t="n"/>
       <c r="M35" s="542" t="n"/>
@@ -16447,10 +16400,7 @@
         <f>D36*F36</f>
         <v/>
       </c>
-      <c r="J36" s="1367">
-        <f>D36*$L$14*G36</f>
-        <v/>
-      </c>
+      <c r="J36" s="1367" t="n"/>
       <c r="K36" s="542" t="n"/>
       <c r="L36" s="542" t="n"/>
       <c r="M36" s="542" t="n"/>
@@ -16481,10 +16431,7 @@
         <f>D37*F37</f>
         <v/>
       </c>
-      <c r="J37" s="1367">
-        <f>D37*$L$14*G37</f>
-        <v/>
-      </c>
+      <c r="J37" s="1367" t="n"/>
       <c r="K37" s="542" t="n"/>
       <c r="L37" s="542" t="n"/>
       <c r="M37" s="542" t="n"/>
@@ -16515,10 +16462,7 @@
         <f>D38*F38</f>
         <v/>
       </c>
-      <c r="J38" s="1367">
-        <f>D38*$L$14*G38</f>
-        <v/>
-      </c>
+      <c r="J38" s="1367" t="n"/>
       <c r="K38" s="542" t="n"/>
       <c r="L38" s="542" t="n"/>
       <c r="M38" s="542" t="n"/>
@@ -16549,10 +16493,7 @@
         <f>D39*F39</f>
         <v/>
       </c>
-      <c r="J39" s="1370">
-        <f>D39*$L$14*G39</f>
-        <v/>
-      </c>
+      <c r="J39" s="1370" t="n"/>
       <c r="N39" s="1064" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="1062">
@@ -16580,10 +16521,7 @@
         <f>D40*F40</f>
         <v/>
       </c>
-      <c r="J40" s="1371">
-        <f>D40*$L$14*G40</f>
-        <v/>
-      </c>
+      <c r="J40" s="1371" t="n"/>
       <c r="N40" s="1064" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1" s="1062">
@@ -16611,10 +16549,7 @@
         <f>D41*F41</f>
         <v/>
       </c>
-      <c r="J41" s="1371">
-        <f>D41*$L$14*G41</f>
-        <v/>
-      </c>
+      <c r="J41" s="1371" t="n"/>
       <c r="N41" s="1064" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="1062">
@@ -16642,10 +16577,7 @@
         <f>D42*F42</f>
         <v/>
       </c>
-      <c r="J42" s="1371">
-        <f>D42*$L$14*G42</f>
-        <v/>
-      </c>
+      <c r="J42" s="1371" t="n"/>
       <c r="N42" s="1064" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="1062">
@@ -16673,10 +16605,7 @@
         <f>D43*F43</f>
         <v/>
       </c>
-      <c r="J43" s="1371">
-        <f>D43*$L$14*G43</f>
-        <v/>
-      </c>
+      <c r="J43" s="1371" t="n"/>
       <c r="N43" s="1064" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1" s="1062">
@@ -16704,10 +16633,7 @@
         <f>D44*F44</f>
         <v/>
       </c>
-      <c r="J44" s="1371">
-        <f>D44*$L$14*G44</f>
-        <v/>
-      </c>
+      <c r="J44" s="1371" t="n"/>
       <c r="N44" s="1064" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1" s="1062">
@@ -16735,10 +16661,7 @@
         <f>D45*F45</f>
         <v/>
       </c>
-      <c r="J45" s="1372">
-        <f>D45*$L$14*G45</f>
-        <v/>
-      </c>
+      <c r="J45" s="1372" t="n"/>
       <c r="K45" s="542" t="n"/>
       <c r="L45" s="542" t="n"/>
       <c r="M45" s="542" t="n"/>
@@ -16767,10 +16690,7 @@
         <f>SUM(I24:I45)</f>
         <v/>
       </c>
-      <c r="J46" s="1375">
-        <f>SUM(J24:J45)</f>
-        <v/>
-      </c>
+      <c r="J46" s="1375" t="n"/>
       <c r="K46" s="1069" t="n"/>
       <c r="L46" s="1069" t="n"/>
       <c r="M46" s="1069" t="n"/>
@@ -16951,70 +16871,34 @@
       <c r="N57" s="554" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="1062">
-      <c r="A58" s="1376" t="inlineStr">
-        <is>
-          <t>AVANCE FINANCIERO Y ADMINISTRATIVO</t>
-        </is>
-      </c>
+      <c r="A58" s="1376" t="n"/>
       <c r="N58" s="1064" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1" s="1062">
-      <c r="A59" s="1131" t="inlineStr">
-        <is>
-          <t>INGRESOS DEL PERÍODO</t>
-        </is>
-      </c>
+      <c r="A59" s="1131" t="n"/>
       <c r="B59" s="545" t="n"/>
       <c r="C59" s="545" t="n"/>
       <c r="D59" s="545" t="n"/>
       <c r="E59" s="545" t="n"/>
       <c r="F59" s="545" t="n"/>
       <c r="G59" s="344" t="n"/>
-      <c r="H59" s="1100" t="inlineStr">
-        <is>
-          <t>EGRESOS / GASTOS DEL PERÍODO</t>
-        </is>
-      </c>
+      <c r="H59" s="1100" t="n"/>
       <c r="N59" s="554" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1" s="1062">
-      <c r="A60" s="1133" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
+      <c r="A60" s="1133" t="n"/>
       <c r="B60" s="1037" t="n"/>
       <c r="C60" s="1037" t="n"/>
-      <c r="D60" s="340" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E60" s="1036" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
+      <c r="D60" s="340" t="n"/>
+      <c r="E60" s="1036" t="n"/>
       <c r="F60" s="1037" t="n"/>
       <c r="G60" s="341" t="n"/>
-      <c r="H60" s="1087" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
+      <c r="H60" s="1087" t="n"/>
       <c r="I60" s="645" t="n"/>
       <c r="J60" s="645" t="n"/>
-      <c r="K60" s="1087" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
+      <c r="K60" s="1087" t="n"/>
       <c r="L60" s="645" t="n"/>
-      <c r="M60" s="1125" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
+      <c r="M60" s="1125" t="n"/>
       <c r="N60" s="1377" t="n"/>
     </row>
     <row r="61">
@@ -17098,37 +16982,19 @@
       <c r="N65" s="1070" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="1062">
-      <c r="A66" s="1054" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
+      <c r="A66" s="1054" t="n"/>
       <c r="B66" s="545" t="n"/>
       <c r="C66" s="545" t="n"/>
       <c r="D66" s="545" t="n"/>
-      <c r="E66" s="1383">
-        <f>SUM(E61:F65)</f>
-        <v/>
-      </c>
+      <c r="E66" s="1383" t="n"/>
       <c r="F66" s="545" t="n"/>
       <c r="G66" s="329" t="n"/>
-      <c r="H66" s="1142" t="inlineStr">
-        <is>
-          <t>TOTAL EGRESOS</t>
-        </is>
-      </c>
-      <c r="M66" s="1384">
-        <f>SUM(M61:N65)</f>
-        <v/>
-      </c>
+      <c r="H66" s="1142" t="n"/>
+      <c r="M66" s="1384" t="n"/>
       <c r="N66" s="554" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="1062">
-      <c r="A67" s="1130" t="inlineStr">
-        <is>
-          <t>BALANCE DEL PERÍODO (INGRESOS - EGRESOS)</t>
-        </is>
-      </c>
+      <c r="A67" s="1130" t="n"/>
       <c r="B67" s="542" t="n"/>
       <c r="C67" s="542" t="n"/>
       <c r="D67" s="542" t="n"/>
@@ -17140,40 +17006,23 @@
       <c r="J67" s="542" t="n"/>
       <c r="K67" s="542" t="n"/>
       <c r="L67" s="542" t="n"/>
-      <c r="M67" s="1385">
-        <f>E66-M66</f>
-        <v/>
-      </c>
+      <c r="M67" s="1385" t="n"/>
       <c r="N67" s="543" t="n"/>
     </row>
     <row r="68" ht="25.05" customHeight="1" s="1062">
-      <c r="A68" s="1134" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO EJECUTADO ACUMULADO ($)</t>
-        </is>
-      </c>
+      <c r="A68" s="1134" t="n"/>
       <c r="B68" s="1086" t="n"/>
       <c r="C68" s="1086" t="n"/>
       <c r="D68" s="1086" t="n"/>
       <c r="E68" s="1086" t="n"/>
       <c r="F68" s="1086" t="n"/>
-      <c r="G68" s="1386">
-        <f>J46</f>
-        <v/>
-      </c>
+      <c r="G68" s="1386" t="n"/>
       <c r="H68" s="1086" t="n"/>
       <c r="I68" s="1086" t="n"/>
-      <c r="J68" s="1058" t="inlineStr">
-        <is>
-          <t>% EJECUTADO vs PRESUPUESTO</t>
-        </is>
-      </c>
+      <c r="J68" s="1058" t="n"/>
       <c r="K68" s="1086" t="n"/>
       <c r="L68" s="1387" t="n"/>
-      <c r="M68" s="1388">
-        <f>IFERROR(J46/$L$14,0)</f>
-        <v/>
-      </c>
+      <c r="M68" s="1388" t="n"/>
       <c r="N68" s="1389" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="1062">
@@ -18496,7 +18345,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="C9:E9"/>
     <mergeCell ref="A36:E36"/>
@@ -18508,6 +18356,7 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="C28:E28"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="A42:E42"/>
@@ -18526,7 +18375,7 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -6,10 +6,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId5"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Informe Semanal" sheetId="3" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Semanal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -6670,7 +6671,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1453">
+  <cellXfs count="1454">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10269,6 +10270,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="21" borderId="417" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10401,465 +10405,52 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69253</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>174506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2952000" cy="1368000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10904,7 +10495,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10974,51 +10565,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2880000" cy="1260000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>69253</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174506</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2952000" cy="1368000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -11211,7 +10757,529 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="42" customWidth="1" style="1036" min="1" max="1"/>
+    <col width="20.77734375" customWidth="1" style="1036" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="1036" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="1036" min="4" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="1036">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="571" t="inlineStr">
+        <is>
+          <t>FICHA TÉCNICA DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="1036">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="579" t="n"/>
+      <c r="C2" s="580" t="n"/>
+      <c r="D2" s="580" t="n"/>
+      <c r="E2" s="580" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="1036">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="195" t="n"/>
+      <c r="C3" s="196" t="n"/>
+      <c r="D3" s="546" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+      <c r="E3" s="547" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="1036">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="577" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="C4" s="537" t="n"/>
+      <c r="D4" s="98" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="E4" s="1185" t="inlineStr">
+        <is>
+          <t>RYR-FT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="1036">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="573" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="C5" s="537" t="n"/>
+      <c r="D5" s="98" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="E5" s="1149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="1036">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="197" t="n"/>
+      <c r="C6" s="198" t="n"/>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="E6" s="175" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="1036">
+      <c r="B7" s="197" t="n"/>
+      <c r="C7" s="198" t="n"/>
+      <c r="D7" s="99" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="E7" s="1153" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="1036">
+      <c r="A8" s="581" t="inlineStr">
+        <is>
+          <t>DATOS GENERALES DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1036">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>Número de pisos (torre)</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="n"/>
+      <c r="C9" s="574" t="inlineStr">
+        <is>
+          <t>pisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="1036">
+      <c r="A10" s="104" t="inlineStr">
+        <is>
+          <t>Número de sótanos (parqueaderos)</t>
+        </is>
+      </c>
+      <c r="B10" s="105" t="n"/>
+      <c r="C10" s="576" t="inlineStr">
+        <is>
+          <t>niveles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="1036">
+      <c r="A11" s="102" t="inlineStr">
+        <is>
+          <t>Área del lote</t>
+        </is>
+      </c>
+      <c r="B11" s="103" t="n"/>
+      <c r="C11" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="1036">
+      <c r="A12" s="104" t="inlineStr">
+        <is>
+          <t>Área construida típica por piso</t>
+        </is>
+      </c>
+      <c r="B12" s="105" t="n"/>
+      <c r="C12" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1036">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>Área construida - torre (12 pisos)</t>
+        </is>
+      </c>
+      <c r="B13" s="106">
+        <f>B9*B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1036">
+      <c r="A14" s="104" t="inlineStr">
+        <is>
+          <t>Área construida - sótanos (2 niveles)</t>
+        </is>
+      </c>
+      <c r="B14" s="105" t="n"/>
+      <c r="C14" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="1036">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>Área cubierta / cuarto de máquinas / tanques</t>
+        </is>
+      </c>
+      <c r="B15" s="103" t="n"/>
+      <c r="C15" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="1036">
+      <c r="A16" s="104" t="inlineStr">
+        <is>
+          <t>ÁREA TOTAL CONSTRUIDA</t>
+        </is>
+      </c>
+      <c r="B16" s="107">
+        <f>B13+B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="1036">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>Número de apartamentos</t>
+        </is>
+      </c>
+      <c r="B17" s="103" t="n"/>
+      <c r="C17" s="574" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="1036">
+      <c r="A18" s="104" t="inlineStr">
+        <is>
+          <t>Área promedio por apartamento (vendible)</t>
+        </is>
+      </c>
+      <c r="B18" s="105" t="n"/>
+      <c r="C18" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="1036">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>Número de parqueaderos</t>
+        </is>
+      </c>
+      <c r="B19" s="103" t="n"/>
+      <c r="C19" s="574" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="1036">
+      <c r="A20" s="104" t="inlineStr">
+        <is>
+          <t>Número de ascensores</t>
+        </is>
+      </c>
+      <c r="B20" s="105" t="n"/>
+      <c r="C20" s="576" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="1036">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>Altura total aproximada (sótano a cubierta)</t>
+        </is>
+      </c>
+      <c r="B21" s="103" t="n"/>
+      <c r="C21" s="574" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="578" t="n"/>
+      <c r="B22" s="578" t="n"/>
+      <c r="C22" s="578" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="1036">
+      <c r="A23" s="575" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="1036">
+      <c r="A24" s="102" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B24" s="1330" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="574" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="1036">
+      <c r="A25" s="104" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B25" s="1331" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C25" s="576" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="1036">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="B26" s="1330" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C26" s="574" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="1036">
+      <c r="A27" s="104" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad</t>
+        </is>
+      </c>
+      <c r="B27" s="1331" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C27" s="576" t="inlineStr">
+        <is>
+          <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="578" t="n"/>
+      <c r="B28" s="578" t="n"/>
+      <c r="C28" s="578" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1036">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>AIU TOTAL (A+I+U)</t>
+        </is>
+      </c>
+      <c r="B29" s="1332">
+        <f>B24+B25+B26</f>
+        <v/>
+      </c>
+      <c r="C29" s="578" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="578" t="n"/>
+      <c r="B30" s="578" t="n"/>
+      <c r="C30" s="578" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1036">
+      <c r="A31" s="575" t="inlineStr">
+        <is>
+          <t>FUENTES Y NOTAS METODOLÓGICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customFormat="1" customHeight="1" s="213">
+      <c r="A32" s="214" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="212" t="n"/>
+      <c r="C32" s="212" t="n"/>
+      <c r="D32" s="212" t="n"/>
+      <c r="E32" s="478">
+        <f>E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="25.5" customHeight="1" s="1036">
+      <c r="A33" s="572" t="inlineStr">
+        <is>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25.5" customHeight="1" s="1036">
+      <c r="A34" s="572" t="inlineStr">
+        <is>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25.5" customHeight="1" s="1036">
+      <c r="A35" s="572" t="inlineStr">
+        <is>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25.5" customHeight="1" s="1036">
+      <c r="A36" s="572" t="inlineStr">
+        <is>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25.5" customHeight="1" s="1036">
+      <c r="A37" s="572" t="inlineStr">
+        <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25.5" customHeight="1" s="1036">
+      <c r="A38" s="572" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25.5" customHeight="1" s="1036">
+      <c r="A39" s="572" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25.5" customHeight="1" s="1036">
+      <c r="A40" s="572" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25.5" customHeight="1" s="1036">
+      <c r="A41" s="572" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25.5" customHeight="1" s="1036">
+      <c r="A42" s="572" t="inlineStr">
+        <is>
+          <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -15748,65 +15816,65 @@
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B92:E92"/>
     <mergeCell ref="B201:E201"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B215:F215"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B93:F93"/>
     <mergeCell ref="B1:B9"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B213:E213"/>
     <mergeCell ref="B76:E76"/>
     <mergeCell ref="B180:F180"/>
+    <mergeCell ref="B203:F203"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B111:F111"/>
     <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B136:F136"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B67:F67"/>
     <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="C1:F3"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B136:F136"/>
     <mergeCell ref="B134:E134"/>
     <mergeCell ref="B194:E194"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B119:F119"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B184:E184"/>
     <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B148:E148"/>
     <mergeCell ref="B164:F164"/>
+    <mergeCell ref="C1:F3"/>
     <mergeCell ref="B171:E171"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B162:E162"/>
+    <mergeCell ref="B178:E178"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B162:E162"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B173:F173"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -15814,7 +15882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -15971,16 +16039,16 @@
       <c r="B13" s="684" t="n"/>
       <c r="C13" s="684" t="n"/>
       <c r="D13" s="684" t="n"/>
-      <c r="E13" s="138" t="n"/>
-      <c r="F13" s="138" t="n"/>
-      <c r="G13" s="138" t="n"/>
-      <c r="H13" s="138" t="n"/>
-      <c r="I13" s="138" t="n"/>
-      <c r="J13" s="138" t="n"/>
-      <c r="K13" s="138" t="n"/>
-      <c r="L13" s="138" t="n"/>
-      <c r="M13" s="138" t="n"/>
-      <c r="N13" s="494" t="n"/>
+      <c r="E13" s="1453" t="n"/>
+      <c r="F13" s="525" t="n"/>
+      <c r="G13" s="525" t="n"/>
+      <c r="H13" s="525" t="n"/>
+      <c r="I13" s="525" t="n"/>
+      <c r="J13" s="525" t="n"/>
+      <c r="K13" s="525" t="n"/>
+      <c r="L13" s="525" t="n"/>
+      <c r="M13" s="525" t="n"/>
+      <c r="N13" s="1013" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="1036">
       <c r="A14" s="1015" t="inlineStr">
@@ -18006,7 +18074,7 @@
       <c r="A122" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="220">
+  <mergeCells count="221">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="K48:N48"/>
     <mergeCell ref="A37:C37"/>
@@ -18217,6 +18285,7 @@
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="L7:N7"/>
     <mergeCell ref="A17:N17"/>
+    <mergeCell ref="E13:N13"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="J21:N21"/>
@@ -18235,526 +18304,4 @@
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="42" customWidth="1" style="1036" min="1" max="1"/>
-    <col width="20.77734375" customWidth="1" style="1036" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="1036" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="1036" min="4" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="1036">
-      <c r="A1" s="4" t="n"/>
-      <c r="B1" s="571" t="inlineStr">
-        <is>
-          <t>FICHA TÉCNICA DEL PROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="1036">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="579" t="n"/>
-      <c r="C2" s="580" t="n"/>
-      <c r="D2" s="580" t="n"/>
-      <c r="E2" s="580" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="1036">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="195" t="n"/>
-      <c r="C3" s="196" t="n"/>
-      <c r="D3" s="546" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-      <c r="E3" s="547" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="1036">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="577" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="C4" s="537" t="n"/>
-      <c r="D4" s="98" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="E4" s="1185" t="inlineStr">
-        <is>
-          <t>RYR-FT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="1036">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="573" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="C5" s="537" t="n"/>
-      <c r="D5" s="98" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="E5" s="1149" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="1036">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="197" t="n"/>
-      <c r="C6" s="198" t="n"/>
-      <c r="D6" s="98" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="E6" s="175" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="1036">
-      <c r="B7" s="197" t="n"/>
-      <c r="C7" s="198" t="n"/>
-      <c r="D7" s="99" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="E7" s="1153" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="1036">
-      <c r="A8" s="581" t="inlineStr">
-        <is>
-          <t>DATOS GENERALES DEL PROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="1036">
-      <c r="A9" s="102" t="inlineStr">
-        <is>
-          <t>Número de pisos (torre)</t>
-        </is>
-      </c>
-      <c r="B9" s="103" t="n"/>
-      <c r="C9" s="574" t="inlineStr">
-        <is>
-          <t>pisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="1036">
-      <c r="A10" s="104" t="inlineStr">
-        <is>
-          <t>Número de sótanos (parqueaderos)</t>
-        </is>
-      </c>
-      <c r="B10" s="105" t="n"/>
-      <c r="C10" s="576" t="inlineStr">
-        <is>
-          <t>niveles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="1036">
-      <c r="A11" s="102" t="inlineStr">
-        <is>
-          <t>Área del lote</t>
-        </is>
-      </c>
-      <c r="B11" s="103" t="n"/>
-      <c r="C11" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="1036">
-      <c r="A12" s="104" t="inlineStr">
-        <is>
-          <t>Área construida típica por piso</t>
-        </is>
-      </c>
-      <c r="B12" s="105" t="n"/>
-      <c r="C12" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="1036">
-      <c r="A13" s="102" t="inlineStr">
-        <is>
-          <t>Área construida - torre (12 pisos)</t>
-        </is>
-      </c>
-      <c r="B13" s="106">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="1036">
-      <c r="A14" s="104" t="inlineStr">
-        <is>
-          <t>Área construida - sótanos (2 niveles)</t>
-        </is>
-      </c>
-      <c r="B14" s="105" t="n"/>
-      <c r="C14" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="1036">
-      <c r="A15" s="102" t="inlineStr">
-        <is>
-          <t>Área cubierta / cuarto de máquinas / tanques</t>
-        </is>
-      </c>
-      <c r="B15" s="103" t="n"/>
-      <c r="C15" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="1036">
-      <c r="A16" s="104" t="inlineStr">
-        <is>
-          <t>ÁREA TOTAL CONSTRUIDA</t>
-        </is>
-      </c>
-      <c r="B16" s="107">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="1036">
-      <c r="A17" s="102" t="inlineStr">
-        <is>
-          <t>Número de apartamentos</t>
-        </is>
-      </c>
-      <c r="B17" s="103" t="n"/>
-      <c r="C17" s="574" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="1036">
-      <c r="A18" s="104" t="inlineStr">
-        <is>
-          <t>Área promedio por apartamento (vendible)</t>
-        </is>
-      </c>
-      <c r="B18" s="105" t="n"/>
-      <c r="C18" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1036">
-      <c r="A19" s="102" t="inlineStr">
-        <is>
-          <t>Número de parqueaderos</t>
-        </is>
-      </c>
-      <c r="B19" s="103" t="n"/>
-      <c r="C19" s="574" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1036">
-      <c r="A20" s="104" t="inlineStr">
-        <is>
-          <t>Número de ascensores</t>
-        </is>
-      </c>
-      <c r="B20" s="105" t="n"/>
-      <c r="C20" s="576" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1036">
-      <c r="A21" s="102" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="103" t="n"/>
-      <c r="C21" s="574" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="578" t="n"/>
-      <c r="B22" s="578" t="n"/>
-      <c r="C22" s="578" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1036">
-      <c r="A23" s="575" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="1036">
-      <c r="A24" s="102" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="B24" s="1330" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C24" s="574" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="1036">
-      <c r="A25" s="104" t="inlineStr">
-        <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="B25" s="1331" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C25" s="576" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="1036">
-      <c r="A26" s="102" t="inlineStr">
-        <is>
-          <t>Utilidad (U)</t>
-        </is>
-      </c>
-      <c r="B26" s="1330" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C26" s="574" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="1036">
-      <c r="A27" s="104" t="inlineStr">
-        <is>
-          <t>IVA sobre Utilidad</t>
-        </is>
-      </c>
-      <c r="B27" s="1331" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C27" s="576" t="inlineStr">
-        <is>
-          <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="578" t="n"/>
-      <c r="B28" s="578" t="n"/>
-      <c r="C28" s="578" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1036">
-      <c r="A29" s="108" t="inlineStr">
-        <is>
-          <t>AIU TOTAL (A+I+U)</t>
-        </is>
-      </c>
-      <c r="B29" s="1332">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C29" s="578" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="578" t="n"/>
-      <c r="B30" s="578" t="n"/>
-      <c r="C30" s="578" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1036">
-      <c r="A31" s="575" t="inlineStr">
-        <is>
-          <t>FUENTES Y NOTAS METODOLÓGICAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="213">
-      <c r="A32" s="214" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="212" t="n"/>
-      <c r="C32" s="212" t="n"/>
-      <c r="D32" s="212" t="n"/>
-      <c r="E32" s="478">
-        <f>E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1036">
-      <c r="A33" s="572" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1036">
-      <c r="A34" s="572" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1036">
-      <c r="A35" s="572" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1036">
-      <c r="A36" s="572" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1036">
-      <c r="A37" s="572" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="25.5" customHeight="1" s="1036">
-      <c r="A38" s="572" t="inlineStr">
-        <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25.5" customHeight="1" s="1036">
-      <c r="A39" s="572" t="inlineStr">
-        <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="25.5" customHeight="1" s="1036">
-      <c r="A40" s="572" t="inlineStr">
-        <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="25.5" customHeight="1" s="1036">
-      <c r="A41" s="572" t="inlineStr">
-        <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="25.5" customHeight="1" s="1036">
-      <c r="A42" s="572" t="inlineStr">
-        <is>
-          <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -6,11 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId5"/>
+    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
+    <sheet name="Informe Semanal" sheetId="3" r:id="rId18"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -6671,7 +6670,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1454">
+  <cellXfs count="1453">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10270,9 +10269,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="21" borderId="417" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="23" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10405,52 +10401,465 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>69253</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174506</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2952000" cy="1368000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Costo directo por capítulo (COP)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </title>
+    <plotArea>
+      <layout/>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Resumen!$C$11</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Valor (COP)</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t>None</a:t>
+                </a:r>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </txPr>
+            <dLblPos val="outEnd"/>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="1"/>
+            <showLeaderLines val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>Resumen!$A$12:$A$25</f>
+              <strCache>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>1</v>
+                </pt>
+                <pt idx="1">
+                  <v>2</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>4</v>
+                </pt>
+                <pt idx="4">
+                  <v>5</v>
+                </pt>
+                <pt idx="5">
+                  <v>6</v>
+                </pt>
+                <pt idx="6">
+                  <v>7</v>
+                </pt>
+                <pt idx="7">
+                  <v>8</v>
+                </pt>
+                <pt idx="8">
+                  <v>9</v>
+                </pt>
+                <pt idx="9">
+                  <v>10</v>
+                </pt>
+                <pt idx="10">
+                  <v>11</v>
+                </pt>
+                <pt idx="11">
+                  <v>12</v>
+                </pt>
+                <pt idx="12">
+                  <v>13</v>
+                </pt>
+                <pt idx="13">
+                  <v>14</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>Resumen!$C$12:$C$25</f>
+              <numCache>
+                <formatCode>"$ "#,##0</formatCode>
+                <ptCount val="14"/>
+                <pt idx="0">
+                  <v>0</v>
+                </pt>
+                <pt idx="1">
+                  <v>0</v>
+                </pt>
+                <pt idx="2">
+                  <v>0</v>
+                </pt>
+                <pt idx="3">
+                  <v>0</v>
+                </pt>
+                <pt idx="4">
+                  <v>0</v>
+                </pt>
+                <pt idx="5">
+                  <v>0</v>
+                </pt>
+                <pt idx="6">
+                  <v>0</v>
+                </pt>
+                <pt idx="7">
+                  <v>0</v>
+                </pt>
+                <pt idx="8">
+                  <v>0</v>
+                </pt>
+                <pt idx="9">
+                  <v>0</v>
+                </pt>
+                <pt idx="10">
+                  <v>0</v>
+                </pt>
+                <pt idx="11">
+                  <v>0</v>
+                </pt>
+                <pt idx="12">
+                  <v>0</v>
+                </pt>
+                <pt idx="13">
+                  <v>0</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="50050775"/>
+        <axId val="41416401"/>
+      </barChart>
+      <catAx>
+        <axId val="50050775"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Capítulo</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </title>
+        <numFmt formatCode="General" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </txPr>
+        <crossAx val="41416401"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
+      </catAx>
+      <valAx>
+        <axId val="41416401"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>COP</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+          <spPr>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </title>
+        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>None</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </txPr>
+        <crossAx val="50050775"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t>None</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
+</chartSpace>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>OpenAI</author>
+  </authors>
+  <commentList>
+    <comment ref="I26" authorId="0" shapeId="0">
+      <text>
+        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0">
+      <text>
+        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
+      </text>
+    </comment>
+    <comment ref="K26" authorId="0" shapeId="0">
+      <text>
+        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10495,7 +10904,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10565,6 +10974,51 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2880000" cy="1260000"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69253</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>174506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="2952000" cy="1368000"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -10757,529 +11211,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
-  <cols>
-    <col width="42" customWidth="1" style="1036" min="1" max="1"/>
-    <col width="20.77734375" customWidth="1" style="1036" min="2" max="2"/>
-    <col width="50.77734375" customWidth="1" style="1036" min="3" max="3"/>
-    <col width="15.77734375" customWidth="1" style="1036" min="4" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="25.5" customHeight="1" s="1036">
-      <c r="A1" s="4" t="n"/>
-      <c r="B1" s="571" t="inlineStr">
-        <is>
-          <t>FICHA TÉCNICA DEL PROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="4.95" customHeight="1" s="1036">
-      <c r="A2" s="5" t="n"/>
-      <c r="B2" s="579" t="n"/>
-      <c r="C2" s="580" t="n"/>
-      <c r="D2" s="580" t="n"/>
-      <c r="E2" s="580" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="1036">
-      <c r="A3" s="5" t="n"/>
-      <c r="B3" s="195" t="n"/>
-      <c r="C3" s="196" t="n"/>
-      <c r="D3" s="546" t="inlineStr">
-        <is>
-          <t>CONTROL DOCUMENTAL</t>
-        </is>
-      </c>
-      <c r="E3" s="547" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="1036">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="577" t="inlineStr">
-        <is>
-          <t>REFORMAS Y REMODELACIONES</t>
-        </is>
-      </c>
-      <c r="C4" s="537" t="n"/>
-      <c r="D4" s="98" t="inlineStr">
-        <is>
-          <t>Código</t>
-        </is>
-      </c>
-      <c r="E4" s="1185" t="inlineStr">
-        <is>
-          <t>RYR-FT-001</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="1036">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="573" t="inlineStr">
-        <is>
-          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
-        </is>
-      </c>
-      <c r="C5" s="537" t="n"/>
-      <c r="D5" s="98" t="inlineStr">
-        <is>
-          <t>Versión</t>
-        </is>
-      </c>
-      <c r="E5" s="1149" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="1036">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="197" t="n"/>
-      <c r="C6" s="198" t="n"/>
-      <c r="D6" s="98" t="inlineStr">
-        <is>
-          <t>Fecha de Emisión</t>
-        </is>
-      </c>
-      <c r="E6" s="175" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="1036">
-      <c r="B7" s="197" t="n"/>
-      <c r="C7" s="198" t="n"/>
-      <c r="D7" s="99" t="inlineStr">
-        <is>
-          <t>Página</t>
-        </is>
-      </c>
-      <c r="E7" s="1153" t="inlineStr">
-        <is>
-          <t>1 de 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="1036">
-      <c r="A8" s="581" t="inlineStr">
-        <is>
-          <t>DATOS GENERALES DEL PROYECTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="1036">
-      <c r="A9" s="102" t="inlineStr">
-        <is>
-          <t>Número de pisos (torre)</t>
-        </is>
-      </c>
-      <c r="B9" s="103" t="n"/>
-      <c r="C9" s="574" t="inlineStr">
-        <is>
-          <t>pisos</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="1036">
-      <c r="A10" s="104" t="inlineStr">
-        <is>
-          <t>Número de sótanos (parqueaderos)</t>
-        </is>
-      </c>
-      <c r="B10" s="105" t="n"/>
-      <c r="C10" s="576" t="inlineStr">
-        <is>
-          <t>niveles</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="1036">
-      <c r="A11" s="102" t="inlineStr">
-        <is>
-          <t>Área del lote</t>
-        </is>
-      </c>
-      <c r="B11" s="103" t="n"/>
-      <c r="C11" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="1036">
-      <c r="A12" s="104" t="inlineStr">
-        <is>
-          <t>Área construida típica por piso</t>
-        </is>
-      </c>
-      <c r="B12" s="105" t="n"/>
-      <c r="C12" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="1036">
-      <c r="A13" s="102" t="inlineStr">
-        <is>
-          <t>Área construida - torre (12 pisos)</t>
-        </is>
-      </c>
-      <c r="B13" s="106">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="1036">
-      <c r="A14" s="104" t="inlineStr">
-        <is>
-          <t>Área construida - sótanos (2 niveles)</t>
-        </is>
-      </c>
-      <c r="B14" s="105" t="n"/>
-      <c r="C14" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="1036">
-      <c r="A15" s="102" t="inlineStr">
-        <is>
-          <t>Área cubierta / cuarto de máquinas / tanques</t>
-        </is>
-      </c>
-      <c r="B15" s="103" t="n"/>
-      <c r="C15" s="574" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="1036">
-      <c r="A16" s="104" t="inlineStr">
-        <is>
-          <t>ÁREA TOTAL CONSTRUIDA</t>
-        </is>
-      </c>
-      <c r="B16" s="107">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="1036">
-      <c r="A17" s="102" t="inlineStr">
-        <is>
-          <t>Número de apartamentos</t>
-        </is>
-      </c>
-      <c r="B17" s="103" t="n"/>
-      <c r="C17" s="574" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="1036">
-      <c r="A18" s="104" t="inlineStr">
-        <is>
-          <t>Área promedio por apartamento (vendible)</t>
-        </is>
-      </c>
-      <c r="B18" s="105" t="n"/>
-      <c r="C18" s="576" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1036">
-      <c r="A19" s="102" t="inlineStr">
-        <is>
-          <t>Número de parqueaderos</t>
-        </is>
-      </c>
-      <c r="B19" s="103" t="n"/>
-      <c r="C19" s="574" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1036">
-      <c r="A20" s="104" t="inlineStr">
-        <is>
-          <t>Número de ascensores</t>
-        </is>
-      </c>
-      <c r="B20" s="105" t="n"/>
-      <c r="C20" s="576" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1036">
-      <c r="A21" s="102" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="103" t="n"/>
-      <c r="C21" s="574" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="578" t="n"/>
-      <c r="B22" s="578" t="n"/>
-      <c r="C22" s="578" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1036">
-      <c r="A23" s="575" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="1036">
-      <c r="A24" s="102" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="B24" s="1330" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C24" s="574" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="1036">
-      <c r="A25" s="104" t="inlineStr">
-        <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="B25" s="1331" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C25" s="576" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="1036">
-      <c r="A26" s="102" t="inlineStr">
-        <is>
-          <t>Utilidad (U)</t>
-        </is>
-      </c>
-      <c r="B26" s="1330" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C26" s="574" t="inlineStr">
-        <is>
-          <t>% s/costo directo</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="1036">
-      <c r="A27" s="104" t="inlineStr">
-        <is>
-          <t>IVA sobre Utilidad</t>
-        </is>
-      </c>
-      <c r="B27" s="1331" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="C27" s="576" t="inlineStr">
-        <is>
-          <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="578" t="n"/>
-      <c r="B28" s="578" t="n"/>
-      <c r="C28" s="578" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1036">
-      <c r="A29" s="108" t="inlineStr">
-        <is>
-          <t>AIU TOTAL (A+I+U)</t>
-        </is>
-      </c>
-      <c r="B29" s="1332">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C29" s="578" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="578" t="n"/>
-      <c r="B30" s="578" t="n"/>
-      <c r="C30" s="578" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1036">
-      <c r="A31" s="575" t="inlineStr">
-        <is>
-          <t>FUENTES Y NOTAS METODOLÓGICAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="213">
-      <c r="A32" s="214" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="212" t="n"/>
-      <c r="C32" s="212" t="n"/>
-      <c r="D32" s="212" t="n"/>
-      <c r="E32" s="478">
-        <f>E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1036">
-      <c r="A33" s="572" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1036">
-      <c r="A34" s="572" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1036">
-      <c r="A35" s="572" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1036">
-      <c r="A36" s="572" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1036">
-      <c r="A37" s="572" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="25.5" customHeight="1" s="1036">
-      <c r="A38" s="572" t="inlineStr">
-        <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="25.5" customHeight="1" s="1036">
-      <c r="A39" s="572" t="inlineStr">
-        <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="25.5" customHeight="1" s="1036">
-      <c r="A40" s="572" t="inlineStr">
-        <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="25.5" customHeight="1" s="1036">
-      <c r="A41" s="572" t="inlineStr">
-        <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="25.5" customHeight="1" s="1036">
-      <c r="A42" s="572" t="inlineStr">
-        <is>
-          <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -15816,65 +15748,65 @@
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B201:E201"/>
+    <mergeCell ref="B1:B9"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B180:F180"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="C1:F3"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B178:E178"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B222:E222"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B209:E209"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B173:F173"/>
     <mergeCell ref="B127:E127"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B92:E92"/>
-    <mergeCell ref="B201:E201"/>
-    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B150:F150"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B1:B9"/>
-    <mergeCell ref="B222:E222"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B213:E213"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B91:E91"/>
     <mergeCell ref="B136:F136"/>
-    <mergeCell ref="B209:E209"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B109:E109"/>
     <mergeCell ref="B134:E134"/>
     <mergeCell ref="B194:E194"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B119:F119"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B184:E184"/>
     <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B220:E220"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B148:E148"/>
     <mergeCell ref="B164:F164"/>
-    <mergeCell ref="C1:F3"/>
     <mergeCell ref="B171:E171"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B203:F203"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B213:E213"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B196:F196"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B98:E98"/>
     <mergeCell ref="B162:E162"/>
-    <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B173:F173"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -15882,7 +15814,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -16039,16 +15971,16 @@
       <c r="B13" s="684" t="n"/>
       <c r="C13" s="684" t="n"/>
       <c r="D13" s="684" t="n"/>
-      <c r="E13" s="1453" t="n"/>
-      <c r="F13" s="525" t="n"/>
-      <c r="G13" s="525" t="n"/>
-      <c r="H13" s="525" t="n"/>
-      <c r="I13" s="525" t="n"/>
-      <c r="J13" s="525" t="n"/>
-      <c r="K13" s="525" t="n"/>
-      <c r="L13" s="525" t="n"/>
-      <c r="M13" s="525" t="n"/>
-      <c r="N13" s="1013" t="n"/>
+      <c r="E13" s="138" t="n"/>
+      <c r="F13" s="138" t="n"/>
+      <c r="G13" s="138" t="n"/>
+      <c r="H13" s="138" t="n"/>
+      <c r="I13" s="138" t="n"/>
+      <c r="J13" s="138" t="n"/>
+      <c r="K13" s="138" t="n"/>
+      <c r="L13" s="138" t="n"/>
+      <c r="M13" s="138" t="n"/>
+      <c r="N13" s="494" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="1036">
       <c r="A14" s="1015" t="inlineStr">
@@ -18074,7 +18006,7 @@
       <c r="A122" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="221">
+  <mergeCells count="220">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="K48:N48"/>
     <mergeCell ref="A37:C37"/>
@@ -18285,7 +18217,6 @@
     <mergeCell ref="G55:H55"/>
     <mergeCell ref="L7:N7"/>
     <mergeCell ref="A17:N17"/>
-    <mergeCell ref="E13:N13"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="J21:N21"/>
@@ -18304,4 +18235,526 @@
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="42" customWidth="1" style="1036" min="1" max="1"/>
+    <col width="20.77734375" customWidth="1" style="1036" min="2" max="2"/>
+    <col width="50.77734375" customWidth="1" style="1036" min="3" max="3"/>
+    <col width="15.77734375" customWidth="1" style="1036" min="4" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25.5" customHeight="1" s="1036">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="571" t="inlineStr">
+        <is>
+          <t>FICHA TÉCNICA DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="4.95" customHeight="1" s="1036">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="579" t="n"/>
+      <c r="C2" s="580" t="n"/>
+      <c r="D2" s="580" t="n"/>
+      <c r="E2" s="580" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="1036">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="195" t="n"/>
+      <c r="C3" s="196" t="n"/>
+      <c r="D3" s="546" t="inlineStr">
+        <is>
+          <t>CONTROL DOCUMENTAL</t>
+        </is>
+      </c>
+      <c r="E3" s="547" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="1036">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="577" t="inlineStr">
+        <is>
+          <t>REFORMAS Y REMODELACIONES</t>
+        </is>
+      </c>
+      <c r="C4" s="537" t="n"/>
+      <c r="D4" s="98" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="E4" s="1185" t="inlineStr">
+        <is>
+          <t>RYR-FT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="1036">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="573" t="inlineStr">
+        <is>
+          <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN</t>
+        </is>
+      </c>
+      <c r="C5" s="537" t="n"/>
+      <c r="D5" s="98" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="E5" s="1149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="1036">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="197" t="n"/>
+      <c r="C6" s="198" t="n"/>
+      <c r="D6" s="98" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="E6" s="175" t="inlineStr">
+        <is>
+          <t>10/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="1036">
+      <c r="B7" s="197" t="n"/>
+      <c r="C7" s="198" t="n"/>
+      <c r="D7" s="99" t="inlineStr">
+        <is>
+          <t>Página</t>
+        </is>
+      </c>
+      <c r="E7" s="1153" t="inlineStr">
+        <is>
+          <t>1 de 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="1036">
+      <c r="A8" s="581" t="inlineStr">
+        <is>
+          <t>DATOS GENERALES DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="1036">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>Número de pisos (torre)</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="n"/>
+      <c r="C9" s="574" t="inlineStr">
+        <is>
+          <t>pisos</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="1036">
+      <c r="A10" s="104" t="inlineStr">
+        <is>
+          <t>Número de sótanos (parqueaderos)</t>
+        </is>
+      </c>
+      <c r="B10" s="105" t="n"/>
+      <c r="C10" s="576" t="inlineStr">
+        <is>
+          <t>niveles</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="1036">
+      <c r="A11" s="102" t="inlineStr">
+        <is>
+          <t>Área del lote</t>
+        </is>
+      </c>
+      <c r="B11" s="103" t="n"/>
+      <c r="C11" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="1036">
+      <c r="A12" s="104" t="inlineStr">
+        <is>
+          <t>Área construida típica por piso</t>
+        </is>
+      </c>
+      <c r="B12" s="105" t="n"/>
+      <c r="C12" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1036">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>Área construida - torre (12 pisos)</t>
+        </is>
+      </c>
+      <c r="B13" s="106">
+        <f>B9*B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="1036">
+      <c r="A14" s="104" t="inlineStr">
+        <is>
+          <t>Área construida - sótanos (2 niveles)</t>
+        </is>
+      </c>
+      <c r="B14" s="105" t="n"/>
+      <c r="C14" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="1036">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>Área cubierta / cuarto de máquinas / tanques</t>
+        </is>
+      </c>
+      <c r="B15" s="103" t="n"/>
+      <c r="C15" s="574" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="1036">
+      <c r="A16" s="104" t="inlineStr">
+        <is>
+          <t>ÁREA TOTAL CONSTRUIDA</t>
+        </is>
+      </c>
+      <c r="B16" s="107">
+        <f>B13+B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="1036">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>Número de apartamentos</t>
+        </is>
+      </c>
+      <c r="B17" s="103" t="n"/>
+      <c r="C17" s="574" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="1036">
+      <c r="A18" s="104" t="inlineStr">
+        <is>
+          <t>Área promedio por apartamento (vendible)</t>
+        </is>
+      </c>
+      <c r="B18" s="105" t="n"/>
+      <c r="C18" s="576" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="1036">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>Número de parqueaderos</t>
+        </is>
+      </c>
+      <c r="B19" s="103" t="n"/>
+      <c r="C19" s="574" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="1036">
+      <c r="A20" s="104" t="inlineStr">
+        <is>
+          <t>Número de ascensores</t>
+        </is>
+      </c>
+      <c r="B20" s="105" t="n"/>
+      <c r="C20" s="576" t="inlineStr">
+        <is>
+          <t>und</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="1036">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>Altura total aproximada (sótano a cubierta)</t>
+        </is>
+      </c>
+      <c r="B21" s="103" t="n"/>
+      <c r="C21" s="574" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="578" t="n"/>
+      <c r="B22" s="578" t="n"/>
+      <c r="C22" s="578" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="1036">
+      <c r="A23" s="575" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="1036">
+      <c r="A24" s="102" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B24" s="1330" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="574" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="1036">
+      <c r="A25" s="104" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B25" s="1331" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C25" s="576" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="1036">
+      <c r="A26" s="102" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="B26" s="1330" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C26" s="574" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="1036">
+      <c r="A27" s="104" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad</t>
+        </is>
+      </c>
+      <c r="B27" s="1331" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C27" s="576" t="inlineStr">
+        <is>
+          <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="578" t="n"/>
+      <c r="B28" s="578" t="n"/>
+      <c r="C28" s="578" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1036">
+      <c r="A29" s="108" t="inlineStr">
+        <is>
+          <t>AIU TOTAL (A+I+U)</t>
+        </is>
+      </c>
+      <c r="B29" s="1332">
+        <f>B24+B25+B26</f>
+        <v/>
+      </c>
+      <c r="C29" s="578" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="578" t="n"/>
+      <c r="B30" s="578" t="n"/>
+      <c r="C30" s="578" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1036">
+      <c r="A31" s="575" t="inlineStr">
+        <is>
+          <t>FUENTES Y NOTAS METODOLÓGICAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customFormat="1" customHeight="1" s="213">
+      <c r="A32" s="214" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="212" t="n"/>
+      <c r="C32" s="212" t="n"/>
+      <c r="D32" s="212" t="n"/>
+      <c r="E32" s="478">
+        <f>E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="25.5" customHeight="1" s="1036">
+      <c r="A33" s="572" t="inlineStr">
+        <is>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="25.5" customHeight="1" s="1036">
+      <c r="A34" s="572" t="inlineStr">
+        <is>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="25.5" customHeight="1" s="1036">
+      <c r="A35" s="572" t="inlineStr">
+        <is>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="25.5" customHeight="1" s="1036">
+      <c r="A36" s="572" t="inlineStr">
+        <is>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25.5" customHeight="1" s="1036">
+      <c r="A37" s="572" t="inlineStr">
+        <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="25.5" customHeight="1" s="1036">
+      <c r="A38" s="572" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25.5" customHeight="1" s="1036">
+      <c r="A39" s="572" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25.5" customHeight="1" s="1036">
+      <c r="A40" s="572" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="25.5" customHeight="1" s="1036">
+      <c r="A41" s="572" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25.5" customHeight="1" s="1036">
+      <c r="A42" s="572" t="inlineStr">
+        <is>
+          <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10098,464 +10098,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10021,7 +10021,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10217,7 +10217,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10308,7 +10308,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10341,7 +10341,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -10749,7 +10749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="42" customWidth="1" style="1223" min="1" max="1"/>
@@ -10849,414 +10849,463 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="1223">
+    <row r="8">
       <c r="A8" s="597" t="inlineStr">
         <is>
+          <t>IDENTIFICACIÓN DEL PROYECTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B9" s="100" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>No de Contrato</t>
+        </is>
+      </c>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión</t>
+        </is>
+      </c>
+      <c r="D10" s="100" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>Contratista</t>
+        </is>
+      </c>
+      <c r="B11" s="100" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="B12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="1223">
+      <c r="A13" s="597" t="inlineStr">
+        <is>
           <t>DATOS GENERALES DEL PROYECTO</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="1223">
-      <c r="A9" s="99" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="1223">
+      <c r="A14" s="99" t="inlineStr">
         <is>
           <t>Número de pisos (torre)</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="593" t="inlineStr">
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="593" t="inlineStr">
         <is>
           <t>pisos</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="1223">
-      <c r="A10" s="101" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="1223">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>Número de sótanos (parqueaderos)</t>
         </is>
       </c>
-      <c r="B10" s="102" t="n"/>
-      <c r="C10" s="590" t="inlineStr">
+      <c r="B15" s="102" t="n"/>
+      <c r="C15" s="590" t="inlineStr">
         <is>
           <t>niveles</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="1223">
-      <c r="A11" s="99" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="1223">
+      <c r="A16" s="99" t="inlineStr">
         <is>
           <t>Área del lote</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="593" t="inlineStr">
+      <c r="B16" s="100" t="n"/>
+      <c r="C16" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="1223">
-      <c r="A12" s="101" t="inlineStr">
+    <row r="17" ht="15" customHeight="1" s="1223">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>Área construida típica por piso</t>
         </is>
       </c>
-      <c r="B12" s="102" t="n"/>
-      <c r="C12" s="590" t="inlineStr">
+      <c r="B17" s="102" t="n"/>
+      <c r="C17" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="1223">
-      <c r="A13" s="99" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="1223">
+      <c r="A18" s="99" t="inlineStr">
         <is>
           <t>Área construida - torre (12 pisos)</t>
         </is>
       </c>
-      <c r="B13" s="103">
-        <f>B9*B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="593" t="inlineStr">
+      <c r="B18" s="103">
+        <f>B14*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="1223">
-      <c r="A14" s="101" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="1223">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>Área construida - sótanos (2 niveles)</t>
         </is>
       </c>
-      <c r="B14" s="102" t="n"/>
-      <c r="C14" s="590" t="inlineStr">
+      <c r="B19" s="102" t="n"/>
+      <c r="C19" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="1223">
-      <c r="A15" s="99" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="1223">
+      <c r="A20" s="99" t="inlineStr">
         <is>
           <t>Área cubierta / cuarto de máquinas / tanques</t>
         </is>
       </c>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="593" t="inlineStr">
+      <c r="B20" s="100" t="n"/>
+      <c r="C20" s="593" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="1223">
-      <c r="A16" s="101" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="1223">
+      <c r="A21" s="101" t="inlineStr">
         <is>
           <t>ÁREA TOTAL CONSTRUIDA</t>
         </is>
       </c>
-      <c r="B16" s="104">
-        <f>B13+B14+B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="590" t="inlineStr">
+      <c r="B21" s="104">
+        <f>B18+B19+B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="590" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="1223">
-      <c r="A17" s="99" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="1223">
+      <c r="A22" s="99" t="inlineStr">
         <is>
           <t>Número de apartamentos</t>
         </is>
       </c>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="593" t="inlineStr">
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="593" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="1223">
-      <c r="A18" s="101" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="1223">
+      <c r="A23" s="101" t="inlineStr">
         <is>
           <t>Área promedio por apartamento (vendible)</t>
         </is>
       </c>
-      <c r="B18" s="102" t="n"/>
-      <c r="C18" s="590" t="inlineStr">
+      <c r="B23" s="102" t="n"/>
+      <c r="C23" s="590" t="inlineStr">
         <is>
           <t>m²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="1223">
-      <c r="A19" s="99" t="inlineStr">
-        <is>
-          <t>Número de parqueaderos</t>
-        </is>
-      </c>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="593" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="1223">
-      <c r="A20" s="101" t="inlineStr">
-        <is>
-          <t>Número de ascensores</t>
-        </is>
-      </c>
-      <c r="B20" s="102" t="n"/>
-      <c r="C20" s="590" t="inlineStr">
-        <is>
-          <t>und</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="1223">
-      <c r="A21" s="99" t="inlineStr">
-        <is>
-          <t>Altura total aproximada (sótano a cubierta)</t>
-        </is>
-      </c>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="593" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="592" t="n"/>
-      <c r="B22" s="592" t="n"/>
-      <c r="C22" s="592" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="1223">
-      <c r="A23" s="594" t="inlineStr">
-        <is>
-          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="1223">
       <c r="A24" s="99" t="inlineStr">
         <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="B24" s="466" t="n">
-        <v>0.1</v>
-      </c>
+          <t>Número de parqueaderos</t>
+        </is>
+      </c>
+      <c r="B24" s="100" t="n"/>
       <c r="C24" s="593" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="1223">
       <c r="A25" s="101" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
-        </is>
-      </c>
-      <c r="B25" s="467" t="n">
-        <v>0.04</v>
-      </c>
+          <t>Número de ascensores</t>
+        </is>
+      </c>
+      <c r="B25" s="102" t="n"/>
       <c r="C25" s="590" t="inlineStr">
         <is>
-          <t>% s/costo directo</t>
+          <t>und</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="1223">
       <c r="A26" s="99" t="inlineStr">
         <is>
+          <t>Altura total aproximada (sótano a cubierta)</t>
+        </is>
+      </c>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="593" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="592" t="n"/>
+      <c r="B27" s="592" t="n"/>
+      <c r="C27" s="592" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="1223">
+      <c r="A28" s="594" t="inlineStr">
+        <is>
+          <t>PARÁMETROS ECONÓMICOS DEL PRESUPUESTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="1223">
+      <c r="A29" s="99" t="inlineStr">
+        <is>
+          <t>Administración (A)</t>
+        </is>
+      </c>
+      <c r="B29" s="466" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="593" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="1223">
+      <c r="A30" s="101" t="inlineStr">
+        <is>
+          <t>Imprevistos (I)</t>
+        </is>
+      </c>
+      <c r="B30" s="467" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C30" s="590" t="inlineStr">
+        <is>
+          <t>% s/costo directo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="1223">
+      <c r="A31" s="99" t="inlineStr">
+        <is>
           <t>Utilidad (U)</t>
         </is>
       </c>
-      <c r="B26" s="466" t="n">
+      <c r="B31" s="466" t="n">
         <v>0.12</v>
       </c>
-      <c r="C26" s="593" t="inlineStr">
+      <c r="C31" s="593" t="inlineStr">
         <is>
           <t>% s/costo directo</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="1223">
-      <c r="A27" s="101" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="1223">
+      <c r="A32" s="101" t="inlineStr">
         <is>
           <t>IVA sobre Utilidad</t>
         </is>
       </c>
-      <c r="B27" s="467" t="n">
+      <c r="B32" s="467" t="n">
         <v>0.19</v>
       </c>
-      <c r="C27" s="590" t="inlineStr">
+      <c r="C32" s="590" t="inlineStr">
         <is>
           <t>% s/utilidad (Ley 1943 / práctica AIU en Colombia)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="592" t="n"/>
-      <c r="B28" s="592" t="n"/>
-      <c r="C28" s="592" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="1223">
-      <c r="A29" s="105" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="592" t="n"/>
+      <c r="B33" s="592" t="n"/>
+      <c r="C33" s="592" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="1223">
+      <c r="A34" s="105" t="inlineStr">
         <is>
           <t>AIU TOTAL (A+I+U)</t>
         </is>
       </c>
-      <c r="B29" s="468">
-        <f>B24+B25+B26</f>
-        <v/>
-      </c>
-      <c r="C29" s="592" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="592" t="n"/>
-      <c r="B30" s="592" t="n"/>
-      <c r="C30" s="592" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="1223">
-      <c r="A31" s="594" t="inlineStr">
+      <c r="B34" s="468">
+        <f>B29+B30+B31</f>
+        <v/>
+      </c>
+      <c r="C34" s="592" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="592" t="n"/>
+      <c r="B35" s="592" t="n"/>
+      <c r="C35" s="592" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="1223">
+      <c r="A36" s="594" t="inlineStr">
         <is>
           <t>FUENTES Y NOTAS METODOLÓGICAS</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customFormat="1" customHeight="1" s="202">
-      <c r="A32" s="203" t="inlineStr">
+    <row r="37" ht="15" customFormat="1" customHeight="1" s="202">
+      <c r="A37" s="203" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B32" s="201" t="n"/>
-      <c r="C32" s="201" t="n"/>
-      <c r="D32" s="201" t="n"/>
-      <c r="E32" s="342">
+      <c r="B37" s="201" t="n"/>
+      <c r="C37" s="201" t="n"/>
+      <c r="D37" s="201" t="n"/>
+      <c r="E37" s="342">
         <f>E4</f>
         <v/>
-      </c>
-    </row>
-    <row r="33" ht="25.5" customHeight="1" s="1223">
-      <c r="A33" s="591" t="inlineStr">
-        <is>
-          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="25.5" customHeight="1" s="1223">
-      <c r="A34" s="591" t="inlineStr">
-        <is>
-          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="25.5" customHeight="1" s="1223">
-      <c r="A35" s="591" t="inlineStr">
-        <is>
-          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="25.5" customHeight="1" s="1223">
-      <c r="A36" s="591" t="inlineStr">
-        <is>
-          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25.5" customHeight="1" s="1223">
-      <c r="A37" s="591" t="inlineStr">
-        <is>
-          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
-        </is>
       </c>
     </row>
     <row r="38" ht="25.5" customHeight="1" s="1223">
       <c r="A38" s="591" t="inlineStr">
         <is>
-          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+          <t>1. Precios de referencia investigados para Bogotá D.C., 2026 (2° semestre). Son precios promedio de mercado; cada obra requiere cotización formal con proveedores.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" s="1223">
       <c r="A39" s="591" t="inlineStr">
         <is>
-          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+          <t>2. Rango de costo directo de construcción en Bogotá 2026 según fuentes de mercado: $2.200.000 - $3.800.000 COP/m² (Aliados de Obras, 2026); promedio de estabilización Ene-Abr 2026: ~$3.050.000 COP/m².</t>
         </is>
       </c>
     </row>
     <row r="40" ht="25.5" customHeight="1" s="1223">
       <c r="A40" s="591" t="inlineStr">
         <is>
-          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+          <t>3. Concreto 3000 PSI para estructura con formaletería: referencia ~$868.306 COP/m³ (Listado de Precios Unitarios, Secretaría de Infraestructura / Fidubogotá, ajustado a 2026).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="25.5" customHeight="1" s="1223">
       <c r="A41" s="591" t="inlineStr">
         <is>
-          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+          <t>4. Acero de refuerzo figurado e instalado: referencia ~$6.500-7.000 COP/kg (Comando Construcciones, 2026; incremento por alza del 23,7% en el SMMLV 2026 según DANE-ICOCED).</t>
         </is>
       </c>
     </row>
     <row r="42" ht="25.5" customHeight="1" s="1223">
       <c r="A42" s="591" t="inlineStr">
         <is>
+          <t>5. Ascensor eléctrico para edificio de 10+ pisos, alta velocidad, instalado: $450M-$750M COP por unidad (OTA Vertical, 2026). Se tomó valor medio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="25.5" customHeight="1" s="1223">
+      <c r="A43" s="591" t="inlineStr">
+        <is>
+          <t>6. Índice de Costos de la Construcción de Edificaciones (ICOCED-DANE): variación interanual ene.2025-ene.2026 de +8,7% en Bogotá, impulsada por incremento salarial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="25.5" customHeight="1" s="1223">
+      <c r="A44" s="591" t="inlineStr">
+        <is>
+          <t>7. AIU recomendado para edificaciones en Colombia: 25%-30% sobre costos directos (Administración 10-12%, Imprevistos 3-5%, Utilidad 10-15%). Se usó 26% (10%+4%+12%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="25.5" customHeight="1" s="1223">
+      <c r="A45" s="591" t="inlineStr">
+        <is>
+          <t>8. IVA: en Colombia, para contratos de obra el IVA se causa típicamente sobre el componente de Utilidad (AIU), no sobre el costo directo de materiales de construcción de vivienda (parcialmente exentos). Verificar con contador/tributarista para el régimen aplicable a cada proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="25.5" customHeight="1" s="1223">
+      <c r="A46" s="591" t="inlineStr">
+        <is>
+          <t>9. Este documento es una ESTIMACIÓN DE PRESUPUESTO (clase de precisión ±15-20%), útil para prefactibilidad y anteproyecto. No reemplaza un presupuesto detallado con cubicación (cantidades de obra) tomada de planos definitivos y cotizaciones de proveedores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="25.5" customHeight="1" s="1223">
+      <c r="A47" s="591" t="inlineStr">
+        <is>
           <t>10. Celdas en color AZUL = dato de entrada editable. Celdas en NEGRO = fórmula (se recalculan automáticamente). Cambie cantidades y precios unitarios en la hoja 'Presupuesto' según su proyecto real.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C11:E11"/>
     <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C23:E23"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="C32:E32"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A33:E33"/>
     <mergeCell ref="C18:E18"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="B11:E11"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A8:E8"/>
     <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C34:E34"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C24:E24"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="C33:E33"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -15969,7 +16018,7 @@
       <c r="C241" s="681" t="n"/>
       <c r="D241" s="681" t="n"/>
       <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$24</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F241" s="482">
@@ -15987,7 +16036,7 @@
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$25</f>
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
         <v/>
       </c>
       <c r="F242" s="482">
@@ -16005,7 +16054,7 @@
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$26</f>
+        <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
       <c r="F243" s="482">
@@ -16053,7 +16102,7 @@
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
       <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$27</f>
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
         <v/>
       </c>
       <c r="F246" s="482">
@@ -16118,7 +16167,7 @@
       <c r="D251" s="91" t="n"/>
       <c r="E251" s="91" t="n"/>
       <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>
@@ -16133,7 +16182,7 @@
       <c r="D252" s="93" t="n"/>
       <c r="E252" s="93" t="n"/>
       <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$16</f>
+        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
         <v/>
       </c>
     </row>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="169">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1231,6 +1231,11 @@
       <color rgb="FF8A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6575,7 +6580,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9800,6 +9805,9 @@
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10862,7 +10870,7 @@
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="B9" s="100" t="n"/>
+      <c r="B9" s="1307" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="99" t="inlineStr">
@@ -10870,13 +10878,13 @@
           <t>No de Contrato</t>
         </is>
       </c>
-      <c r="B10" s="100" t="n"/>
+      <c r="B10" s="1307" t="n"/>
       <c r="C10" s="99" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="D10" s="100" t="n"/>
+      <c r="D10" s="1307" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="99" t="inlineStr">
@@ -10884,7 +10892,7 @@
           <t>Contratista</t>
         </is>
       </c>
-      <c r="B11" s="100" t="n"/>
+      <c r="B11" s="1307" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="99" t="inlineStr">
@@ -10892,7 +10900,7 @@
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="100" t="n"/>
+      <c r="B12" s="1307" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="1223">
       <c r="A13" s="597" t="inlineStr">
@@ -11297,13 +11305,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11532,12 +11540,12 @@
       </c>
       <c r="B15" s="373" t="inlineStr">
         <is>
-          <t>Replanteo general de ejes y niveles</t>
+          <t>Localización y Replanteo</t>
         </is>
       </c>
       <c r="C15" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D15" s="262" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
-  <fonts count="169">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1236,6 +1236,10 @@
       <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="008A8F99"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -6580,7 +6584,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1308">
+  <cellXfs count="1309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9809,6 +9813,7 @@
     <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11328,7 +11333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="8" customWidth="1" style="586" min="1" max="1"/>
@@ -12656,76 +12661,76 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="82" t="n"/>
-      <c r="B68" s="674" t="inlineStr">
+      <c r="A68" s="81" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="B68" s="373" t="inlineStr">
+        <is>
+          <t>Concreto premezclado o de planta (suministro)</t>
+        </is>
+      </c>
+      <c r="C68" s="261" t="inlineStr">
+        <is>
+          <t>M³</t>
+        </is>
+      </c>
+      <c r="D68" s="262" t="n"/>
+      <c r="E68" s="477" t="n"/>
+      <c r="F68" s="478">
+        <f>D68*E68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="82" t="n"/>
+      <c r="B69" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 4 - ESTRUCTURA</t>
         </is>
       </c>
-      <c r="C68" s="530" t="n"/>
-      <c r="D68" s="530" t="n"/>
-      <c r="E68" s="530" t="n"/>
-      <c r="F68" s="479">
-        <f>SUM(F52:F67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="83" t="n"/>
-      <c r="B69" s="681" t="n"/>
-      <c r="C69" s="681" t="n"/>
-      <c r="D69" s="681" t="n"/>
-      <c r="E69" s="681" t="n"/>
-      <c r="F69" s="675" t="n"/>
+      <c r="C69" s="530" t="n"/>
+      <c r="D69" s="530" t="n"/>
+      <c r="E69" s="530" t="n"/>
+      <c r="F69" s="479">
+        <f>SUM(F51:F68)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="185" t="inlineStr">
+      <c r="A70" s="83" t="n"/>
+      <c r="B70" s="681" t="n"/>
+      <c r="C70" s="681" t="n"/>
+      <c r="D70" s="681" t="n"/>
+      <c r="E70" s="681" t="n"/>
+      <c r="F70" s="675" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="185" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B70" s="680" t="inlineStr">
+      <c r="B71" s="680" t="inlineStr">
         <is>
           <t>MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C70" s="581" t="n"/>
-      <c r="D70" s="581" t="n"/>
-      <c r="E70" s="581" t="n"/>
-      <c r="F70" s="582" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="81" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B71" s="373" t="inlineStr">
-        <is>
-          <t>Mampostería en bloque de concreto</t>
-        </is>
-      </c>
-      <c r="C71" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D71" s="262" t="n"/>
-      <c r="E71" s="477" t="n"/>
-      <c r="F71" s="478">
-        <f>D71*E71</f>
-        <v/>
-      </c>
+      <c r="C71" s="581" t="n"/>
+      <c r="D71" s="581" t="n"/>
+      <c r="E71" s="581" t="n"/>
+      <c r="F71" s="582" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="81" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B72" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo</t>
+          <t>Mampostería en bloque de concreto</t>
         </is>
       </c>
       <c r="C72" s="261" t="inlineStr">
@@ -12743,12 +12748,12 @@
     <row r="73">
       <c r="A73" s="81" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B73" s="373" t="inlineStr">
         <is>
-          <t>Mampostería estructural</t>
+          <t>Mampostería en ladrillo</t>
         </is>
       </c>
       <c r="C73" s="261" t="inlineStr">
@@ -12766,12 +12771,12 @@
     <row r="74">
       <c r="A74" s="81" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="B74" s="373" t="inlineStr">
         <is>
-          <t>Muros en sistema liviano / drywall</t>
+          <t>Mampostería estructural</t>
         </is>
       </c>
       <c r="C74" s="261" t="inlineStr">
@@ -12789,17 +12794,17 @@
     <row r="75">
       <c r="A75" s="81" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="B75" s="373" t="inlineStr">
         <is>
-          <t>Dinteles sobre vanos</t>
+          <t>Muros en sistema liviano / drywall</t>
         </is>
       </c>
       <c r="C75" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D75" s="262" t="n"/>
@@ -12812,12 +12817,12 @@
     <row r="76">
       <c r="A76" s="81" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="B76" s="373" t="inlineStr">
         <is>
-          <t>Alfajías y remates</t>
+          <t>Dinteles sobre vanos</t>
         </is>
       </c>
       <c r="C76" s="261" t="inlineStr">
@@ -12835,17 +12840,17 @@
     <row r="77">
       <c r="A77" s="81" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="B77" s="373" t="inlineStr">
         <is>
-          <t>Anclajes y refuerzos de mampostería</t>
+          <t>Alfajías y remates</t>
         </is>
       </c>
       <c r="C77" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D77" s="262" t="n"/>
@@ -12858,17 +12863,17 @@
     <row r="78">
       <c r="A78" s="81" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="B78" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
+          <t>Anclajes y refuerzos de mampostería</t>
         </is>
       </c>
       <c r="C78" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D78" s="262" t="n"/>
@@ -12881,12 +12886,12 @@
     <row r="79">
       <c r="A79" s="81" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="B79" s="373" t="inlineStr">
         <is>
-          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+          <t>Mampostería en ladrillo tolete a la vista (reforzada)</t>
         </is>
       </c>
       <c r="C79" s="261" t="inlineStr">
@@ -12902,74 +12907,76 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="82" t="n"/>
-      <c r="B80" s="674" t="inlineStr">
+      <c r="A80" s="81" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="B80" s="373" t="inlineStr">
+        <is>
+          <t>Mampostería en ladrillo a la vista (no reforzada)</t>
+        </is>
+      </c>
+      <c r="C80" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D80" s="262" t="n"/>
+      <c r="E80" s="477" t="n"/>
+      <c r="F80" s="478">
+        <f>D80*E80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="82" t="n"/>
+      <c r="B81" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 5 - MAMPOSTERÍA</t>
         </is>
       </c>
-      <c r="C80" s="530" t="n"/>
-      <c r="D80" s="530" t="n"/>
-      <c r="E80" s="530" t="n"/>
-      <c r="F80" s="479">
-        <f>SUM(F71:F79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="83" t="n"/>
-      <c r="B81" s="681" t="n"/>
       <c r="C81" s="530" t="n"/>
       <c r="D81" s="530" t="n"/>
       <c r="E81" s="530" t="n"/>
-      <c r="F81" s="675" t="n"/>
+      <c r="F81" s="479">
+        <f>SUM(F72:F80)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="185" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B82" s="682" t="inlineStr">
-        <is>
-          <t>CUBIERTAS</t>
-        </is>
-      </c>
+      <c r="A82" s="83" t="n"/>
+      <c r="B82" s="681" t="n"/>
       <c r="C82" s="530" t="n"/>
       <c r="D82" s="530" t="n"/>
       <c r="E82" s="530" t="n"/>
-      <c r="F82" s="530" t="n"/>
+      <c r="F82" s="675" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="81" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="B83" s="374" t="inlineStr">
-        <is>
-          <t>Estructura metálica o de madera para cubierta</t>
-        </is>
-      </c>
-      <c r="C83" s="261" t="inlineStr">
-        <is>
-          <t>KG</t>
-        </is>
-      </c>
-      <c r="F83">
-        <f>D83*E83</f>
-        <v/>
-      </c>
+      <c r="A83" s="185" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B83" s="682" t="inlineStr">
+        <is>
+          <t>CUBIERTAS</t>
+        </is>
+      </c>
+      <c r="C83" s="530" t="n"/>
+      <c r="D83" s="530" t="n"/>
+      <c r="E83" s="530" t="n"/>
+      <c r="F83" s="530" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="81" t="inlineStr">
         <is>
-          <t>6.2</t>
-        </is>
-      </c>
-      <c r="B84" s="373" t="inlineStr">
-        <is>
-          <t>Cerchas y elementos estructurales</t>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B84" s="374" t="inlineStr">
+        <is>
+          <t>Estructura metálica o de madera para cubierta</t>
         </is>
       </c>
       <c r="C84" s="261" t="inlineStr">
@@ -12977,9 +12984,7 @@
           <t>KG</t>
         </is>
       </c>
-      <c r="D84" s="262" t="n"/>
-      <c r="E84" s="477" t="n"/>
-      <c r="F84" s="478">
+      <c r="F84">
         <f>D84*E84</f>
         <v/>
       </c>
@@ -12987,17 +12992,17 @@
     <row r="85">
       <c r="A85" s="81" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="B85" s="373" t="inlineStr">
         <is>
-          <t>Suministro e instalación de teja</t>
+          <t>Cerchas y elementos estructurales</t>
         </is>
       </c>
       <c r="C85" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D85" s="262" t="n"/>
@@ -13010,12 +13015,12 @@
     <row r="86">
       <c r="A86" s="81" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="B86" s="373" t="inlineStr">
         <is>
-          <t>Impermeabilización de cubierta</t>
+          <t>Suministro e instalación de teja</t>
         </is>
       </c>
       <c r="C86" s="261" t="inlineStr">
@@ -13033,12 +13038,12 @@
     <row r="87">
       <c r="A87" s="81" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="B87" s="373" t="inlineStr">
         <is>
-          <t>Aislamiento térmico/acústico</t>
+          <t>Impermeabilización de cubierta</t>
         </is>
       </c>
       <c r="C87" s="261" t="inlineStr">
@@ -13056,17 +13061,17 @@
     <row r="88">
       <c r="A88" s="81" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="B88" s="373" t="inlineStr">
         <is>
-          <t>Canales de aguas lluvias</t>
+          <t>Aislamiento térmico/acústico</t>
         </is>
       </c>
       <c r="C88" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D88" s="262" t="n"/>
@@ -13079,12 +13084,12 @@
     <row r="89">
       <c r="A89" s="81" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="B89" s="373" t="inlineStr">
         <is>
-          <t>Bajantes de aguas lluvias</t>
+          <t>Canales de aguas lluvias</t>
         </is>
       </c>
       <c r="C89" s="261" t="inlineStr">
@@ -13102,17 +13107,17 @@
     <row r="90">
       <c r="A90" s="81" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="B90" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso Dry Wall</t>
+          <t>Bajantes de aguas lluvias</t>
         </is>
       </c>
       <c r="C90" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D90" s="262" t="n"/>
@@ -13125,12 +13130,12 @@
     <row r="91">
       <c r="A91" s="81" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="B91" s="373" t="inlineStr">
         <is>
-          <t>Cielo raso en lámina acústica de fibra mineral</t>
+          <t>Cielo raso Dry Wall</t>
         </is>
       </c>
       <c r="C91" s="261" t="inlineStr">
@@ -13146,76 +13151,76 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="82" t="n"/>
-      <c r="B92" s="674" t="inlineStr">
+      <c r="A92" s="81" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="B92" s="373" t="inlineStr">
+        <is>
+          <t>Cielo raso en lámina acústica de fibra mineral</t>
+        </is>
+      </c>
+      <c r="C92" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D92" s="262" t="n"/>
+      <c r="E92" s="477" t="n"/>
+      <c r="F92" s="478">
+        <f>D92*E92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="82" t="n"/>
+      <c r="B93" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 6 - CUBIERTAS</t>
         </is>
       </c>
-      <c r="C92" s="530" t="n"/>
-      <c r="D92" s="530" t="n"/>
-      <c r="E92" s="530" t="n"/>
-      <c r="F92" s="479">
-        <f>SUM(F83:F91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="83" t="n"/>
-      <c r="B93" s="681" t="n"/>
-      <c r="C93" s="681" t="n"/>
-      <c r="D93" s="681" t="n"/>
-      <c r="E93" s="681" t="n"/>
-      <c r="F93" s="675" t="n"/>
+      <c r="C93" s="530" t="n"/>
+      <c r="D93" s="530" t="n"/>
+      <c r="E93" s="530" t="n"/>
+      <c r="F93" s="479">
+        <f>SUM(F84:F92)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="185" t="inlineStr">
+      <c r="A94" s="83" t="n"/>
+      <c r="B94" s="681" t="n"/>
+      <c r="C94" s="681" t="n"/>
+      <c r="D94" s="681" t="n"/>
+      <c r="E94" s="681" t="n"/>
+      <c r="F94" s="675" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="185" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B94" s="677" t="inlineStr">
+      <c r="B95" s="677" t="inlineStr">
         <is>
           <t>IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C94" s="530" t="n"/>
-      <c r="D94" s="530" t="n"/>
-      <c r="E94" s="530" t="n"/>
-      <c r="F94" s="530" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="81" t="inlineStr">
-        <is>
-          <t>7.1</t>
-        </is>
-      </c>
-      <c r="B95" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de losas y terrazas</t>
-        </is>
-      </c>
-      <c r="C95" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D95" s="262" t="n"/>
-      <c r="E95" s="477" t="n"/>
-      <c r="F95" s="478">
-        <f>D95*E95</f>
-        <v/>
-      </c>
+      <c r="C95" s="530" t="n"/>
+      <c r="D95" s="530" t="n"/>
+      <c r="E95" s="530" t="n"/>
+      <c r="F95" s="530" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="81" t="inlineStr">
         <is>
-          <t>7.2</t>
-        </is>
-      </c>
-      <c r="B96" s="374" t="inlineStr">
-        <is>
-          <t>Impermeabilización de muros</t>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B96" s="373" t="inlineStr">
+        <is>
+          <t>Impermeabilización de losas y terrazas</t>
         </is>
       </c>
       <c r="C96" s="261" t="inlineStr">
@@ -13223,7 +13228,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F96">
+      <c r="D96" s="262" t="n"/>
+      <c r="E96" s="477" t="n"/>
+      <c r="F96" s="478">
         <f>D96*E96</f>
         <v/>
       </c>
@@ -13231,12 +13238,12 @@
     <row r="97">
       <c r="A97" s="81" t="inlineStr">
         <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="B97" s="373" t="inlineStr">
-        <is>
-          <t>Impermeabilización de zonas húmedas</t>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="B97" s="374" t="inlineStr">
+        <is>
+          <t>Impermeabilización de muros</t>
         </is>
       </c>
       <c r="C97" s="261" t="inlineStr">
@@ -13244,9 +13251,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D97" s="262" t="n"/>
-      <c r="E97" s="477" t="n"/>
-      <c r="F97" s="478">
+      <c r="F97">
         <f>D97*E97</f>
         <v/>
       </c>
@@ -13254,12 +13259,12 @@
     <row r="98">
       <c r="A98" s="81" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="B98" s="373" t="inlineStr">
         <is>
-          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+          <t>Impermeabilización de zonas húmedas</t>
         </is>
       </c>
       <c r="C98" s="261" t="inlineStr">
@@ -13275,74 +13280,76 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="82" t="n"/>
-      <c r="B99" s="674" t="inlineStr">
+      <c r="A99" s="81" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="B99" s="373" t="inlineStr">
+        <is>
+          <t>Geomembrana HDPE para impermeabilización de terrenos</t>
+        </is>
+      </c>
+      <c r="C99" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D99" s="262" t="n"/>
+      <c r="E99" s="477" t="n"/>
+      <c r="F99" s="478">
+        <f>D99*E99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="82" t="n"/>
+      <c r="B100" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 7 - IMPERMEABILIZACIONES</t>
         </is>
       </c>
-      <c r="C99" s="530" t="n"/>
-      <c r="D99" s="530" t="n"/>
-      <c r="E99" s="530" t="n"/>
-      <c r="F99" s="479">
-        <f>SUM(F95:F98)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="83" t="n"/>
-      <c r="B100" s="681" t="n"/>
       <c r="C100" s="530" t="n"/>
       <c r="D100" s="530" t="n"/>
       <c r="E100" s="530" t="n"/>
-      <c r="F100" s="675" t="n"/>
+      <c r="F100" s="479">
+        <f>SUM(F96:F99)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="185" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B101" s="677" t="inlineStr">
-        <is>
-          <t>PAÑETES Y REVOQUES</t>
-        </is>
-      </c>
+      <c r="A101" s="83" t="n"/>
+      <c r="B101" s="681" t="n"/>
       <c r="C101" s="530" t="n"/>
       <c r="D101" s="530" t="n"/>
       <c r="E101" s="530" t="n"/>
-      <c r="F101" s="530" t="n"/>
+      <c r="F101" s="675" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="81" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="B102" s="374" t="inlineStr">
-        <is>
-          <t>Pañete / revoque interior</t>
-        </is>
-      </c>
-      <c r="C102" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F102">
-        <f>D102*E102</f>
-        <v/>
-      </c>
+      <c r="A102" s="185" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B102" s="677" t="inlineStr">
+        <is>
+          <t>PAÑETES Y REVOQUES</t>
+        </is>
+      </c>
+      <c r="C102" s="530" t="n"/>
+      <c r="D102" s="530" t="n"/>
+      <c r="E102" s="530" t="n"/>
+      <c r="F102" s="530" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="81" t="inlineStr">
         <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="B103" s="373" t="inlineStr">
-        <is>
-          <t>Pañete / revoque exterior</t>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="B103" s="374" t="inlineStr">
+        <is>
+          <t>Pañete / revoque interior</t>
         </is>
       </c>
       <c r="C103" s="261" t="inlineStr">
@@ -13350,9 +13357,7 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D103" s="262" t="n"/>
-      <c r="E103" s="477" t="n"/>
-      <c r="F103" s="478">
+      <c r="F103">
         <f>D103*E103</f>
         <v/>
       </c>
@@ -13360,12 +13365,12 @@
     <row r="104">
       <c r="A104" s="81" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="B104" s="373" t="inlineStr">
         <is>
-          <t>Pañete impermeabilizado</t>
+          <t>Pañete / revoque exterior</t>
         </is>
       </c>
       <c r="C104" s="261" t="inlineStr">
@@ -13383,12 +13388,12 @@
     <row r="105">
       <c r="A105" s="81" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="B105" s="373" t="inlineStr">
         <is>
-          <t>Estuco plástico o tradicional</t>
+          <t>Pañete impermeabilizado</t>
         </is>
       </c>
       <c r="C105" s="261" t="inlineStr">
@@ -13396,82 +13401,82 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D105" s="262" t="n"/>
+      <c r="E105" s="477" t="n"/>
       <c r="F105" s="478">
         <f>D105*E105</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="82" t="n"/>
-      <c r="B106" s="674" t="inlineStr">
+      <c r="A106" s="81" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="B106" s="373" t="inlineStr">
+        <is>
+          <t>Estuco plástico o tradicional</t>
+        </is>
+      </c>
+      <c r="C106" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F106" s="478">
+        <f>D106*E106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="82" t="n"/>
+      <c r="B107" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 8 - PAÑETES Y REVOQUES</t>
         </is>
       </c>
-      <c r="C106" s="530" t="n"/>
-      <c r="D106" s="530" t="n"/>
-      <c r="E106" s="530" t="n"/>
-      <c r="F106" s="479">
-        <f>SUM(F102:F105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="83" t="n"/>
-      <c r="B107" s="675" t="n"/>
       <c r="C107" s="530" t="n"/>
       <c r="D107" s="530" t="n"/>
       <c r="E107" s="530" t="n"/>
-      <c r="F107" s="579" t="n"/>
+      <c r="F107" s="479">
+        <f>SUM(F103:F106)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="185" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B108" s="677" t="inlineStr">
-        <is>
-          <t>PISOS Y ENCHAPES</t>
-        </is>
-      </c>
+      <c r="A108" s="83" t="n"/>
+      <c r="B108" s="675" t="n"/>
       <c r="C108" s="530" t="n"/>
       <c r="D108" s="530" t="n"/>
       <c r="E108" s="530" t="n"/>
-      <c r="F108" s="530" t="n"/>
+      <c r="F108" s="579" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="81" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B109" s="373" t="inlineStr">
-        <is>
-          <t>Mortero de nivelación</t>
-        </is>
-      </c>
-      <c r="C109" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D109" s="262" t="n"/>
-      <c r="E109" s="477" t="n"/>
-      <c r="F109" s="478">
-        <f>D109*E109</f>
-        <v/>
-      </c>
+      <c r="A109" s="185" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B109" s="677" t="inlineStr">
+        <is>
+          <t>PISOS Y ENCHAPES</t>
+        </is>
+      </c>
+      <c r="C109" s="530" t="n"/>
+      <c r="D109" s="530" t="n"/>
+      <c r="E109" s="530" t="n"/>
+      <c r="F109" s="530" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="81" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B110" s="373" t="inlineStr">
         <is>
-          <t>Piso cerámico</t>
+          <t>Mortero de nivelación</t>
         </is>
       </c>
       <c r="C110" s="261" t="inlineStr">
@@ -13489,12 +13494,12 @@
     <row r="111">
       <c r="A111" s="81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="B111" s="373" t="inlineStr">
         <is>
-          <t>Piso en porcelanato</t>
+          <t>Piso cerámico</t>
         </is>
       </c>
       <c r="C111" s="261" t="inlineStr">
@@ -13512,12 +13517,12 @@
     <row r="112">
       <c r="A112" s="81" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="B112" s="373" t="inlineStr">
         <is>
-          <t>Piso vinílico</t>
+          <t>Piso en porcelanato</t>
         </is>
       </c>
       <c r="C112" s="261" t="inlineStr">
@@ -13535,12 +13540,12 @@
     <row r="113">
       <c r="A113" s="81" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="B113" s="373" t="inlineStr">
         <is>
-          <t>Piso laminado</t>
+          <t>Piso vinílico</t>
         </is>
       </c>
       <c r="C113" s="261" t="inlineStr">
@@ -13558,12 +13563,12 @@
     <row r="114">
       <c r="A114" s="81" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="B114" s="373" t="inlineStr">
         <is>
-          <t>Enchape cerámico en muros</t>
+          <t>Piso laminado</t>
         </is>
       </c>
       <c r="C114" s="261" t="inlineStr">
@@ -13571,6 +13576,8 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D114" s="262" t="n"/>
+      <c r="E114" s="477" t="n"/>
       <c r="F114" s="478">
         <f>D114*E114</f>
         <v/>
@@ -13579,21 +13586,19 @@
     <row r="115">
       <c r="A115" s="81" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="B115" s="373" t="inlineStr">
         <is>
-          <t>Guardaescoba</t>
+          <t>Enchape cerámico en muros</t>
         </is>
       </c>
       <c r="C115" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D115" s="262" t="n"/>
-      <c r="E115" s="477" t="n"/>
+          <t>M²</t>
+        </is>
+      </c>
       <c r="F115" s="478">
         <f>D115*E115</f>
         <v/>
@@ -13602,12 +13607,12 @@
     <row r="116">
       <c r="A116" s="81" t="inlineStr">
         <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="B116" s="374" t="inlineStr">
-        <is>
-          <t>Juntas de dilatación / construcción</t>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="B116" s="373" t="inlineStr">
+        <is>
+          <t>Guardaescoba</t>
         </is>
       </c>
       <c r="C116" s="261" t="inlineStr">
@@ -13615,7 +13620,9 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="F116">
+      <c r="D116" s="262" t="n"/>
+      <c r="E116" s="477" t="n"/>
+      <c r="F116" s="478">
         <f>D116*E116</f>
         <v/>
       </c>
@@ -13623,17 +13630,17 @@
     <row r="117">
       <c r="A117" s="81" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="B117" s="374" t="inlineStr">
         <is>
-          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
+          <t>Juntas de dilatación / construcción</t>
         </is>
       </c>
       <c r="C117" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="F117">
@@ -13644,12 +13651,12 @@
     <row r="118">
       <c r="A118" s="81" t="inlineStr">
         <is>
-          <t>9.10</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="B118" s="374" t="inlineStr">
         <is>
-          <t>Baldosa de granito</t>
+          <t>Piso en concreto afinado con endurecedor de cuarzo</t>
         </is>
       </c>
       <c r="C118" s="261" t="inlineStr">
@@ -13665,12 +13672,12 @@
     <row r="119">
       <c r="A119" s="81" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.10</t>
         </is>
       </c>
       <c r="B119" s="374" t="inlineStr">
         <is>
-          <t>Enchape en granito pulido</t>
+          <t>Baldosa de granito</t>
         </is>
       </c>
       <c r="C119" s="261" t="inlineStr">
@@ -13684,76 +13691,74 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="82" t="n"/>
-      <c r="B120" s="674" t="inlineStr">
+      <c r="A120" s="81" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="B120" s="374" t="inlineStr">
+        <is>
+          <t>Enchape en granito pulido</t>
+        </is>
+      </c>
+      <c r="C120" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F120">
+        <f>D120*E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="82" t="n"/>
+      <c r="B121" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 9 - PISOS Y ENCHAPES</t>
         </is>
       </c>
-      <c r="C120" s="530" t="n"/>
-      <c r="D120" s="530" t="n"/>
-      <c r="E120" s="530" t="n"/>
-      <c r="F120" s="479">
-        <f>SUM(F109:F119)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="83" t="n"/>
-      <c r="B121" s="681" t="n"/>
-      <c r="C121" s="681" t="n"/>
-      <c r="D121" s="681" t="n"/>
-      <c r="E121" s="681" t="n"/>
-      <c r="F121" s="675" t="n"/>
+      <c r="C121" s="530" t="n"/>
+      <c r="D121" s="530" t="n"/>
+      <c r="E121" s="530" t="n"/>
+      <c r="F121" s="479">
+        <f>SUM(F110:F120)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="185" t="inlineStr">
+      <c r="A122" s="83" t="n"/>
+      <c r="B122" s="681" t="n"/>
+      <c r="C122" s="681" t="n"/>
+      <c r="D122" s="681" t="n"/>
+      <c r="E122" s="681" t="n"/>
+      <c r="F122" s="675" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="185" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B122" s="677" t="inlineStr">
+      <c r="B123" s="677" t="inlineStr">
         <is>
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="C122" s="530" t="n"/>
-      <c r="D122" s="530" t="n"/>
-      <c r="E122" s="530" t="n"/>
-      <c r="F122" s="530" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="81" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B123" s="373" t="inlineStr">
-        <is>
-          <t>Pintura vinílica interior</t>
-        </is>
-      </c>
-      <c r="C123" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D123" s="262" t="n"/>
-      <c r="E123" s="477" t="n"/>
-      <c r="F123" s="478">
-        <f>D123*E123</f>
-        <v/>
-      </c>
+      <c r="C123" s="530" t="n"/>
+      <c r="D123" s="530" t="n"/>
+      <c r="E123" s="530" t="n"/>
+      <c r="F123" s="530" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="81" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B124" s="373" t="inlineStr">
         <is>
-          <t>Pintura exterior</t>
+          <t>Pintura vinílica interior</t>
         </is>
       </c>
       <c r="C124" s="261" t="inlineStr">
@@ -13771,12 +13776,12 @@
     <row r="125">
       <c r="A125" s="81" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B125" s="373" t="inlineStr">
         <is>
-          <t>Pintura esmalte en superficies metálicas/madera</t>
+          <t>Pintura exterior</t>
         </is>
       </c>
       <c r="C125" s="261" t="inlineStr">
@@ -13794,12 +13799,12 @@
     <row r="126">
       <c r="A126" s="81" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="B126" s="373" t="inlineStr">
         <is>
-          <t>Pintura anticorrosiva</t>
+          <t>Pintura esmalte en superficies metálicas/madera</t>
         </is>
       </c>
       <c r="C126" s="261" t="inlineStr">
@@ -13817,12 +13822,12 @@
     <row r="127">
       <c r="A127" s="81" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="B127" s="373" t="inlineStr">
         <is>
-          <t>Sellador / imprimante</t>
+          <t>Pintura anticorrosiva</t>
         </is>
       </c>
       <c r="C127" s="261" t="inlineStr">
@@ -13830,89 +13835,91 @@
           <t>M²</t>
         </is>
       </c>
+      <c r="D127" s="262" t="n"/>
+      <c r="E127" s="477" t="n"/>
       <c r="F127" s="478">
         <f>D127*E127</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="82" t="n"/>
-      <c r="B128" s="674" t="inlineStr">
+      <c r="A128" s="81" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B128" s="373" t="inlineStr">
+        <is>
+          <t>Sellador / imprimante</t>
+        </is>
+      </c>
+      <c r="C128" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F128" s="478">
+        <f>D128*E128</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="82" t="n"/>
+      <c r="B129" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 10 - PINTURA</t>
         </is>
       </c>
-      <c r="C128" s="530" t="n"/>
-      <c r="D128" s="530" t="n"/>
-      <c r="E128" s="530" t="n"/>
-      <c r="F128" s="479">
-        <f>SUM(F123:F127)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="83" t="n"/>
-      <c r="B129" s="675" t="n"/>
       <c r="C129" s="530" t="n"/>
       <c r="D129" s="530" t="n"/>
       <c r="E129" s="530" t="n"/>
-      <c r="F129" s="579" t="n"/>
+      <c r="F129" s="479">
+        <f>SUM(F124:F128)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="185" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B130" s="677" t="inlineStr">
-        <is>
-          <t>CARPINTERÍA</t>
-        </is>
-      </c>
+      <c r="A130" s="83" t="n"/>
+      <c r="B130" s="675" t="n"/>
       <c r="C130" s="530" t="n"/>
       <c r="D130" s="530" t="n"/>
       <c r="E130" s="530" t="n"/>
-      <c r="F130" s="530" t="n"/>
+      <c r="F130" s="579" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="81" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="B131" s="373" t="inlineStr">
-        <is>
-          <t>Puertas de madera</t>
-        </is>
-      </c>
-      <c r="C131" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D131" s="262" t="n"/>
-      <c r="E131" s="477" t="n"/>
-      <c r="F131" s="478">
-        <f>D131*E131</f>
-        <v/>
-      </c>
+      <c r="A131" s="185" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B131" s="677" t="inlineStr">
+        <is>
+          <t>CARPINTERÍA</t>
+        </is>
+      </c>
+      <c r="C131" s="530" t="n"/>
+      <c r="D131" s="530" t="n"/>
+      <c r="E131" s="530" t="n"/>
+      <c r="F131" s="530" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="81" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="B132" s="373" t="inlineStr">
         <is>
-          <t>Muebles fijos de madera</t>
+          <t>Puertas de madera</t>
         </is>
       </c>
       <c r="C132" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D132" s="262" t="n"/>
+      <c r="E132" s="477" t="n"/>
       <c r="F132" s="478">
         <f>D132*E132</f>
         <v/>
@@ -13921,21 +13928,19 @@
     <row r="133">
       <c r="A133" s="81" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.2</t>
         </is>
       </c>
       <c r="B133" s="373" t="inlineStr">
         <is>
-          <t>Puertas metálicas</t>
+          <t>Muebles fijos de madera</t>
         </is>
       </c>
       <c r="C133" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D133" s="262" t="n"/>
-      <c r="E133" s="477" t="n"/>
+          <t>ML</t>
+        </is>
+      </c>
       <c r="F133" s="478">
         <f>D133*E133</f>
         <v/>
@@ -13944,20 +13949,22 @@
     <row r="134">
       <c r="A134" s="81" t="inlineStr">
         <is>
-          <t>11.4</t>
-        </is>
-      </c>
-      <c r="B134" s="374" t="inlineStr">
-        <is>
-          <t>Barandas metálicas</t>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="B134" s="373" t="inlineStr">
+        <is>
+          <t>Puertas metálicas</t>
         </is>
       </c>
       <c r="C134" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F134">
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D134" s="262" t="n"/>
+      <c r="E134" s="477" t="n"/>
+      <c r="F134" s="478">
         <f>D134*E134</f>
         <v/>
       </c>
@@ -13965,12 +13972,12 @@
     <row r="135">
       <c r="A135" s="81" t="inlineStr">
         <is>
-          <t>11.5</t>
-        </is>
-      </c>
-      <c r="B135" s="373" t="inlineStr">
-        <is>
-          <t>Pasamanos</t>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="B135" s="374" t="inlineStr">
+        <is>
+          <t>Barandas metálicas</t>
         </is>
       </c>
       <c r="C135" s="261" t="inlineStr">
@@ -13978,9 +13985,7 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D135" s="262" t="n"/>
-      <c r="E135" s="477" t="n"/>
-      <c r="F135" s="478">
+      <c r="F135">
         <f>D135*E135</f>
         <v/>
       </c>
@@ -13988,17 +13993,17 @@
     <row r="136">
       <c r="A136" s="81" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>11.5</t>
         </is>
       </c>
       <c r="B136" s="373" t="inlineStr">
         <is>
-          <t>Ventanas de aluminio</t>
+          <t>Pasamanos</t>
         </is>
       </c>
       <c r="C136" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D136" s="262" t="n"/>
@@ -14011,12 +14016,12 @@
     <row r="137">
       <c r="A137" s="81" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="B137" s="373" t="inlineStr">
         <is>
-          <t>Divisiones de aluminio</t>
+          <t>Ventanas de aluminio</t>
         </is>
       </c>
       <c r="C137" s="261" t="inlineStr">
@@ -14034,17 +14039,17 @@
     <row r="138">
       <c r="A138" s="81" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="B138" s="373" t="inlineStr">
         <is>
-          <t>Puerta antipánico</t>
+          <t>Divisiones de aluminio</t>
         </is>
       </c>
       <c r="C138" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D138" s="262" t="n"/>
@@ -14055,74 +14060,76 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="82" t="n"/>
-      <c r="B139" s="674" t="inlineStr">
+      <c r="A139" s="81" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="B139" s="373" t="inlineStr">
+        <is>
+          <t>Puerta antipánico</t>
+        </is>
+      </c>
+      <c r="C139" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D139" s="262" t="n"/>
+      <c r="E139" s="477" t="n"/>
+      <c r="F139" s="478">
+        <f>D139*E139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="82" t="n"/>
+      <c r="B140" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 11 - CARPINTERÍA</t>
         </is>
       </c>
-      <c r="C139" s="530" t="n"/>
-      <c r="D139" s="530" t="n"/>
-      <c r="E139" s="530" t="n"/>
-      <c r="F139" s="479">
-        <f>SUM(F131:F138)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="83" t="n"/>
-      <c r="B140" s="681" t="n"/>
-      <c r="C140" s="681" t="n"/>
-      <c r="D140" s="681" t="n"/>
-      <c r="E140" s="681" t="n"/>
-      <c r="F140" s="675" t="n"/>
+      <c r="C140" s="530" t="n"/>
+      <c r="D140" s="530" t="n"/>
+      <c r="E140" s="530" t="n"/>
+      <c r="F140" s="479">
+        <f>SUM(F132:F139)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="185" t="inlineStr">
+      <c r="A141" s="83" t="n"/>
+      <c r="B141" s="681" t="n"/>
+      <c r="C141" s="681" t="n"/>
+      <c r="D141" s="681" t="n"/>
+      <c r="E141" s="681" t="n"/>
+      <c r="F141" s="675" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="185" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B141" s="677" t="inlineStr">
+      <c r="B142" s="677" t="inlineStr">
         <is>
           <t>VIDRIOS</t>
         </is>
       </c>
-      <c r="C141" s="530" t="n"/>
-      <c r="D141" s="530" t="n"/>
-      <c r="E141" s="530" t="n"/>
-      <c r="F141" s="530" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="81" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
-      <c r="B142" s="373" t="inlineStr">
-        <is>
-          <t>Vidrio templado</t>
-        </is>
-      </c>
-      <c r="C142" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="F142" s="478">
-        <f>D142*E142</f>
-        <v/>
-      </c>
+      <c r="C142" s="530" t="n"/>
+      <c r="D142" s="530" t="n"/>
+      <c r="E142" s="530" t="n"/>
+      <c r="F142" s="530" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="81" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="B143" s="373" t="inlineStr">
         <is>
-          <t>Vidrio laminado</t>
+          <t>Vidrio templado</t>
         </is>
       </c>
       <c r="C143" s="261" t="inlineStr">
@@ -14130,8 +14137,6 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="D143" s="262" t="n"/>
-      <c r="E143" s="477" t="n"/>
       <c r="F143" s="478">
         <f>D143*E143</f>
         <v/>
@@ -14140,12 +14145,12 @@
     <row r="144">
       <c r="A144" s="81" t="inlineStr">
         <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="B144" s="374" t="inlineStr">
-        <is>
-          <t>Espejos</t>
+          <t>12.2</t>
+        </is>
+      </c>
+      <c r="B144" s="373" t="inlineStr">
+        <is>
+          <t>Vidrio laminado</t>
         </is>
       </c>
       <c r="C144" s="261" t="inlineStr">
@@ -14153,7 +14158,9 @@
           <t>M²</t>
         </is>
       </c>
-      <c r="F144">
+      <c r="D144" s="262" t="n"/>
+      <c r="E144" s="477" t="n"/>
+      <c r="F144" s="478">
         <f>D144*E144</f>
         <v/>
       </c>
@@ -14161,95 +14168,95 @@
     <row r="145">
       <c r="A145" s="81" t="inlineStr">
         <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="B145" s="374" t="inlineStr">
+        <is>
+          <t>Espejos</t>
+        </is>
+      </c>
+      <c r="C145" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="F145">
+        <f>D145*E145</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="81" t="inlineStr">
+        <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="B145" s="373" t="inlineStr">
+      <c r="B146" s="373" t="inlineStr">
         <is>
           <t>Sellos y silicona</t>
         </is>
       </c>
-      <c r="C145" s="261" t="inlineStr">
+      <c r="C146" s="261" t="inlineStr">
         <is>
           <t>ML</t>
         </is>
       </c>
-      <c r="D145" s="262" t="n"/>
-      <c r="E145" s="477" t="n"/>
-      <c r="F145" s="478">
-        <f>D145*E145</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="82" t="n"/>
-      <c r="B146" s="674" t="inlineStr">
+      <c r="D146" s="262" t="n"/>
+      <c r="E146" s="477" t="n"/>
+      <c r="F146" s="478">
+        <f>D146*E146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="82" t="n"/>
+      <c r="B147" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 12 - VIDRIOS</t>
         </is>
       </c>
-      <c r="C146" s="530" t="n"/>
-      <c r="D146" s="530" t="n"/>
-      <c r="E146" s="530" t="n"/>
-      <c r="F146" s="479">
-        <f>SUM(F142:F145)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="83" t="n"/>
-      <c r="B147" s="681" t="n"/>
-      <c r="C147" s="681" t="n"/>
-      <c r="D147" s="681" t="n"/>
-      <c r="E147" s="681" t="n"/>
-      <c r="F147" s="675" t="n"/>
+      <c r="C147" s="530" t="n"/>
+      <c r="D147" s="530" t="n"/>
+      <c r="E147" s="530" t="n"/>
+      <c r="F147" s="479">
+        <f>SUM(F143:F146)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="185" t="inlineStr">
+      <c r="A148" s="83" t="n"/>
+      <c r="B148" s="681" t="n"/>
+      <c r="C148" s="681" t="n"/>
+      <c r="D148" s="681" t="n"/>
+      <c r="E148" s="681" t="n"/>
+      <c r="F148" s="675" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="185" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B148" s="677" t="inlineStr">
+      <c r="B149" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C148" s="530" t="n"/>
-      <c r="D148" s="530" t="n"/>
-      <c r="E148" s="530" t="n"/>
-      <c r="F148" s="530" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="81" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="B149" s="373" t="inlineStr">
-        <is>
-          <t>Tubería de agua fría</t>
-        </is>
-      </c>
-      <c r="C149" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="F149" s="478">
-        <f>D149*E149</f>
-        <v/>
-      </c>
+      <c r="C149" s="530" t="n"/>
+      <c r="D149" s="530" t="n"/>
+      <c r="E149" s="530" t="n"/>
+      <c r="F149" s="530" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="81" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="B150" s="373" t="inlineStr">
         <is>
-          <t>Tubería de agua caliente</t>
+          <t>Tubería de agua fría</t>
         </is>
       </c>
       <c r="C150" s="261" t="inlineStr">
@@ -14257,8 +14264,6 @@
           <t>ML</t>
         </is>
       </c>
-      <c r="D150" s="262" t="n"/>
-      <c r="E150" s="477" t="n"/>
       <c r="F150" s="478">
         <f>D150*E150</f>
         <v/>
@@ -14267,19 +14272,21 @@
     <row r="151">
       <c r="A151" s="81" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="B151" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Tubería de agua caliente</t>
         </is>
       </c>
       <c r="C151" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
-        </is>
-      </c>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D151" s="262" t="n"/>
+      <c r="E151" s="477" t="n"/>
       <c r="F151" s="478">
         <f>D151*E151</f>
         <v/>
@@ -14288,21 +14295,19 @@
     <row r="152">
       <c r="A152" s="81" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="B152" s="373" t="inlineStr">
         <is>
-          <t>Tubería sanitaria</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C152" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D152" s="262" t="n"/>
-      <c r="E152" s="477" t="n"/>
+          <t>UND</t>
+        </is>
+      </c>
       <c r="F152" s="478">
         <f>D152*E152</f>
         <v/>
@@ -14311,12 +14316,12 @@
     <row r="153">
       <c r="A153" s="81" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="B153" s="373" t="inlineStr">
         <is>
-          <t>Tubería de aguas lluvias</t>
+          <t>Tubería sanitaria</t>
         </is>
       </c>
       <c r="C153" s="261" t="inlineStr">
@@ -14334,17 +14339,17 @@
     <row r="154">
       <c r="A154" s="81" t="inlineStr">
         <is>
-          <t>13.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="B154" s="373" t="inlineStr">
         <is>
-          <t>Cajas de inspección</t>
+          <t>Tubería de aguas lluvias</t>
         </is>
       </c>
       <c r="C154" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D154" s="262" t="n"/>
@@ -14357,12 +14362,12 @@
     <row r="155">
       <c r="A155" s="81" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>13.6</t>
         </is>
       </c>
       <c r="B155" s="373" t="inlineStr">
         <is>
-          <t>Aparatos sanitarios</t>
+          <t>Cajas de inspección</t>
         </is>
       </c>
       <c r="C155" s="261" t="inlineStr">
@@ -14380,12 +14385,12 @@
     <row r="156">
       <c r="A156" s="81" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="B156" s="373" t="inlineStr">
         <is>
-          <t>Lavamanos</t>
+          <t>Aparatos sanitarios</t>
         </is>
       </c>
       <c r="C156" s="261" t="inlineStr">
@@ -14403,12 +14408,12 @@
     <row r="157">
       <c r="A157" s="81" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="B157" s="373" t="inlineStr">
         <is>
-          <t>Griferías</t>
+          <t>Lavamanos</t>
         </is>
       </c>
       <c r="C157" s="261" t="inlineStr">
@@ -14426,12 +14431,12 @@
     <row r="158">
       <c r="A158" s="81" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="B158" s="373" t="inlineStr">
         <is>
-          <t>Duchas</t>
+          <t>Griferías</t>
         </is>
       </c>
       <c r="C158" s="261" t="inlineStr">
@@ -14449,17 +14454,17 @@
     <row r="159">
       <c r="A159" s="81" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="B159" s="373" t="inlineStr">
         <is>
-          <t>Pruebas hidráulicas y de estanqueidad</t>
+          <t>Duchas</t>
         </is>
       </c>
       <c r="C159" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D159" s="262" t="n"/>
@@ -14472,17 +14477,17 @@
     <row r="160">
       <c r="A160" s="81" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="B160" s="373" t="inlineStr">
         <is>
-          <t>Orinal institucional</t>
+          <t>Pruebas hidráulicas y de estanqueidad</t>
         </is>
       </c>
       <c r="C160" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D160" s="262" t="n"/>
@@ -14493,76 +14498,76 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="82" t="n"/>
-      <c r="B161" s="674" t="inlineStr">
+      <c r="A161" s="81" t="inlineStr">
+        <is>
+          <t>13.12</t>
+        </is>
+      </c>
+      <c r="B161" s="373" t="inlineStr">
+        <is>
+          <t>Orinal institucional</t>
+        </is>
+      </c>
+      <c r="C161" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D161" s="262" t="n"/>
+      <c r="E161" s="477" t="n"/>
+      <c r="F161" s="478">
+        <f>D161*E161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="82" t="n"/>
+      <c r="B162" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 13 - INSTALACIONES HIDROSANITARIAS</t>
         </is>
       </c>
-      <c r="C161" s="530" t="n"/>
-      <c r="D161" s="530" t="n"/>
-      <c r="E161" s="530" t="n"/>
-      <c r="F161" s="479">
-        <f>SUM(F149:F160)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="83" t="n"/>
-      <c r="B162" s="681" t="n"/>
-      <c r="C162" s="681" t="n"/>
-      <c r="D162" s="681" t="n"/>
-      <c r="E162" s="681" t="n"/>
-      <c r="F162" s="675" t="n"/>
+      <c r="C162" s="530" t="n"/>
+      <c r="D162" s="530" t="n"/>
+      <c r="E162" s="530" t="n"/>
+      <c r="F162" s="479">
+        <f>SUM(F150:F161)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="185" t="inlineStr">
+      <c r="A163" s="83" t="n"/>
+      <c r="B163" s="681" t="n"/>
+      <c r="C163" s="681" t="n"/>
+      <c r="D163" s="681" t="n"/>
+      <c r="E163" s="681" t="n"/>
+      <c r="F163" s="675" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="185" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B163" s="677" t="inlineStr">
+      <c r="B164" s="677" t="inlineStr">
         <is>
           <t>INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C163" s="530" t="n"/>
-      <c r="D163" s="530" t="n"/>
-      <c r="E163" s="530" t="n"/>
-      <c r="F163" s="530" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="81" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="B164" s="373" t="inlineStr">
-        <is>
-          <t>Tubería/conduit eléctrica</t>
-        </is>
-      </c>
-      <c r="C164" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D164" s="262" t="n"/>
-      <c r="E164" s="477" t="n"/>
-      <c r="F164" s="478">
-        <f>D164*E164</f>
-        <v/>
-      </c>
+      <c r="C164" s="530" t="n"/>
+      <c r="D164" s="530" t="n"/>
+      <c r="E164" s="530" t="n"/>
+      <c r="F164" s="530" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="81" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="B165" s="373" t="inlineStr">
         <is>
-          <t>Bandejas portacables</t>
+          <t>Tubería/conduit eléctrica</t>
         </is>
       </c>
       <c r="C165" s="261" t="inlineStr">
@@ -14580,17 +14585,17 @@
     <row r="166">
       <c r="A166" s="81" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="B166" s="373" t="inlineStr">
         <is>
-          <t>Cajas eléctricas</t>
+          <t>Bandejas portacables</t>
         </is>
       </c>
       <c r="C166" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D166" s="262" t="n"/>
@@ -14603,17 +14608,17 @@
     <row r="167">
       <c r="A167" s="81" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="B167" s="373" t="inlineStr">
         <is>
-          <t>Cableado de fuerza</t>
+          <t>Cajas eléctricas</t>
         </is>
       </c>
       <c r="C167" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D167" s="262" t="n"/>
@@ -14626,12 +14631,12 @@
     <row r="168">
       <c r="A168" s="81" t="inlineStr">
         <is>
-          <t>14.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="B168" s="373" t="inlineStr">
         <is>
-          <t>Cableado de iluminación</t>
+          <t>Cableado de fuerza</t>
         </is>
       </c>
       <c r="C168" s="261" t="inlineStr">
@@ -14649,17 +14654,17 @@
     <row r="169">
       <c r="A169" s="81" t="inlineStr">
         <is>
-          <t>14.6</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="B169" s="373" t="inlineStr">
         <is>
-          <t>Tableros eléctricos</t>
+          <t>Cableado de iluminación</t>
         </is>
       </c>
       <c r="C169" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D169" s="262" t="n"/>
@@ -14672,12 +14677,12 @@
     <row r="170">
       <c r="A170" s="81" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>14.6</t>
         </is>
       </c>
       <c r="B170" s="373" t="inlineStr">
         <is>
-          <t>Tomacorrientes</t>
+          <t>Tableros eléctricos</t>
         </is>
       </c>
       <c r="C170" s="261" t="inlineStr">
@@ -14695,12 +14700,12 @@
     <row r="171">
       <c r="A171" s="81" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="B171" s="373" t="inlineStr">
         <is>
-          <t>Interruptores</t>
+          <t>Tomacorrientes</t>
         </is>
       </c>
       <c r="C171" s="261" t="inlineStr">
@@ -14718,12 +14723,12 @@
     <row r="172">
       <c r="A172" s="81" t="inlineStr">
         <is>
-          <t>14.9</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="B172" s="373" t="inlineStr">
         <is>
-          <t>Luminarias</t>
+          <t>Interruptores</t>
         </is>
       </c>
       <c r="C172" s="261" t="inlineStr">
@@ -14741,17 +14746,17 @@
     <row r="173">
       <c r="A173" s="81" t="inlineStr">
         <is>
-          <t>14.10</t>
+          <t>14.9</t>
         </is>
       </c>
       <c r="B173" s="373" t="inlineStr">
         <is>
-          <t>Sistema de puesta a tierra</t>
+          <t>Luminarias</t>
         </is>
       </c>
       <c r="C173" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D173" s="262" t="n"/>
@@ -14764,12 +14769,12 @@
     <row r="174">
       <c r="A174" s="81" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>14.10</t>
         </is>
       </c>
       <c r="B174" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificaciones</t>
+          <t>Sistema de puesta a tierra</t>
         </is>
       </c>
       <c r="C174" s="261" t="inlineStr">
@@ -14785,81 +14790,81 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="82" t="n"/>
-      <c r="B175" s="674" t="inlineStr">
+      <c r="A175" s="81" t="inlineStr">
+        <is>
+          <t>14.11</t>
+        </is>
+      </c>
+      <c r="B175" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificaciones</t>
+        </is>
+      </c>
+      <c r="C175" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D175" s="262" t="n"/>
+      <c r="E175" s="477" t="n"/>
+      <c r="F175" s="478">
+        <f>D175*E175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="82" t="n"/>
+      <c r="B176" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 14 - INSTALACIONES ELÉCTRICAS</t>
         </is>
       </c>
-      <c r="C175" s="530" t="n"/>
-      <c r="D175" s="530" t="n"/>
-      <c r="E175" s="530" t="n"/>
-      <c r="F175" s="479">
-        <f>SUM(F164:F174)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="83" t="n"/>
-      <c r="B176" s="681" t="n"/>
-      <c r="C176" s="681" t="n"/>
-      <c r="D176" s="681" t="n"/>
-      <c r="E176" s="681" t="n"/>
-      <c r="F176" s="675" t="n"/>
+      <c r="C176" s="530" t="n"/>
+      <c r="D176" s="530" t="n"/>
+      <c r="E176" s="530" t="n"/>
+      <c r="F176" s="479">
+        <f>SUM(F165:F175)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="185" t="inlineStr">
+      <c r="A177" s="83" t="n"/>
+      <c r="B177" s="681" t="n"/>
+      <c r="C177" s="681" t="n"/>
+      <c r="D177" s="681" t="n"/>
+      <c r="E177" s="681" t="n"/>
+      <c r="F177" s="675" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="185" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B177" s="677" t="inlineStr">
+      <c r="B178" s="677" t="inlineStr">
         <is>
           <t>COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C177" s="530" t="n"/>
-      <c r="D177" s="530" t="n"/>
-      <c r="E177" s="530" t="n"/>
-      <c r="F177" s="530" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="81" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
-      <c r="B178" s="373" t="inlineStr">
-        <is>
-          <t>Cableado estructurado de datos</t>
-        </is>
-      </c>
-      <c r="C178" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D178" s="262" t="n"/>
-      <c r="E178" s="477" t="n"/>
-      <c r="F178" s="478">
-        <f>D178*E178</f>
-        <v/>
-      </c>
+      <c r="C178" s="530" t="n"/>
+      <c r="D178" s="530" t="n"/>
+      <c r="E178" s="530" t="n"/>
+      <c r="F178" s="530" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="81" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="B179" s="373" t="inlineStr">
         <is>
-          <t>Rack de comunicaciones</t>
+          <t>Cableado estructurado de datos</t>
         </is>
       </c>
       <c r="C179" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D179" s="262" t="n"/>
@@ -14872,12 +14877,12 @@
     <row r="180">
       <c r="A180" s="81" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="B180" s="373" t="inlineStr">
         <is>
-          <t>Cámaras y sistema CCTV</t>
+          <t>Rack de comunicaciones</t>
         </is>
       </c>
       <c r="C180" s="261" t="inlineStr">
@@ -14895,12 +14900,12 @@
     <row r="181">
       <c r="A181" s="81" t="inlineStr">
         <is>
-          <t>15.4</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="B181" s="373" t="inlineStr">
         <is>
-          <t>Control de acceso</t>
+          <t>Cámaras y sistema CCTV</t>
         </is>
       </c>
       <c r="C181" s="261" t="inlineStr">
@@ -14918,12 +14923,12 @@
     <row r="182">
       <c r="A182" s="81" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="B182" s="373" t="inlineStr">
         <is>
-          <t>Sistema de citofonía</t>
+          <t>Control de acceso</t>
         </is>
       </c>
       <c r="C182" s="261" t="inlineStr">
@@ -14941,17 +14946,17 @@
     <row r="183">
       <c r="A183" s="81" t="inlineStr">
         <is>
-          <t>15.6</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="B183" s="373" t="inlineStr">
         <is>
-          <t>Sistema de detección de incendios</t>
+          <t>Sistema de citofonía</t>
         </is>
       </c>
       <c r="C183" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D183" s="262" t="n"/>
@@ -14962,81 +14967,81 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="82" t="n"/>
-      <c r="B184" s="674" t="inlineStr">
+      <c r="A184" s="81" t="inlineStr">
+        <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="B184" s="373" t="inlineStr">
+        <is>
+          <t>Sistema de detección de incendios</t>
+        </is>
+      </c>
+      <c r="C184" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D184" s="262" t="n"/>
+      <c r="E184" s="477" t="n"/>
+      <c r="F184" s="478">
+        <f>D184*E184</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="82" t="n"/>
+      <c r="B185" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 15 - COMUNICACIONES Y SEGURIDAD</t>
         </is>
       </c>
-      <c r="C184" s="530" t="n"/>
-      <c r="D184" s="530" t="n"/>
-      <c r="E184" s="530" t="n"/>
-      <c r="F184" s="479">
-        <f>SUM(F178:F183)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="83" t="n"/>
-      <c r="B185" s="681" t="n"/>
-      <c r="C185" s="681" t="n"/>
-      <c r="D185" s="681" t="n"/>
-      <c r="E185" s="681" t="n"/>
-      <c r="F185" s="675" t="n"/>
+      <c r="C185" s="530" t="n"/>
+      <c r="D185" s="530" t="n"/>
+      <c r="E185" s="530" t="n"/>
+      <c r="F185" s="479">
+        <f>SUM(F179:F184)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="185" t="inlineStr">
+      <c r="A186" s="83" t="n"/>
+      <c r="B186" s="681" t="n"/>
+      <c r="C186" s="681" t="n"/>
+      <c r="D186" s="681" t="n"/>
+      <c r="E186" s="681" t="n"/>
+      <c r="F186" s="675" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="185" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B186" s="677" t="inlineStr">
+      <c r="B187" s="677" t="inlineStr">
         <is>
           <t>CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C186" s="530" t="n"/>
-      <c r="D186" s="530" t="n"/>
-      <c r="E186" s="530" t="n"/>
-      <c r="F186" s="530" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="81" t="inlineStr">
-        <is>
-          <t>16.1</t>
-        </is>
-      </c>
-      <c r="B187" s="373" t="inlineStr">
-        <is>
-          <t>Equipos de aire acondicionado</t>
-        </is>
-      </c>
-      <c r="C187" s="261" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D187" s="262" t="n"/>
-      <c r="E187" s="477" t="n"/>
-      <c r="F187" s="478">
-        <f>D187*E187</f>
-        <v/>
-      </c>
+      <c r="C187" s="530" t="n"/>
+      <c r="D187" s="530" t="n"/>
+      <c r="E187" s="530" t="n"/>
+      <c r="F187" s="530" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="81" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="B188" s="373" t="inlineStr">
         <is>
-          <t>Ductos de ventilación</t>
+          <t>Equipos de aire acondicionado</t>
         </is>
       </c>
       <c r="C188" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D188" s="262" t="n"/>
@@ -15049,17 +15054,17 @@
     <row r="189">
       <c r="A189" s="81" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="B189" s="373" t="inlineStr">
         <is>
-          <t>Tubería de refrigerante</t>
+          <t>Ductos de ventilación</t>
         </is>
       </c>
       <c r="C189" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D189" s="262" t="n"/>
@@ -15072,17 +15077,17 @@
     <row r="190">
       <c r="A190" s="81" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="B190" s="373" t="inlineStr">
         <is>
-          <t>Rejillas y difusores</t>
+          <t>Tubería de refrigerante</t>
         </is>
       </c>
       <c r="C190" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D190" s="262" t="n"/>
@@ -15093,81 +15098,81 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="82" t="n"/>
-      <c r="B191" s="674" t="inlineStr">
+      <c r="A191" s="81" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="B191" s="373" t="inlineStr">
+        <is>
+          <t>Rejillas y difusores</t>
+        </is>
+      </c>
+      <c r="C191" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D191" s="262" t="n"/>
+      <c r="E191" s="477" t="n"/>
+      <c r="F191" s="478">
+        <f>D191*E191</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="82" t="n"/>
+      <c r="B192" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 16 - CLIMATIZACIÓN Y VENTILACIÓN</t>
         </is>
       </c>
-      <c r="C191" s="530" t="n"/>
-      <c r="D191" s="530" t="n"/>
-      <c r="E191" s="530" t="n"/>
-      <c r="F191" s="479">
-        <f>SUM(F187:F190)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="83" t="n"/>
-      <c r="B192" s="681" t="n"/>
-      <c r="C192" s="681" t="n"/>
-      <c r="D192" s="681" t="n"/>
-      <c r="E192" s="681" t="n"/>
-      <c r="F192" s="675" t="n"/>
+      <c r="C192" s="530" t="n"/>
+      <c r="D192" s="530" t="n"/>
+      <c r="E192" s="530" t="n"/>
+      <c r="F192" s="479">
+        <f>SUM(F188:F191)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="185" t="inlineStr">
+      <c r="A193" s="83" t="n"/>
+      <c r="B193" s="681" t="n"/>
+      <c r="C193" s="681" t="n"/>
+      <c r="D193" s="681" t="n"/>
+      <c r="E193" s="681" t="n"/>
+      <c r="F193" s="675" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="185" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B193" s="677" t="inlineStr">
+      <c r="B194" s="677" t="inlineStr">
         <is>
           <t>GAS</t>
         </is>
       </c>
-      <c r="C193" s="530" t="n"/>
-      <c r="D193" s="530" t="n"/>
-      <c r="E193" s="530" t="n"/>
-      <c r="F193" s="530" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="81" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="B194" s="373" t="inlineStr">
-        <is>
-          <t>Red interna de gas</t>
-        </is>
-      </c>
-      <c r="C194" s="261" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D194" s="262" t="n"/>
-      <c r="E194" s="477" t="n"/>
-      <c r="F194" s="478">
-        <f>D194*E194</f>
-        <v/>
-      </c>
+      <c r="C194" s="530" t="n"/>
+      <c r="D194" s="530" t="n"/>
+      <c r="E194" s="530" t="n"/>
+      <c r="F194" s="530" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="81" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="B195" s="373" t="inlineStr">
         <is>
-          <t>Válvulas y accesorios</t>
+          <t>Red interna de gas</t>
         </is>
       </c>
       <c r="C195" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D195" s="262" t="n"/>
@@ -15180,17 +15185,17 @@
     <row r="196">
       <c r="A196" s="81" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="B196" s="373" t="inlineStr">
         <is>
-          <t>Pruebas y certificación</t>
+          <t>Válvulas y accesorios</t>
         </is>
       </c>
       <c r="C196" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D196" s="262" t="n"/>
@@ -15201,81 +15206,81 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="82" t="n"/>
-      <c r="B197" s="674" t="inlineStr">
+      <c r="A197" s="81" t="inlineStr">
+        <is>
+          <t>17.3</t>
+        </is>
+      </c>
+      <c r="B197" s="373" t="inlineStr">
+        <is>
+          <t>Pruebas y certificación</t>
+        </is>
+      </c>
+      <c r="C197" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D197" s="262" t="n"/>
+      <c r="E197" s="477" t="n"/>
+      <c r="F197" s="478">
+        <f>D197*E197</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="82" t="n"/>
+      <c r="B198" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 17 - GAS</t>
         </is>
       </c>
-      <c r="C197" s="530" t="n"/>
-      <c r="D197" s="530" t="n"/>
-      <c r="E197" s="530" t="n"/>
-      <c r="F197" s="479">
-        <f>SUM(F194:F196)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="83" t="n"/>
-      <c r="B198" s="681" t="n"/>
-      <c r="C198" s="681" t="n"/>
-      <c r="D198" s="681" t="n"/>
-      <c r="E198" s="681" t="n"/>
-      <c r="F198" s="675" t="n"/>
+      <c r="C198" s="530" t="n"/>
+      <c r="D198" s="530" t="n"/>
+      <c r="E198" s="530" t="n"/>
+      <c r="F198" s="479">
+        <f>SUM(F195:F197)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="185" t="inlineStr">
+      <c r="A199" s="83" t="n"/>
+      <c r="B199" s="681" t="n"/>
+      <c r="C199" s="681" t="n"/>
+      <c r="D199" s="681" t="n"/>
+      <c r="E199" s="681" t="n"/>
+      <c r="F199" s="675" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="185" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B199" s="677" t="inlineStr">
+      <c r="B200" s="677" t="inlineStr">
         <is>
           <t>URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C199" s="530" t="n"/>
-      <c r="D199" s="530" t="n"/>
-      <c r="E199" s="530" t="n"/>
-      <c r="F199" s="530" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="81" t="inlineStr">
-        <is>
-          <t>18.1</t>
-        </is>
-      </c>
-      <c r="B200" s="373" t="inlineStr">
-        <is>
-          <t>Construcción de andenes</t>
-        </is>
-      </c>
-      <c r="C200" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D200" s="262" t="n"/>
-      <c r="E200" s="477" t="n"/>
-      <c r="F200" s="478">
-        <f>D200*E200</f>
-        <v/>
-      </c>
+      <c r="C200" s="530" t="n"/>
+      <c r="D200" s="530" t="n"/>
+      <c r="E200" s="530" t="n"/>
+      <c r="F200" s="530" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="81" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="B201" s="373" t="inlineStr">
         <is>
-          <t>Placas de concreto exteriores</t>
+          <t>Construcción de andenes</t>
         </is>
       </c>
       <c r="C201" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D201" s="262" t="n"/>
@@ -15288,17 +15293,17 @@
     <row r="202">
       <c r="A202" s="81" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="B202" s="373" t="inlineStr">
         <is>
-          <t>Pavimento en adoquín</t>
+          <t>Placas de concreto exteriores</t>
         </is>
       </c>
       <c r="C202" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D202" s="262" t="n"/>
@@ -15311,17 +15316,17 @@
     <row r="203">
       <c r="A203" s="81" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="B203" s="373" t="inlineStr">
         <is>
-          <t>Sardineles y bordillos</t>
+          <t>Pavimento en adoquín</t>
         </is>
       </c>
       <c r="C203" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D203" s="262" t="n"/>
@@ -15334,17 +15339,17 @@
     <row r="204">
       <c r="A204" s="81" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="B204" s="373" t="inlineStr">
         <is>
-          <t>Sumideros exteriores</t>
+          <t>Sardineles y bordillos</t>
         </is>
       </c>
       <c r="C204" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D204" s="262" t="n"/>
@@ -15357,17 +15362,17 @@
     <row r="205">
       <c r="A205" s="81" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="B205" s="373" t="inlineStr">
         <is>
-          <t>Suministro y extendido de tierra vegetal</t>
+          <t>Sumideros exteriores</t>
         </is>
       </c>
       <c r="C205" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>UND</t>
         </is>
       </c>
       <c r="D205" s="262" t="n"/>
@@ -15380,17 +15385,17 @@
     <row r="206">
       <c r="A206" s="81" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="B206" s="373" t="inlineStr">
         <is>
-          <t>Siembra y jardinería</t>
+          <t>Suministro y extendido de tierra vegetal</t>
         </is>
       </c>
       <c r="C206" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D206" s="262" t="n"/>
@@ -15403,12 +15408,12 @@
     <row r="207">
       <c r="A207" s="81" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="B207" s="373" t="inlineStr">
         <is>
-          <t>Geotextil para drenaje y filtración</t>
+          <t>Siembra y jardinería</t>
         </is>
       </c>
       <c r="C207" s="261" t="inlineStr">
@@ -15426,17 +15431,17 @@
     <row r="208">
       <c r="A208" s="81" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="B208" s="373" t="inlineStr">
         <is>
-          <t>Gaviones para obras de contención</t>
+          <t>Geotextil para drenaje y filtración</t>
         </is>
       </c>
       <c r="C208" s="261" t="inlineStr">
         <is>
-          <t>M³</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D208" s="262" t="n"/>
@@ -15449,17 +15454,17 @@
     <row r="209">
       <c r="A209" s="81" t="inlineStr">
         <is>
-          <t>18.10</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="B209" s="373" t="inlineStr">
         <is>
-          <t>Filtro francés (drenaje de terrenos)</t>
+          <t>Gaviones para obras de contención</t>
         </is>
       </c>
       <c r="C209" s="261" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>M³</t>
         </is>
       </c>
       <c r="D209" s="262" t="n"/>
@@ -15472,17 +15477,17 @@
     <row r="210">
       <c r="A210" s="81" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>18.10</t>
         </is>
       </c>
       <c r="B210" s="373" t="inlineStr">
         <is>
-          <t>Revegetalización / empradización</t>
+          <t>Filtro francés (drenaje de terrenos)</t>
         </is>
       </c>
       <c r="C210" s="261" t="inlineStr">
         <is>
-          <t>M²</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D210" s="262" t="n"/>
@@ -15493,81 +15498,81 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="82" t="n"/>
-      <c r="B211" s="674" t="inlineStr">
+      <c r="A211" s="81" t="inlineStr">
+        <is>
+          <t>18.11</t>
+        </is>
+      </c>
+      <c r="B211" s="373" t="inlineStr">
+        <is>
+          <t>Revegetalización / empradización</t>
+        </is>
+      </c>
+      <c r="C211" s="261" t="inlineStr">
+        <is>
+          <t>M²</t>
+        </is>
+      </c>
+      <c r="D211" s="262" t="n"/>
+      <c r="E211" s="477" t="n"/>
+      <c r="F211" s="478">
+        <f>D211*E211</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="82" t="n"/>
+      <c r="B212" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 18 - URBANISMO Y EXTERIORES</t>
         </is>
       </c>
-      <c r="C211" s="530" t="n"/>
-      <c r="D211" s="530" t="n"/>
-      <c r="E211" s="530" t="n"/>
-      <c r="F211" s="479">
-        <f>SUM(F200:F210)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="83" t="n"/>
-      <c r="B212" s="681" t="n"/>
-      <c r="C212" s="681" t="n"/>
-      <c r="D212" s="681" t="n"/>
-      <c r="E212" s="681" t="n"/>
-      <c r="F212" s="675" t="n"/>
+      <c r="C212" s="530" t="n"/>
+      <c r="D212" s="530" t="n"/>
+      <c r="E212" s="530" t="n"/>
+      <c r="F212" s="479">
+        <f>SUM(F201:F211)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="185" t="inlineStr">
+      <c r="A213" s="83" t="n"/>
+      <c r="B213" s="681" t="n"/>
+      <c r="C213" s="681" t="n"/>
+      <c r="D213" s="681" t="n"/>
+      <c r="E213" s="681" t="n"/>
+      <c r="F213" s="675" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="185" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B213" s="677" t="inlineStr">
+      <c r="B214" s="677" t="inlineStr">
         <is>
           <t>OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C213" s="530" t="n"/>
-      <c r="D213" s="530" t="n"/>
-      <c r="E213" s="530" t="n"/>
-      <c r="F213" s="530" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="81" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="B214" s="373" t="inlineStr">
-        <is>
-          <t>Rejas metálicas</t>
-        </is>
-      </c>
-      <c r="C214" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D214" s="262" t="n"/>
-      <c r="E214" s="477" t="n"/>
-      <c r="F214" s="478">
-        <f>D214*E214</f>
-        <v/>
-      </c>
+      <c r="C214" s="530" t="n"/>
+      <c r="D214" s="530" t="n"/>
+      <c r="E214" s="530" t="n"/>
+      <c r="F214" s="530" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="81" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="B215" s="373" t="inlineStr">
         <is>
-          <t>Escaleras metálicas</t>
+          <t>Rejas metálicas</t>
         </is>
       </c>
       <c r="C215" s="261" t="inlineStr">
         <is>
-          <t>KG</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D215" s="262" t="n"/>
@@ -15580,12 +15585,12 @@
     <row r="216">
       <c r="A216" s="81" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="B216" s="373" t="inlineStr">
         <is>
-          <t>Elementos metálicos especiales</t>
+          <t>Escaleras metálicas</t>
         </is>
       </c>
       <c r="C216" s="261" t="inlineStr">
@@ -15603,17 +15608,17 @@
     <row r="217">
       <c r="A217" s="81" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="B217" s="373" t="inlineStr">
         <is>
-          <t>Mobiliario fijo de obra</t>
+          <t>Elementos metálicos especiales</t>
         </is>
       </c>
       <c r="C217" s="261" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>KG</t>
         </is>
       </c>
       <c r="D217" s="262" t="n"/>
@@ -15624,76 +15629,76 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="82" t="n"/>
-      <c r="B218" s="674" t="inlineStr">
+      <c r="A218" s="81" t="inlineStr">
+        <is>
+          <t>19.4</t>
+        </is>
+      </c>
+      <c r="B218" s="373" t="inlineStr">
+        <is>
+          <t>Mobiliario fijo de obra</t>
+        </is>
+      </c>
+      <c r="C218" s="261" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D218" s="262" t="n"/>
+      <c r="E218" s="477" t="n"/>
+      <c r="F218" s="478">
+        <f>D218*E218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="82" t="n"/>
+      <c r="B219" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 19 - OBRAS COMPLEMENTARIAS</t>
         </is>
       </c>
-      <c r="C218" s="530" t="n"/>
-      <c r="D218" s="530" t="n"/>
-      <c r="E218" s="530" t="n"/>
-      <c r="F218" s="479">
-        <f>SUM(F214:F217)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="83" t="n"/>
-      <c r="B219" s="681" t="n"/>
-      <c r="C219" s="681" t="n"/>
-      <c r="D219" s="681" t="n"/>
-      <c r="E219" s="681" t="n"/>
-      <c r="F219" s="675" t="n"/>
+      <c r="C219" s="530" t="n"/>
+      <c r="D219" s="530" t="n"/>
+      <c r="E219" s="530" t="n"/>
+      <c r="F219" s="479">
+        <f>SUM(F215:F218)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="185" t="inlineStr">
+      <c r="A220" s="83" t="n"/>
+      <c r="B220" s="681" t="n"/>
+      <c r="C220" s="681" t="n"/>
+      <c r="D220" s="681" t="n"/>
+      <c r="E220" s="681" t="n"/>
+      <c r="F220" s="675" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="185" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B220" s="677" t="inlineStr">
+      <c r="B221" s="677" t="inlineStr">
         <is>
           <t>ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C220" s="530" t="n"/>
-      <c r="D220" s="530" t="n"/>
-      <c r="E220" s="530" t="n"/>
-      <c r="F220" s="530" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="81" t="inlineStr">
-        <is>
-          <t>20.1</t>
-        </is>
-      </c>
-      <c r="B221" s="373" t="inlineStr">
-        <is>
-          <t>Limpieza gruesa y fina de obra</t>
-        </is>
-      </c>
-      <c r="C221" s="261" t="inlineStr">
-        <is>
-          <t>M²</t>
-        </is>
-      </c>
-      <c r="D221" s="262" t="n"/>
-      <c r="E221" s="477" t="n"/>
-      <c r="F221" s="478">
-        <f>D221*E221</f>
-        <v/>
-      </c>
+      <c r="C221" s="530" t="n"/>
+      <c r="D221" s="530" t="n"/>
+      <c r="E221" s="530" t="n"/>
+      <c r="F221" s="530" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="81" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="B222" s="373" t="inlineStr">
         <is>
-          <t>Limpieza final para entrega</t>
+          <t>Limpieza gruesa y fina de obra</t>
         </is>
       </c>
       <c r="C222" s="261" t="inlineStr">
@@ -15711,17 +15716,17 @@
     <row r="223">
       <c r="A223" s="81" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="B223" s="373" t="inlineStr">
         <is>
-          <t>Pruebas, puesta en marcha y ajustes</t>
+          <t>Limpieza final para entrega</t>
         </is>
       </c>
       <c r="C223" s="261" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>M²</t>
         </is>
       </c>
       <c r="D223" s="262" t="n"/>
@@ -15734,12 +15739,12 @@
     <row r="224">
       <c r="A224" s="81" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="B224" s="373" t="inlineStr">
         <is>
-          <t>Actualización de planos récord / as-built</t>
+          <t>Pruebas, puesta en marcha y ajustes</t>
         </is>
       </c>
       <c r="C224" s="261" t="inlineStr">
@@ -15757,12 +15762,12 @@
     <row r="225">
       <c r="A225" s="81" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="B225" s="373" t="inlineStr">
         <is>
-          <t>Entrega, manuales y acta de recibo</t>
+          <t>Actualización de planos récord / as-built</t>
         </is>
       </c>
       <c r="C225" s="261" t="inlineStr">
@@ -15778,138 +15783,138 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="82" t="n"/>
-      <c r="B226" s="674" t="inlineStr">
+      <c r="A226" s="81" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="B226" s="373" t="inlineStr">
+        <is>
+          <t>Entrega, manuales y acta de recibo</t>
+        </is>
+      </c>
+      <c r="C226" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D226" s="262" t="n"/>
+      <c r="E226" s="477" t="n"/>
+      <c r="F226" s="478">
+        <f>D226*E226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="82" t="n"/>
+      <c r="B227" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 20 - ASEO, ENTREGA Y CIERRE</t>
         </is>
       </c>
-      <c r="C226" s="530" t="n"/>
-      <c r="D226" s="530" t="n"/>
-      <c r="E226" s="530" t="n"/>
-      <c r="F226" s="479">
-        <f>SUM(F221:F225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="83" t="n"/>
-      <c r="B227" s="681" t="n"/>
-      <c r="C227" s="681" t="n"/>
-      <c r="D227" s="681" t="n"/>
-      <c r="E227" s="681" t="n"/>
-      <c r="F227" s="675" t="n"/>
+      <c r="C227" s="530" t="n"/>
+      <c r="D227" s="530" t="n"/>
+      <c r="E227" s="530" t="n"/>
+      <c r="F227" s="479">
+        <f>SUM(F222:F226)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="185" t="inlineStr">
+      <c r="A228" s="83" t="n"/>
+      <c r="B228" s="681" t="n"/>
+      <c r="C228" s="681" t="n"/>
+      <c r="D228" s="681" t="n"/>
+      <c r="E228" s="681" t="n"/>
+      <c r="F228" s="675" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="185" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B228" s="677" t="inlineStr">
+      <c r="B229" s="677" t="inlineStr">
         <is>
           <t>ASCENSORES</t>
         </is>
       </c>
-      <c r="C228" s="530" t="n"/>
-      <c r="D228" s="530" t="n"/>
-      <c r="E228" s="530" t="n"/>
-      <c r="F228" s="530" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="81" t="inlineStr">
+      <c r="C229" s="530" t="n"/>
+      <c r="D229" s="530" t="n"/>
+      <c r="E229" s="530" t="n"/>
+      <c r="F229" s="530" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="81" t="inlineStr">
         <is>
           <t>21.1</t>
         </is>
       </c>
-      <c r="B229" s="373" t="inlineStr">
+      <c r="B230" s="373" t="inlineStr">
         <is>
           <t>Suministro e instalación de ascensor eléctrico</t>
         </is>
       </c>
-      <c r="C229" s="261" t="inlineStr">
+      <c r="C230" s="261" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D229" s="262" t="n"/>
-      <c r="E229" s="477" t="n"/>
-      <c r="F229" s="478">
-        <f>D229*E229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="82" t="n"/>
-      <c r="B230" s="674" t="inlineStr">
+      <c r="D230" s="262" t="n"/>
+      <c r="E230" s="477" t="n"/>
+      <c r="F230" s="478">
+        <f>D230*E230</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="82" t="n"/>
+      <c r="B231" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 21 - ASCENSORES</t>
         </is>
       </c>
-      <c r="C230" s="530" t="n"/>
-      <c r="D230" s="530" t="n"/>
-      <c r="E230" s="530" t="n"/>
-      <c r="F230" s="479">
-        <f>SUM(F229:F229)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="83" t="n"/>
-      <c r="B231" s="681" t="n"/>
-      <c r="C231" s="681" t="n"/>
-      <c r="D231" s="681" t="n"/>
-      <c r="E231" s="681" t="n"/>
-      <c r="F231" s="675" t="n"/>
+      <c r="C231" s="530" t="n"/>
+      <c r="D231" s="530" t="n"/>
+      <c r="E231" s="530" t="n"/>
+      <c r="F231" s="479">
+        <f>SUM(F230:F230)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="185" t="inlineStr">
+      <c r="A232" s="83" t="n"/>
+      <c r="B232" s="681" t="n"/>
+      <c r="C232" s="681" t="n"/>
+      <c r="D232" s="681" t="n"/>
+      <c r="E232" s="681" t="n"/>
+      <c r="F232" s="675" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="185" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B232" s="677" t="inlineStr">
+      <c r="B233" s="677" t="inlineStr">
         <is>
           <t>GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C232" s="530" t="n"/>
-      <c r="D232" s="530" t="n"/>
-      <c r="E232" s="530" t="n"/>
-      <c r="F232" s="530" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="81" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="B233" s="373" t="inlineStr">
-        <is>
-          <t>Estudio de suelos y geotecnia</t>
-        </is>
-      </c>
-      <c r="C233" s="261" t="inlineStr">
-        <is>
-          <t>GL</t>
-        </is>
-      </c>
-      <c r="D233" s="262" t="n"/>
-      <c r="E233" s="477" t="n"/>
-      <c r="F233" s="478">
-        <f>D233*E233</f>
-        <v/>
-      </c>
+      <c r="C233" s="530" t="n"/>
+      <c r="D233" s="530" t="n"/>
+      <c r="E233" s="530" t="n"/>
+      <c r="F233" s="530" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="81" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="B234" s="373" t="inlineStr">
         <is>
-          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
+          <t>Estudio de suelos y geotecnia</t>
         </is>
       </c>
       <c r="C234" s="261" t="inlineStr">
@@ -15927,12 +15932,12 @@
     <row r="235">
       <c r="A235" s="81" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="B235" s="373" t="inlineStr">
         <is>
-          <t>Licencia de construcción y trámites de curaduría urbana</t>
+          <t>Diseños arquitectónicos, estructurales, hidrosanitarios y eléctricos</t>
         </is>
       </c>
       <c r="C235" s="261" t="inlineStr">
@@ -15950,12 +15955,12 @@
     <row r="236">
       <c r="A236" s="81" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="B236" s="373" t="inlineStr">
         <is>
-          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+          <t>Licencia de construcción y trámites de curaduría urbana</t>
         </is>
       </c>
       <c r="C236" s="261" t="inlineStr">
@@ -15971,84 +15976,89 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="82" t="n"/>
-      <c r="B237" s="674" t="inlineStr">
+      <c r="A237" s="81" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="B237" s="373" t="inlineStr">
+        <is>
+          <t>Póliza de estabilidad de obra y seguros de construcción (todo riesgo)</t>
+        </is>
+      </c>
+      <c r="C237" s="261" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D237" s="262" t="n"/>
+      <c r="E237" s="477" t="n"/>
+      <c r="F237" s="478">
+        <f>D237*E237</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="82" t="n"/>
+      <c r="B238" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL CAPÍTULO 22 - GESTIÓN, DISEÑO Y ADMINISTRACIÓN</t>
         </is>
       </c>
-      <c r="C237" s="530" t="n"/>
-      <c r="D237" s="530" t="n"/>
-      <c r="E237" s="530" t="n"/>
-      <c r="F237" s="479">
-        <f>SUM(F233:F236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="83" t="n"/>
-      <c r="B238" s="681" t="n"/>
-      <c r="C238" s="681" t="n"/>
-      <c r="D238" s="681" t="n"/>
-      <c r="E238" s="681" t="n"/>
-      <c r="F238" s="675" t="n"/>
-    </row>
-    <row r="239" ht="15" customHeight="1" s="1223">
-      <c r="A239" s="84" t="n"/>
-      <c r="B239" s="676" t="inlineStr">
+      <c r="C238" s="530" t="n"/>
+      <c r="D238" s="530" t="n"/>
+      <c r="E238" s="530" t="n"/>
+      <c r="F238" s="479">
+        <f>SUM(F234:F237)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="83" t="n"/>
+      <c r="B239" s="681" t="n"/>
+      <c r="C239" s="681" t="n"/>
+      <c r="D239" s="681" t="n"/>
+      <c r="E239" s="681" t="n"/>
+      <c r="F239" s="675" t="n"/>
+    </row>
+    <row r="240" ht="15" customHeight="1" s="1223">
+      <c r="A240" s="84" t="n"/>
+      <c r="B240" s="676" t="inlineStr">
         <is>
           <t>COSTO DIRECTO TOTAL (suma de capítulos 1 a 22)</t>
         </is>
       </c>
-      <c r="C239" s="530" t="n"/>
-      <c r="D239" s="530" t="n"/>
-      <c r="E239" s="530" t="n"/>
-      <c r="F239" s="480">
-        <f>F25+F39+F49+F68+F80+F92+F99+F106+F120+F128+F139+F146+F161+F175+F184+F191+F197+F211+F218+F226+F230+F237</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="85" t="n"/>
-      <c r="B240" s="28" t="n"/>
-      <c r="C240" s="28" t="n"/>
-      <c r="D240" s="28" t="n"/>
-      <c r="E240" s="28" t="n"/>
-      <c r="F240" s="86" t="n"/>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="1223">
-      <c r="A241" s="83" t="n"/>
-      <c r="B241" s="46" t="inlineStr">
-        <is>
-          <t>Administración (A)</t>
-        </is>
-      </c>
-      <c r="C241" s="681" t="n"/>
-      <c r="D241" s="681" t="n"/>
-      <c r="E241" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$29</f>
-        <v/>
-      </c>
-      <c r="F241" s="482">
-        <f>F239*E241</f>
-        <v/>
-      </c>
+      <c r="C240" s="530" t="n"/>
+      <c r="D240" s="530" t="n"/>
+      <c r="E240" s="530" t="n"/>
+      <c r="F240" s="480">
+        <f>F25+F39+F49+F69+F81+F93+F100+F107+F121+F129+F140+F147+F162+F176+F185+F192+F198+F212+F219+F227+F231+F238</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="85" t="n"/>
+      <c r="B241" s="28" t="n"/>
+      <c r="C241" s="28" t="n"/>
+      <c r="D241" s="28" t="n"/>
+      <c r="E241" s="28" t="n"/>
+      <c r="F241" s="86" t="n"/>
     </row>
     <row r="242" ht="15" customHeight="1" s="1223">
       <c r="A242" s="83" t="n"/>
       <c r="B242" s="46" t="inlineStr">
         <is>
-          <t>Imprevistos (I)</t>
+          <t>Administración (A)</t>
         </is>
       </c>
       <c r="C242" s="681" t="n"/>
       <c r="D242" s="681" t="n"/>
       <c r="E242" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <f>'Ficha Técnica del Proyecto'!$B$29</f>
         <v/>
       </c>
       <c r="F242" s="482">
-        <f>F239*E242</f>
+        <f>F240*E242</f>
         <v/>
       </c>
     </row>
@@ -16056,47 +16066,50 @@
       <c r="A243" s="83" t="n"/>
       <c r="B243" s="46" t="inlineStr">
         <is>
-          <t>Utilidad (U)</t>
+          <t>Imprevistos (I)</t>
         </is>
       </c>
       <c r="C243" s="681" t="n"/>
       <c r="D243" s="681" t="n"/>
       <c r="E243" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$30</f>
+        <v/>
+      </c>
+      <c r="F243" s="482">
+        <f>F240*E243</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="1223">
+      <c r="A244" s="83" t="n"/>
+      <c r="B244" s="46" t="inlineStr">
+        <is>
+          <t>Utilidad (U)</t>
+        </is>
+      </c>
+      <c r="C244" s="681" t="n"/>
+      <c r="D244" s="681" t="n"/>
+      <c r="E244" s="481">
         <f>'Ficha Técnica del Proyecto'!$B$31</f>
         <v/>
       </c>
-      <c r="F243" s="482">
-        <f>F239*E243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="1223">
-      <c r="A244" s="82" t="n"/>
-      <c r="B244" s="674" t="inlineStr">
+      <c r="F244" s="482">
+        <f>F240*E244</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="1223">
+      <c r="A245" s="82" t="n"/>
+      <c r="B245" s="674" t="inlineStr">
         <is>
           <t>SUBTOTAL AIU (A+I+U)</t>
         </is>
       </c>
-      <c r="C244" s="29" t="n"/>
-      <c r="D244" s="29" t="n"/>
-      <c r="E244" s="30" t="n"/>
-      <c r="F244" s="479">
-        <f>F241+F242+F243</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="1223">
-      <c r="A245" s="83" t="n"/>
-      <c r="B245" s="46" t="inlineStr">
-        <is>
-          <t>COSTO DIRECTO + AIU</t>
-        </is>
-      </c>
-      <c r="C245" s="681" t="n"/>
-      <c r="D245" s="681" t="n"/>
-      <c r="E245" s="47" t="n"/>
-      <c r="F245" s="482">
-        <f>F239+F244</f>
+      <c r="C245" s="29" t="n"/>
+      <c r="D245" s="29" t="n"/>
+      <c r="E245" s="30" t="n"/>
+      <c r="F245" s="479">
+        <f>F242+F243+F244</f>
         <v/>
       </c>
     </row>
@@ -16104,103 +16117,110 @@
       <c r="A246" s="83" t="n"/>
       <c r="B246" s="46" t="inlineStr">
         <is>
-          <t>IVA sobre Utilidad (19%)</t>
+          <t>COSTO DIRECTO + AIU</t>
         </is>
       </c>
       <c r="C246" s="681" t="n"/>
       <c r="D246" s="681" t="n"/>
-      <c r="E246" s="481">
-        <f>'Ficha Técnica del Proyecto'!$B$32</f>
-        <v/>
-      </c>
+      <c r="E246" s="47" t="n"/>
       <c r="F246" s="482">
-        <f>F243*E246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247">
+        <f>F240+F245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="1223">
       <c r="A247" s="83" t="n"/>
-      <c r="B247" s="681" t="n"/>
+      <c r="B247" s="46" t="inlineStr">
+        <is>
+          <t>IVA sobre Utilidad (19%)</t>
+        </is>
+      </c>
       <c r="C247" s="681" t="n"/>
       <c r="D247" s="681" t="n"/>
-      <c r="E247" s="681" t="n"/>
-      <c r="F247" s="675" t="n"/>
-    </row>
-    <row r="248" ht="24" customHeight="1" s="1223">
-      <c r="A248" s="87" t="n"/>
-      <c r="B248" s="677" t="inlineStr">
+      <c r="E247" s="481">
+        <f>'Ficha Técnica del Proyecto'!$B$32</f>
+        <v/>
+      </c>
+      <c r="F247" s="482">
+        <f>F244*E247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="83" t="n"/>
+      <c r="B248" s="681" t="n"/>
+      <c r="C248" s="681" t="n"/>
+      <c r="D248" s="681" t="n"/>
+      <c r="E248" s="681" t="n"/>
+      <c r="F248" s="675" t="n"/>
+    </row>
+    <row r="249" ht="24" customHeight="1" s="1223">
+      <c r="A249" s="87" t="n"/>
+      <c r="B249" s="677" t="inlineStr">
         <is>
           <t>PRESUPUESTO TOTAL DE OBRA</t>
         </is>
       </c>
-      <c r="C248" s="530" t="n"/>
-      <c r="D248" s="530" t="n"/>
-      <c r="E248" s="530" t="n"/>
-      <c r="F248" s="483">
-        <f>F245+F246</f>
-        <v/>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="88" t="n"/>
-      <c r="B249" s="206" t="inlineStr">
-        <is>
-          <t>REV. 10/09/2026</t>
-        </is>
-      </c>
-      <c r="C249" s="281" t="n"/>
-      <c r="D249" s="281" t="n"/>
-      <c r="E249" s="281" t="n"/>
-      <c r="F249" s="350">
-        <f>F6</f>
+      <c r="C249" s="530" t="n"/>
+      <c r="D249" s="530" t="n"/>
+      <c r="E249" s="530" t="n"/>
+      <c r="F249" s="483">
+        <f>F246+F247</f>
         <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="88" t="n"/>
-      <c r="B250" s="206" t="n"/>
+      <c r="B250" s="206" t="inlineStr">
+        <is>
+          <t>REV. 10/09/2026</t>
+        </is>
+      </c>
       <c r="C250" s="281" t="n"/>
       <c r="D250" s="281" t="n"/>
       <c r="E250" s="281" t="n"/>
-      <c r="F250" s="204" t="n"/>
-    </row>
-    <row r="251" ht="15" customHeight="1" s="1223">
+      <c r="F250" s="350">
+        <f>F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251">
       <c r="A251" s="88" t="n"/>
-      <c r="B251" s="90" t="inlineStr">
+      <c r="B251" s="206" t="n"/>
+      <c r="C251" s="281" t="n"/>
+      <c r="D251" s="281" t="n"/>
+      <c r="E251" s="281" t="n"/>
+      <c r="F251" s="204" t="n"/>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="1223">
+      <c r="A252" s="88" t="n"/>
+      <c r="B252" s="90" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Costo Directo Total)</t>
         </is>
       </c>
-      <c r="C251" s="91" t="n"/>
-      <c r="D251" s="91" t="n"/>
-      <c r="E251" s="91" t="n"/>
-      <c r="F251" s="484">
-        <f>F239/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="1223">
-      <c r="A252" s="89" t="n"/>
-      <c r="B252" s="92" t="inlineStr">
+      <c r="C252" s="91" t="n"/>
+      <c r="D252" s="91" t="n"/>
+      <c r="E252" s="91" t="n"/>
+      <c r="F252" s="484">
+        <f>F240/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="1223">
+      <c r="A253" s="89" t="n"/>
+      <c r="B253" s="92" t="inlineStr">
         <is>
           <t>Costo por m² construido (sobre Presupuesto Total)</t>
         </is>
       </c>
-      <c r="C252" s="93" t="n"/>
-      <c r="D252" s="93" t="n"/>
-      <c r="E252" s="93" t="n"/>
-      <c r="F252" s="485">
-        <f>F248/'Ficha Técnica del Proyecto'!$B$21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="27" t="n"/>
-      <c r="B253" s="281" t="n"/>
-      <c r="C253" s="281" t="n"/>
-      <c r="D253" s="281" t="n"/>
-      <c r="E253" s="281" t="n"/>
-      <c r="F253" s="281" t="n"/>
+      <c r="C253" s="93" t="n"/>
+      <c r="D253" s="93" t="n"/>
+      <c r="E253" s="93" t="n"/>
+      <c r="F253" s="485">
+        <f>F249/'Ficha Técnica del Proyecto'!$B$21</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="27" t="n"/>
@@ -16242,69 +16262,77 @@
       <c r="E258" s="281" t="n"/>
       <c r="F258" s="281" t="n"/>
     </row>
+    <row r="259">
+      <c r="A259" s="27" t="n"/>
+      <c r="B259" s="281" t="n"/>
+      <c r="C259" s="281" t="n"/>
+      <c r="D259" s="281" t="n"/>
+      <c r="E259" s="281" t="n"/>
+      <c r="F259" s="281" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B211:E211"/>
-    <mergeCell ref="B226:E226"/>
-    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B109:F109"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B239:E239"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B232:F232"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B200:F200"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B192:E192"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B199:F199"/>
-    <mergeCell ref="B68:E68"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B139:E139"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B80:E80"/>
-    <mergeCell ref="B220:F220"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B214:F214"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B102:F102"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B70:F70"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B197:E197"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="B237:E237"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B218:E218"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B129:E129"/>
     <mergeCell ref="B100:E100"/>
+    <mergeCell ref="B229:F229"/>
+    <mergeCell ref="B227:E227"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B185:E185"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B148:F148"/>
-    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B121:E121"/>
+    <mergeCell ref="B93:E93"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B184:E184"/>
+    <mergeCell ref="B140:E140"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B161:E161"/>
+    <mergeCell ref="B238:E238"/>
+    <mergeCell ref="B178:F178"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B219:E219"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B240:E240"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B187:F187"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="B83:F83"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="C1:F3"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B147:E147"/>
+    <mergeCell ref="B249:E249"/>
+    <mergeCell ref="B162:E162"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B191:E191"/>
-    <mergeCell ref="B213:F213"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B41:F41"/>
   </mergeCells>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" paperSize="9" scale="53" horizontalDpi="300" verticalDpi="300"/>
@@ -16528,7 +16556,7 @@
       <c r="J14" s="530" t="n"/>
       <c r="K14" s="530" t="n"/>
       <c r="L14" s="1086">
-        <f>'Presupuesto '!F248</f>
+        <f>'Presupuesto '!F249</f>
         <v/>
       </c>
       <c r="M14" s="530" t="n"/>
@@ -16767,7 +16795,7 @@
       <c r="B24" s="530" t="n"/>
       <c r="C24" s="654" t="n"/>
       <c r="D24" s="514">
-        <f>'Presupuesto '!F25/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F25/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E24" s="80" t="n"/>
@@ -16801,7 +16829,7 @@
       <c r="B25" s="530" t="n"/>
       <c r="C25" s="654" t="n"/>
       <c r="D25" s="514">
-        <f>'Presupuesto '!F39/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F39/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E25" s="80" t="n"/>
@@ -16835,7 +16863,7 @@
       <c r="B26" s="530" t="n"/>
       <c r="C26" s="654" t="n"/>
       <c r="D26" s="514">
-        <f>'Presupuesto '!F49/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F49/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E26" s="80" t="n"/>
@@ -16869,7 +16897,7 @@
       <c r="B27" s="530" t="n"/>
       <c r="C27" s="654" t="n"/>
       <c r="D27" s="514">
-        <f>'Presupuesto '!F68/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F69/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E27" s="80" t="n"/>
@@ -16903,7 +16931,7 @@
       <c r="B28" s="530" t="n"/>
       <c r="C28" s="654" t="n"/>
       <c r="D28" s="514">
-        <f>'Presupuesto '!F80/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F81/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E28" s="80" t="n"/>
@@ -16937,7 +16965,7 @@
       <c r="B29" s="530" t="n"/>
       <c r="C29" s="654" t="n"/>
       <c r="D29" s="514">
-        <f>'Presupuesto '!F92/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F93/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E29" s="80" t="n"/>
@@ -16971,7 +16999,7 @@
       <c r="B30" s="530" t="n"/>
       <c r="C30" s="654" t="n"/>
       <c r="D30" s="514">
-        <f>'Presupuesto '!F99/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F100/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E30" s="80" t="n"/>
@@ -17005,7 +17033,7 @@
       <c r="B31" s="530" t="n"/>
       <c r="C31" s="654" t="n"/>
       <c r="D31" s="514">
-        <f>'Presupuesto '!F106/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F107/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E31" s="80" t="n"/>
@@ -17039,7 +17067,7 @@
       <c r="B32" s="530" t="n"/>
       <c r="C32" s="654" t="n"/>
       <c r="D32" s="514">
-        <f>'Presupuesto '!F120/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F121/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E32" s="80" t="n"/>
@@ -17073,7 +17101,7 @@
       <c r="B33" s="530" t="n"/>
       <c r="C33" s="654" t="n"/>
       <c r="D33" s="514">
-        <f>'Presupuesto '!F128/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F129/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E33" s="80" t="n"/>
@@ -17107,7 +17135,7 @@
       <c r="B34" s="530" t="n"/>
       <c r="C34" s="654" t="n"/>
       <c r="D34" s="514">
-        <f>'Presupuesto '!F139/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F140/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E34" s="80" t="n"/>
@@ -17141,7 +17169,7 @@
       <c r="B35" s="530" t="n"/>
       <c r="C35" s="654" t="n"/>
       <c r="D35" s="514">
-        <f>'Presupuesto '!F146/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F147/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E35" s="80" t="n"/>
@@ -17175,7 +17203,7 @@
       <c r="B36" s="530" t="n"/>
       <c r="C36" s="654" t="n"/>
       <c r="D36" s="514">
-        <f>'Presupuesto '!F161/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F162/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E36" s="80" t="n"/>
@@ -17209,7 +17237,7 @@
       <c r="B37" s="530" t="n"/>
       <c r="C37" s="654" t="n"/>
       <c r="D37" s="514">
-        <f>'Presupuesto '!F175/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F176/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E37" s="80" t="n"/>
@@ -17243,7 +17271,7 @@
       <c r="B38" s="530" t="n"/>
       <c r="C38" s="654" t="n"/>
       <c r="D38" s="514">
-        <f>'Presupuesto '!F184/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F185/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E38" s="80" t="n"/>
@@ -17277,7 +17305,7 @@
       <c r="B39" s="530" t="n"/>
       <c r="C39" s="654" t="n"/>
       <c r="D39" s="517">
-        <f>'Presupuesto '!F191/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F192/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E39" s="265" t="n"/>
@@ -17308,7 +17336,7 @@
       <c r="B40" s="530" t="n"/>
       <c r="C40" s="654" t="n"/>
       <c r="D40" s="517">
-        <f>'Presupuesto '!F197/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F198/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E40" s="265" t="n"/>
@@ -17339,7 +17367,7 @@
       <c r="B41" s="530" t="n"/>
       <c r="C41" s="654" t="n"/>
       <c r="D41" s="517">
-        <f>'Presupuesto '!F211/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F212/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E41" s="265" t="n"/>
@@ -17370,7 +17398,7 @@
       <c r="B42" s="530" t="n"/>
       <c r="C42" s="654" t="n"/>
       <c r="D42" s="517">
-        <f>'Presupuesto '!F218/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F219/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E42" s="265" t="n"/>
@@ -17401,7 +17429,7 @@
       <c r="B43" s="530" t="n"/>
       <c r="C43" s="654" t="n"/>
       <c r="D43" s="517">
-        <f>'Presupuesto '!F226/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F227/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E43" s="265" t="n"/>
@@ -17432,7 +17460,7 @@
       <c r="B44" s="530" t="n"/>
       <c r="C44" s="654" t="n"/>
       <c r="D44" s="517">
-        <f>'Presupuesto '!F230/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F231/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E44" s="265" t="n"/>
@@ -17463,7 +17491,7 @@
       <c r="B45" s="530" t="n"/>
       <c r="C45" s="654" t="n"/>
       <c r="D45" s="517">
-        <f>'Presupuesto '!F237/'Presupuesto '!$F$239</f>
+        <f>'Presupuesto '!F238/'Presupuesto '!$F$240</f>
         <v/>
       </c>
       <c r="E45" s="265" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -25,6 +25,7 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="170">
     <font>
@@ -1690,7 +1691,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6575,6 +6576,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6584,7 +6599,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1309">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9814,6 +9829,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10759,7 +10786,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11330,7 +11356,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16344,7 +16369,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N122"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10405,31 +10405,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10771,7 +10771,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11342,7 +11341,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16356,7 +16354,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N122"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Informe Semanal" sheetId="3" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Semanal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -9982,439 +9983,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -10460,7 +10028,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10505,7 +10073,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11290,7 +10858,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11323,8 +10890,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11337,7 +10905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -16350,7 +15918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -16590,7 +16158,7 @@
       <c r="H15" s="654" t="n"/>
       <c r="I15" s="1066" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>Período (Semana)</t>
         </is>
       </c>
       <c r="J15" s="530" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
     <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="170">
+  <fonts count="171">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1242,6 +1242,11 @@
       <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="76">
     <fill>
@@ -1692,7 +1697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="412">
+  <borders count="414">
     <border>
       <left/>
       <right/>
@@ -6590,6 +6595,28 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB8C2CC"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.3499862666707358"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.5999633777886288"/>
       </bottom>
     </border>
   </borders>
@@ -6600,7 +6627,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1319">
+  <cellXfs count="1334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9852,6 +9879,51 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="107" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="116" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="91" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="249" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="126" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="291" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="46" fillId="0" borderId="292" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="338" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="412" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="413" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16033,10 +16105,10 @@
           <t>Versión</t>
         </is>
       </c>
-      <c r="M9" s="199" t="n">
+      <c r="M9" s="982" t="n">
         <v>1</v>
       </c>
-      <c r="N9" s="982" t="n"/>
+      <c r="N9" s="565" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="1223">
       <c r="A10" s="1258" t="n"/>
@@ -17177,11 +17249,11 @@
       <c r="D49" s="581" t="n"/>
       <c r="E49" s="581" t="n"/>
       <c r="F49" s="581" t="n"/>
-      <c r="G49" s="1067" t="n"/>
+      <c r="G49" s="1319" t="n"/>
       <c r="H49" s="581" t="n"/>
       <c r="I49" s="581" t="n"/>
       <c r="J49" s="581" t="n"/>
-      <c r="K49" s="582" t="n"/>
+      <c r="K49" s="1331" t="n"/>
       <c r="L49" s="581" t="n"/>
       <c r="M49" s="581" t="n"/>
       <c r="N49" s="582" t="n"/>
@@ -17193,14 +17265,14 @@
       <c r="D50" s="530" t="n"/>
       <c r="E50" s="530" t="n"/>
       <c r="F50" s="530" t="n"/>
-      <c r="G50" s="1107" t="n"/>
+      <c r="G50" s="1035" t="n"/>
       <c r="H50" s="530" t="n"/>
       <c r="I50" s="1045" t="n"/>
       <c r="J50" s="530" t="n"/>
-      <c r="K50" s="1077" t="n"/>
-      <c r="L50" s="1018" t="n"/>
-      <c r="M50" s="1018" t="n"/>
-      <c r="N50" s="1019" t="n"/>
+      <c r="K50" s="1332" t="n"/>
+      <c r="L50" s="530" t="n"/>
+      <c r="M50" s="530" t="n"/>
+      <c r="N50" s="579" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1015" t="n"/>
@@ -17213,8 +17285,10 @@
       <c r="H51" s="530" t="n"/>
       <c r="I51" s="1045" t="n"/>
       <c r="J51" s="530" t="n"/>
-      <c r="K51" s="1071" t="n"/>
-      <c r="N51" s="546" t="n"/>
+      <c r="K51" s="1332" t="n"/>
+      <c r="L51" s="530" t="n"/>
+      <c r="M51" s="530" t="n"/>
+      <c r="N51" s="579" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="1015" t="n"/>
@@ -17227,8 +17301,10 @@
       <c r="H52" s="530" t="n"/>
       <c r="I52" s="1045" t="n"/>
       <c r="J52" s="530" t="n"/>
-      <c r="K52" s="1071" t="n"/>
-      <c r="N52" s="546" t="n"/>
+      <c r="K52" s="1332" t="n"/>
+      <c r="L52" s="530" t="n"/>
+      <c r="M52" s="530" t="n"/>
+      <c r="N52" s="579" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1026" t="n"/>
@@ -17241,8 +17317,10 @@
       <c r="H53" s="530" t="n"/>
       <c r="I53" s="530" t="n"/>
       <c r="J53" s="530" t="n"/>
-      <c r="K53" s="1059" t="n"/>
-      <c r="N53" s="546" t="n"/>
+      <c r="K53" s="1332" t="n"/>
+      <c r="L53" s="530" t="n"/>
+      <c r="M53" s="530" t="n"/>
+      <c r="N53" s="579" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1026" t="n"/>
@@ -17255,8 +17333,10 @@
       <c r="H54" s="530" t="n"/>
       <c r="I54" s="530" t="n"/>
       <c r="J54" s="530" t="n"/>
-      <c r="K54" s="1059" t="n"/>
-      <c r="N54" s="546" t="n"/>
+      <c r="K54" s="1332" t="n"/>
+      <c r="L54" s="530" t="n"/>
+      <c r="M54" s="530" t="n"/>
+      <c r="N54" s="579" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="1026" t="n"/>
@@ -17269,8 +17349,10 @@
       <c r="H55" s="530" t="n"/>
       <c r="I55" s="530" t="n"/>
       <c r="J55" s="530" t="n"/>
-      <c r="K55" s="1059" t="n"/>
-      <c r="N55" s="546" t="n"/>
+      <c r="K55" s="1332" t="n"/>
+      <c r="L55" s="530" t="n"/>
+      <c r="M55" s="530" t="n"/>
+      <c r="N55" s="579" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1026" t="n"/>
@@ -17283,8 +17365,10 @@
       <c r="H56" s="530" t="n"/>
       <c r="I56" s="530" t="n"/>
       <c r="J56" s="530" t="n"/>
-      <c r="K56" s="1059" t="n"/>
-      <c r="N56" s="546" t="n"/>
+      <c r="K56" s="1332" t="n"/>
+      <c r="L56" s="530" t="n"/>
+      <c r="M56" s="530" t="n"/>
+      <c r="N56" s="579" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1026" t="n"/>
@@ -17297,8 +17381,10 @@
       <c r="H57" s="530" t="n"/>
       <c r="I57" s="530" t="n"/>
       <c r="J57" s="530" t="n"/>
-      <c r="K57" s="1059" t="n"/>
-      <c r="N57" s="546" t="n"/>
+      <c r="K57" s="1332" t="n"/>
+      <c r="L57" s="530" t="n"/>
+      <c r="M57" s="530" t="n"/>
+      <c r="N57" s="579" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="1223">
       <c r="A58" s="1083" t="inlineStr">
@@ -17335,7 +17421,7 @@
       </c>
       <c r="B60" s="1079" t="n"/>
       <c r="C60" s="1079" t="n"/>
-      <c r="D60" s="270" t="inlineStr">
+      <c r="D60" s="1323" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
@@ -17371,8 +17457,8 @@
       <c r="A61" s="1087" t="n"/>
       <c r="B61" s="1088" t="n"/>
       <c r="C61" s="1089" t="n"/>
-      <c r="D61" s="268" t="n"/>
-      <c r="E61" s="1104" t="n"/>
+      <c r="D61" s="1324" t="n"/>
+      <c r="E61" s="1325" t="n"/>
       <c r="F61" s="1089" t="n"/>
       <c r="G61" s="269" t="n"/>
       <c r="H61" s="1087" t="n"/>
@@ -17380,15 +17466,15 @@
       <c r="J61" s="1089" t="n"/>
       <c r="K61" s="1121" t="n"/>
       <c r="L61" s="1089" t="n"/>
-      <c r="M61" s="1122" t="n"/>
+      <c r="M61" s="1325" t="n"/>
       <c r="N61" s="1089" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="1038" t="n"/>
       <c r="B62" s="530" t="n"/>
       <c r="C62" s="654" t="n"/>
-      <c r="D62" s="1038" t="n"/>
-      <c r="E62" s="1014" t="n"/>
+      <c r="D62" s="1326" t="n"/>
+      <c r="E62" s="1327" t="n"/>
       <c r="F62" s="654" t="n"/>
       <c r="G62" s="267" t="n"/>
       <c r="H62" s="1038" t="n"/>
@@ -17396,15 +17482,15 @@
       <c r="J62" s="654" t="n"/>
       <c r="K62" s="1061" t="n"/>
       <c r="L62" s="654" t="n"/>
-      <c r="M62" s="1049" t="n"/>
+      <c r="M62" s="1327" t="n"/>
       <c r="N62" s="654" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1038" t="n"/>
       <c r="B63" s="530" t="n"/>
       <c r="C63" s="654" t="n"/>
-      <c r="D63" s="1038" t="n"/>
-      <c r="E63" s="1014" t="n"/>
+      <c r="D63" s="1326" t="n"/>
+      <c r="E63" s="1327" t="n"/>
       <c r="F63" s="654" t="n"/>
       <c r="G63" s="267" t="n"/>
       <c r="H63" s="1038" t="n"/>
@@ -17412,15 +17498,15 @@
       <c r="J63" s="654" t="n"/>
       <c r="K63" s="1061" t="n"/>
       <c r="L63" s="654" t="n"/>
-      <c r="M63" s="1049" t="n"/>
+      <c r="M63" s="1327" t="n"/>
       <c r="N63" s="654" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="1038" t="n"/>
       <c r="B64" s="530" t="n"/>
       <c r="C64" s="654" t="n"/>
-      <c r="D64" s="1038" t="n"/>
-      <c r="E64" s="1014" t="n"/>
+      <c r="D64" s="1326" t="n"/>
+      <c r="E64" s="1327" t="n"/>
       <c r="F64" s="654" t="n"/>
       <c r="G64" s="267" t="n"/>
       <c r="H64" s="1038" t="n"/>
@@ -17428,15 +17514,15 @@
       <c r="J64" s="654" t="n"/>
       <c r="K64" s="1061" t="n"/>
       <c r="L64" s="654" t="n"/>
-      <c r="M64" s="1049" t="n"/>
+      <c r="M64" s="1327" t="n"/>
       <c r="N64" s="654" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1038" t="n"/>
       <c r="B65" s="530" t="n"/>
       <c r="C65" s="654" t="n"/>
-      <c r="D65" s="1038" t="n"/>
-      <c r="E65" s="1014" t="n"/>
+      <c r="D65" s="1326" t="n"/>
+      <c r="E65" s="1327" t="n"/>
       <c r="F65" s="654" t="n"/>
       <c r="G65" s="267" t="n"/>
       <c r="H65" s="1038" t="n"/>
@@ -17444,7 +17530,7 @@
       <c r="J65" s="654" t="n"/>
       <c r="K65" s="1105" t="n"/>
       <c r="L65" s="1030" t="n"/>
-      <c r="M65" s="1069" t="n"/>
+      <c r="M65" s="1328" t="n"/>
       <c r="N65" s="1030" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="1223">
@@ -17579,7 +17665,7 @@
       <c r="N72" s="565" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="1111" t="n"/>
+      <c r="A73" s="1329" t="n"/>
       <c r="B73" s="684" t="n"/>
       <c r="C73" s="684" t="n"/>
       <c r="D73" s="684" t="n"/>
@@ -17595,7 +17681,7 @@
       <c r="N73" s="1112" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="1025" t="n"/>
+      <c r="A74" s="1330" t="n"/>
       <c r="B74" s="530" t="n"/>
       <c r="C74" s="530" t="n"/>
       <c r="D74" s="530" t="n"/>
@@ -17611,7 +17697,7 @@
       <c r="N74" s="579" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="1025" t="n"/>
+      <c r="A75" s="1330" t="n"/>
       <c r="B75" s="530" t="n"/>
       <c r="C75" s="530" t="n"/>
       <c r="D75" s="530" t="n"/>
@@ -17627,7 +17713,7 @@
       <c r="N75" s="579" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="1025" t="n"/>
+      <c r="A76" s="1330" t="n"/>
       <c r="B76" s="530" t="n"/>
       <c r="C76" s="530" t="n"/>
       <c r="D76" s="530" t="n"/>
@@ -17791,33 +17877,26 @@
       <c r="N92" s="546" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="1020" t="n"/>
-      <c r="G93" s="1054" t="n"/>
-      <c r="H93" s="1020" t="n"/>
-      <c r="N93" s="546" t="n"/>
+      <c r="A93" s="1031" t="n"/>
+      <c r="B93" s="581" t="n"/>
+      <c r="C93" s="581" t="n"/>
+      <c r="D93" s="581" t="n"/>
+      <c r="E93" s="581" t="n"/>
+      <c r="F93" s="581" t="n"/>
+      <c r="G93" s="1032" t="n"/>
+      <c r="H93" s="1031" t="n"/>
+      <c r="I93" s="581" t="n"/>
+      <c r="J93" s="581" t="n"/>
+      <c r="K93" s="581" t="n"/>
+      <c r="L93" s="581" t="n"/>
+      <c r="M93" s="581" t="n"/>
+      <c r="N93" s="582" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="1020" t="n"/>
-      <c r="G94" s="1054" t="n"/>
-      <c r="H94" s="1020" t="n"/>
-      <c r="N94" s="546" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1031" t="n"/>
-      <c r="B95" s="581" t="n"/>
-      <c r="C95" s="581" t="n"/>
-      <c r="D95" s="581" t="n"/>
-      <c r="E95" s="581" t="n"/>
-      <c r="F95" s="581" t="n"/>
-      <c r="G95" s="1032" t="n"/>
-      <c r="H95" s="1031" t="n"/>
-      <c r="I95" s="581" t="n"/>
-      <c r="J95" s="581" t="n"/>
-      <c r="K95" s="581" t="n"/>
-      <c r="L95" s="581" t="n"/>
-      <c r="M95" s="581" t="n"/>
-      <c r="N95" s="582" t="n"/>
-    </row>
+      <c r="A94" s="1333" t="n"/>
+      <c r="H94" s="1333" t="n"/>
+    </row>
+    <row r="95"/>
     <row r="96">
       <c r="A96" s="1117" t="inlineStr">
         <is>
@@ -17915,33 +17994,26 @@
       <c r="N108" s="546" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="1020" t="n"/>
-      <c r="G109" s="1054" t="n"/>
-      <c r="H109" s="1020" t="n"/>
-      <c r="N109" s="546" t="n"/>
+      <c r="A109" s="1021" t="n"/>
+      <c r="B109" s="596" t="n"/>
+      <c r="C109" s="596" t="n"/>
+      <c r="D109" s="596" t="n"/>
+      <c r="E109" s="596" t="n"/>
+      <c r="F109" s="596" t="n"/>
+      <c r="G109" s="1118" t="n"/>
+      <c r="H109" s="1021" t="n"/>
+      <c r="I109" s="596" t="n"/>
+      <c r="J109" s="596" t="n"/>
+      <c r="K109" s="596" t="n"/>
+      <c r="L109" s="596" t="n"/>
+      <c r="M109" s="596" t="n"/>
+      <c r="N109" s="730" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="1020" t="n"/>
-      <c r="G110" s="1054" t="n"/>
-      <c r="H110" s="1020" t="n"/>
-      <c r="N110" s="546" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1021" t="n"/>
-      <c r="B111" s="596" t="n"/>
-      <c r="C111" s="596" t="n"/>
-      <c r="D111" s="596" t="n"/>
-      <c r="E111" s="596" t="n"/>
-      <c r="F111" s="596" t="n"/>
-      <c r="G111" s="1118" t="n"/>
-      <c r="H111" s="1021" t="n"/>
-      <c r="I111" s="596" t="n"/>
-      <c r="J111" s="596" t="n"/>
-      <c r="K111" s="596" t="n"/>
-      <c r="L111" s="596" t="n"/>
-      <c r="M111" s="596" t="n"/>
-      <c r="N111" s="730" t="n"/>
-    </row>
+      <c r="A110" s="1333" t="n"/>
+      <c r="H110" s="1333" t="n"/>
+    </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" s="1113" t="n"/>
       <c r="H112" s="1099" t="n"/>
@@ -18136,15 +18208,15 @@
       <c r="A122" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="220">
+  <mergeCells count="225">
     <mergeCell ref="C52:F52"/>
     <mergeCell ref="K48:N48"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="E62:F62"/>
     <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A94:G95"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="H96:N111"/>
     <mergeCell ref="J117:J118"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="E64:F64"/>
@@ -18199,9 +18271,10 @@
     <mergeCell ref="J29:N29"/>
     <mergeCell ref="K53:N53"/>
     <mergeCell ref="J38:N38"/>
+    <mergeCell ref="H96:N109"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="K64:L64"/>
-    <mergeCell ref="H80:N95"/>
+    <mergeCell ref="H80:N93"/>
     <mergeCell ref="K119:N120"/>
     <mergeCell ref="I57:J57"/>
     <mergeCell ref="J40:N40"/>
@@ -18258,6 +18331,7 @@
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="M67:N67"/>
     <mergeCell ref="J28:N28"/>
+    <mergeCell ref="M9:N9"/>
     <mergeCell ref="J37:N37"/>
     <mergeCell ref="C57:F57"/>
     <mergeCell ref="G68:I68"/>
@@ -18273,6 +18347,7 @@
     <mergeCell ref="G20:I20"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="H112:N112"/>
+    <mergeCell ref="H94:N95"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A18:N18"/>
@@ -18299,6 +18374,7 @@
     <mergeCell ref="G54:H54"/>
     <mergeCell ref="J43:N43"/>
     <mergeCell ref="K65:L65"/>
+    <mergeCell ref="A80:G93"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A72:N72"/>
     <mergeCell ref="E15:H15"/>
@@ -18310,21 +18386,21 @@
     <mergeCell ref="G56:H56"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="I16:K16"/>
-    <mergeCell ref="A80:G95"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="G52:H52"/>
+    <mergeCell ref="A110:G111"/>
     <mergeCell ref="I49:J49"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A73:N73"/>
     <mergeCell ref="A112:G112"/>
+    <mergeCell ref="A96:G109"/>
     <mergeCell ref="K57:N57"/>
     <mergeCell ref="I22:I23"/>
     <mergeCell ref="A70:N70"/>
     <mergeCell ref="J34:N34"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="A96:G111"/>
     <mergeCell ref="G53:H53"/>
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="J36:N36"/>
@@ -18333,6 +18409,7 @@
     <mergeCell ref="J45:N45"/>
     <mergeCell ref="A74:N74"/>
     <mergeCell ref="A50:B50"/>
+    <mergeCell ref="H110:N111"/>
     <mergeCell ref="H62:J62"/>
     <mergeCell ref="E119:E120"/>
     <mergeCell ref="I55:J55"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ficha Técnica del Proyecto" sheetId="1" r:id="rId1"/>
-    <sheet name="Presupuesto " sheetId="2" r:id="rId12"/>
-    <sheet name="Informe Semanal" sheetId="3" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ficha Técnica del Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Presupuesto " sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Informe Semanal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -10461,7 +10462,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -10506,7 +10507,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11291,7 +11292,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11324,8 +11324,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11338,7 +11339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
@@ -16351,7 +16352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -17071,7 +17072,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" s="550">
       <c r="A32" s="1058">
-        <f>'Presupuesto '!B109</f>
+        <f>'Presupuesto '!B108</f>
         <v/>
       </c>
       <c r="B32" s="567" t="n"/>
@@ -17105,7 +17106,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" s="550">
       <c r="A33" s="1058">
-        <f>'Presupuesto '!B123</f>
+        <f>'Presupuesto '!B122</f>
         <v/>
       </c>
       <c r="B33" s="567" t="n"/>
@@ -17139,7 +17140,7 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="550">
       <c r="A34" s="1058">
-        <f>'Presupuesto '!B131</f>
+        <f>'Presupuesto '!B132</f>
         <v/>
       </c>
       <c r="B34" s="567" t="n"/>
@@ -17173,7 +17174,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="550">
       <c r="A35" s="1058">
-        <f>'Presupuesto '!B142</f>
+        <f>'Presupuesto '!B143</f>
         <v/>
       </c>
       <c r="B35" s="567" t="n"/>
@@ -17207,7 +17208,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="550">
       <c r="A36" s="1058">
-        <f>'Presupuesto '!B149</f>
+        <f>'Presupuesto '!B150</f>
         <v/>
       </c>
       <c r="B36" s="567" t="n"/>
@@ -17241,7 +17242,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="550">
       <c r="A37" s="1058">
-        <f>'Presupuesto '!B164</f>
+        <f>'Presupuesto '!B165</f>
         <v/>
       </c>
       <c r="B37" s="567" t="n"/>
@@ -17275,7 +17276,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="550">
       <c r="A38" s="1058">
-        <f>'Presupuesto '!B178</f>
+        <f>'Presupuesto '!B179</f>
         <v/>
       </c>
       <c r="B38" s="567" t="n"/>
@@ -17309,7 +17310,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="550">
       <c r="A39" s="1119">
-        <f>'Presupuesto '!B187</f>
+        <f>'Presupuesto '!B188</f>
         <v/>
       </c>
       <c r="B39" s="567" t="n"/>
@@ -17340,7 +17341,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="550">
       <c r="A40" s="1119">
-        <f>'Presupuesto '!B194</f>
+        <f>'Presupuesto '!B195</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17371,7 +17372,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="550">
       <c r="A41" s="1119">
-        <f>'Presupuesto '!B200</f>
+        <f>'Presupuesto '!B201</f>
         <v/>
       </c>
       <c r="B41" s="567" t="n"/>
@@ -17402,7 +17403,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" s="550">
       <c r="A42" s="1058">
-        <f>'Presupuesto '!B214</f>
+        <f>'Presupuesto '!B215</f>
         <v/>
       </c>
       <c r="B42" s="567" t="n"/>
@@ -17433,7 +17434,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="550">
       <c r="A43" s="1058">
-        <f>'Presupuesto '!B221</f>
+        <f>'Presupuesto '!B222</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17464,7 +17465,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="550">
       <c r="A44" s="1058">
-        <f>'Presupuesto '!B229</f>
+        <f>'Presupuesto '!B230</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17495,7 +17496,7 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="550">
       <c r="A45" s="1058">
-        <f>'Presupuesto '!B233</f>
+        <f>'Presupuesto '!B234</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10418,32 +10418,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>69253</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174506</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>69253</colOff>
+      <row>6</row>
+      <rowOff>174506</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10455,40 +10455,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2766370</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>172889</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>2766370</colOff>
+      <row>8</row>
+      <rowOff>172889</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3312000" cy="1584000"/>
@@ -10500,40 +10500,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>13409</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>62385</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>144355</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="21" name="Image 2" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>13409</rowOff>
+    </from>
+    <to>
+      <col>7</col>
+      <colOff>62385</colOff>
+      <row>125</row>
+      <rowOff>144355</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="22186668"/>
           <a:ext cx="5330533" cy="845909"/>
@@ -10545,35 +10545,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>13630</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>176148</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Imagen 2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>4</col>
+      <colOff>13630</colOff>
+      <row>8</row>
+      <rowOff>176148</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Imagen 2"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3024000" cy="1512000"/>
@@ -10585,11 +10585,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10773,6 +10773,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11292,6 +11293,7 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11324,9 +11326,8 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A13:E13"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -11343,6 +11344,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16356,6 +16358,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N122"/>
@@ -16902,7 +16905,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="550">
       <c r="A27" s="1058">
-        <f>'Presupuesto '!B51</f>
+        <f>'Presupuesto '!B52</f>
         <v/>
       </c>
       <c r="B27" s="567" t="n"/>
@@ -16936,7 +16939,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" s="550">
       <c r="A28" s="1058">
-        <f>'Presupuesto '!B71</f>
+        <f>'Presupuesto '!B70</f>
         <v/>
       </c>
       <c r="B28" s="567" t="n"/>
@@ -16970,7 +16973,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" s="550">
       <c r="A29" s="1058">
-        <f>'Presupuesto '!B83</f>
+        <f>'Presupuesto '!B82</f>
         <v/>
       </c>
       <c r="B29" s="567" t="n"/>
@@ -17004,7 +17007,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" s="550">
       <c r="A30" s="1058">
-        <f>'Presupuesto '!B95</f>
+        <f>'Presupuesto '!B94</f>
         <v/>
       </c>
       <c r="B30" s="567" t="n"/>
@@ -17038,7 +17041,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" s="550">
       <c r="A31" s="1058">
-        <f>'Presupuesto '!B102</f>
+        <f>'Presupuesto '!B101</f>
         <v/>
       </c>
       <c r="B31" s="567" t="n"/>
@@ -17072,7 +17075,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" s="550">
       <c r="A32" s="1058">
-        <f>'Presupuesto '!B108</f>
+        <f>'Presupuesto '!B107</f>
         <v/>
       </c>
       <c r="B32" s="567" t="n"/>
@@ -17106,7 +17109,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" s="550">
       <c r="A33" s="1058">
-        <f>'Presupuesto '!B122</f>
+        <f>'Presupuesto '!B121</f>
         <v/>
       </c>
       <c r="B33" s="567" t="n"/>
@@ -17140,7 +17143,7 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="550">
       <c r="A34" s="1058">
-        <f>'Presupuesto '!B132</f>
+        <f>'Presupuesto '!B131</f>
         <v/>
       </c>
       <c r="B34" s="567" t="n"/>
@@ -17174,7 +17177,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="550">
       <c r="A35" s="1058">
-        <f>'Presupuesto '!B143</f>
+        <f>'Presupuesto '!B142</f>
         <v/>
       </c>
       <c r="B35" s="567" t="n"/>
@@ -17208,7 +17211,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="550">
       <c r="A36" s="1058">
-        <f>'Presupuesto '!B150</f>
+        <f>'Presupuesto '!B149</f>
         <v/>
       </c>
       <c r="B36" s="567" t="n"/>
@@ -17242,7 +17245,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="550">
       <c r="A37" s="1058">
-        <f>'Presupuesto '!B165</f>
+        <f>'Presupuesto '!B164</f>
         <v/>
       </c>
       <c r="B37" s="567" t="n"/>
@@ -17276,7 +17279,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="550">
       <c r="A38" s="1058">
-        <f>'Presupuesto '!B179</f>
+        <f>'Presupuesto '!B178</f>
         <v/>
       </c>
       <c r="B38" s="567" t="n"/>
@@ -17310,7 +17313,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="550">
       <c r="A39" s="1119">
-        <f>'Presupuesto '!B188</f>
+        <f>'Presupuesto '!B187</f>
         <v/>
       </c>
       <c r="B39" s="567" t="n"/>
@@ -17341,7 +17344,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="550">
       <c r="A40" s="1119">
-        <f>'Presupuesto '!B195</f>
+        <f>'Presupuesto '!B194</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17372,7 +17375,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="550">
       <c r="A41" s="1119">
-        <f>'Presupuesto '!B201</f>
+        <f>'Presupuesto '!B200</f>
         <v/>
       </c>
       <c r="B41" s="567" t="n"/>
@@ -17403,7 +17406,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" s="550">
       <c r="A42" s="1058">
-        <f>'Presupuesto '!B215</f>
+        <f>'Presupuesto '!B214</f>
         <v/>
       </c>
       <c r="B42" s="567" t="n"/>
@@ -17434,7 +17437,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="550">
       <c r="A43" s="1058">
-        <f>'Presupuesto '!B222</f>
+        <f>'Presupuesto '!B221</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17465,7 +17468,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="550">
       <c r="A44" s="1058">
-        <f>'Presupuesto '!B230</f>
+        <f>'Presupuesto '!B229</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17496,7 +17499,7 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="550">
       <c r="A45" s="1058">
-        <f>'Presupuesto '!B234</f>
+        <f>'Presupuesto '!B233</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -11293,7 +11293,6 @@
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="C29:E29"/>
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="C31:E31"/>
     <mergeCell ref="C22:E22"/>
@@ -11326,8 +11325,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
     <mergeCell ref="A40:E40"/>
@@ -16905,7 +16905,7 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="550">
       <c r="A27" s="1058">
-        <f>'Presupuesto '!B52</f>
+        <f>'Presupuesto '!B51</f>
         <v/>
       </c>
       <c r="B27" s="567" t="n"/>
@@ -16939,7 +16939,7 @@
     </row>
     <row r="28" ht="15" customHeight="1" s="550">
       <c r="A28" s="1058">
-        <f>'Presupuesto '!B70</f>
+        <f>'Presupuesto '!B64</f>
         <v/>
       </c>
       <c r="B28" s="567" t="n"/>
@@ -16973,7 +16973,7 @@
     </row>
     <row r="29" ht="15" customHeight="1" s="550">
       <c r="A29" s="1058">
-        <f>'Presupuesto '!B82</f>
+        <f>'Presupuesto '!B76</f>
         <v/>
       </c>
       <c r="B29" s="567" t="n"/>
@@ -17007,7 +17007,7 @@
     </row>
     <row r="30" ht="15" customHeight="1" s="550">
       <c r="A30" s="1058">
-        <f>'Presupuesto '!B94</f>
+        <f>'Presupuesto '!B88</f>
         <v/>
       </c>
       <c r="B30" s="567" t="n"/>
@@ -17041,7 +17041,7 @@
     </row>
     <row r="31" ht="15" customHeight="1" s="550">
       <c r="A31" s="1058">
-        <f>'Presupuesto '!B101</f>
+        <f>'Presupuesto '!B95</f>
         <v/>
       </c>
       <c r="B31" s="567" t="n"/>
@@ -17075,7 +17075,7 @@
     </row>
     <row r="32" ht="15" customHeight="1" s="550">
       <c r="A32" s="1058">
-        <f>'Presupuesto '!B107</f>
+        <f>'Presupuesto '!B101</f>
         <v/>
       </c>
       <c r="B32" s="567" t="n"/>
@@ -17109,7 +17109,7 @@
     </row>
     <row r="33" ht="15" customHeight="1" s="550">
       <c r="A33" s="1058">
-        <f>'Presupuesto '!B121</f>
+        <f>'Presupuesto '!B115</f>
         <v/>
       </c>
       <c r="B33" s="567" t="n"/>
@@ -17143,7 +17143,7 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="550">
       <c r="A34" s="1058">
-        <f>'Presupuesto '!B131</f>
+        <f>'Presupuesto '!B125</f>
         <v/>
       </c>
       <c r="B34" s="567" t="n"/>
@@ -17177,7 +17177,7 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="550">
       <c r="A35" s="1058">
-        <f>'Presupuesto '!B142</f>
+        <f>'Presupuesto '!B136</f>
         <v/>
       </c>
       <c r="B35" s="567" t="n"/>
@@ -17211,7 +17211,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="550">
       <c r="A36" s="1058">
-        <f>'Presupuesto '!B149</f>
+        <f>'Presupuesto '!B143</f>
         <v/>
       </c>
       <c r="B36" s="567" t="n"/>
@@ -17245,7 +17245,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="550">
       <c r="A37" s="1058">
-        <f>'Presupuesto '!B164</f>
+        <f>'Presupuesto '!B158</f>
         <v/>
       </c>
       <c r="B37" s="567" t="n"/>
@@ -17279,7 +17279,7 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="550">
       <c r="A38" s="1058">
-        <f>'Presupuesto '!B178</f>
+        <f>'Presupuesto '!B172</f>
         <v/>
       </c>
       <c r="B38" s="567" t="n"/>
@@ -17313,7 +17313,7 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="550">
       <c r="A39" s="1119">
-        <f>'Presupuesto '!B187</f>
+        <f>'Presupuesto '!B181</f>
         <v/>
       </c>
       <c r="B39" s="567" t="n"/>
@@ -17344,7 +17344,7 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="550">
       <c r="A40" s="1119">
-        <f>'Presupuesto '!B194</f>
+        <f>'Presupuesto '!B188</f>
         <v/>
       </c>
       <c r="B40" s="567" t="n"/>
@@ -17375,7 +17375,7 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="550">
       <c r="A41" s="1119">
-        <f>'Presupuesto '!B200</f>
+        <f>'Presupuesto '!B194</f>
         <v/>
       </c>
       <c r="B41" s="567" t="n"/>
@@ -17406,7 +17406,7 @@
     </row>
     <row r="42" ht="15" customHeight="1" s="550">
       <c r="A42" s="1058">
-        <f>'Presupuesto '!B214</f>
+        <f>'Presupuesto '!B208</f>
         <v/>
       </c>
       <c r="B42" s="567" t="n"/>
@@ -17437,7 +17437,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="550">
       <c r="A43" s="1058">
-        <f>'Presupuesto '!B221</f>
+        <f>'Presupuesto '!B215</f>
         <v/>
       </c>
       <c r="B43" s="567" t="n"/>
@@ -17468,7 +17468,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="550">
       <c r="A44" s="1058">
-        <f>'Presupuesto '!B229</f>
+        <f>'Presupuesto '!B223</f>
         <v/>
       </c>
       <c r="B44" s="567" t="n"/>
@@ -17499,7 +17499,7 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="550">
       <c r="A45" s="1058">
-        <f>'Presupuesto '!B233</f>
+        <f>'Presupuesto '!B227</f>
         <v/>
       </c>
       <c r="B45" s="567" t="n"/>

--- a/public/plantilla-semanal.xlsx
+++ b/public/plantilla-semanal.xlsx
@@ -10418,32 +10418,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>69253</colOff>
-      <row>6</row>
-      <rowOff>174506</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>69253</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>174506</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="2952000" cy="1368000"/>
@@ -10455,40 +10455,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>2766370</colOff>
-      <row>8</row>
-      <rowOff>172889</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2766370</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>172889</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3312000" cy="1584000"/>
@@ -10500,40 +10500,40 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>121</row>
-      <rowOff>13409</rowOff>
-    </from>
-    <to>
-      <col>7</col>
-      <colOff>62385</colOff>
-      <row>125</row>
-      <rowOff>144355</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>13409</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>62385</xdr:colOff>
+      <xdr:row>140</xdr:row>
+      <xdr:rowOff>144355</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Image 2" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="22186668"/>
           <a:ext cx="5330533" cy="845909"/>
@@ -10545,35 +10545,35 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>4</col>
-      <colOff>13630</colOff>
-      <row>8</row>
-      <rowOff>176148</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Imagen 2"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>13630</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>176148</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3024000" cy="1512000"/>
@@ -10585,11 +10585,11 @@
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10773,7 +10773,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E47"/>
@@ -11324,13 +11323,13 @@
     <mergeCell ref="A38:E38"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C35:E35"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C29:E29"/>
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="C35:E35"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="C25:E25"/>
   </mergeCells>
@@ -11344,7 +11343,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF2E7D32"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F259"/>
@@ -16358,10 +16356,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" style="550" min="1" max="14"/>
@@ -16718,13 +16715,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1371">
-        <f>H46</f>
+        <f>H61</f>
         <v/>
       </c>
       <c r="B21" s="595" t="n"/>
       <c r="C21" s="595" t="n"/>
       <c r="D21" s="1372">
-        <f>I46</f>
+        <f>I61</f>
         <v/>
       </c>
       <c r="E21" s="595" t="n"/>
@@ -16736,7 +16733,7 @@
       <c r="H21" s="595" t="n"/>
       <c r="I21" s="595" t="n"/>
       <c r="J21" s="1373">
-        <f>IFERROR(J46/$L$14,0)</f>
+        <f>IFERROR(J61/$L$14,0)</f>
         <v/>
       </c>
       <c r="K21" s="595" t="n"/>
@@ -17531,762 +17528,1071 @@
       <c r="M45" s="609" t="n"/>
       <c r="N45" s="1078" t="n"/>
     </row>
-    <row r="46">
-      <c r="A46" s="1059" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
+    <row r="46" ht="15" customHeight="1" s="550">
+      <c r="A46" s="1058" t="n"/>
       <c r="B46" s="567" t="n"/>
       <c r="C46" s="682" t="n"/>
-      <c r="D46" s="1385">
-        <f>SUM(D24:D45)</f>
-        <v/>
-      </c>
-      <c r="E46" s="261" t="n"/>
-      <c r="F46" s="261" t="n"/>
-      <c r="G46" s="262" t="n"/>
-      <c r="H46" s="1386">
-        <f>SUM(H24:H45)</f>
-        <v/>
-      </c>
-      <c r="I46" s="1386">
-        <f>SUM(I24:I45)</f>
-        <v/>
-      </c>
-      <c r="J46" s="1387">
-        <f>SUM(J24:J45)</f>
-        <v/>
-      </c>
-      <c r="K46" s="1064" t="n"/>
-      <c r="L46" s="1064" t="n"/>
-      <c r="M46" s="1064" t="n"/>
-      <c r="N46" s="1076" t="n"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="550">
-      <c r="A47" s="1111" t="inlineStr">
-        <is>
-          <t>ACTIVIDADES MÁS RELEVANTES DEL PERÍODO</t>
-        </is>
-      </c>
-      <c r="N47" s="562" t="n"/>
+      <c r="D46" s="1379" t="n"/>
+      <c r="E46" s="1380" t="n"/>
+      <c r="F46" s="1380" t="n"/>
+      <c r="G46" s="1376">
+        <f>F46-E46</f>
+        <v/>
+      </c>
+      <c r="H46" s="1381">
+        <f>D46*E46</f>
+        <v/>
+      </c>
+      <c r="I46" s="1381">
+        <f>D46*F46</f>
+        <v/>
+      </c>
+      <c r="J46" s="1384">
+        <f>D46*$L$14*G46</f>
+        <v/>
+      </c>
+      <c r="K46" s="609" t="n"/>
+      <c r="L46" s="609" t="n"/>
+      <c r="M46" s="609" t="n"/>
+      <c r="N46" s="1078" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="550">
+      <c r="A47" s="1058" t="n"/>
+      <c r="B47" s="567" t="n"/>
+      <c r="C47" s="682" t="n"/>
+      <c r="D47" s="1379" t="n"/>
+      <c r="E47" s="1380" t="n"/>
+      <c r="F47" s="1380" t="n"/>
+      <c r="G47" s="1376">
+        <f>F47-E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="1381">
+        <f>D47*E47</f>
+        <v/>
+      </c>
+      <c r="I47" s="1381">
+        <f>D47*F47</f>
+        <v/>
+      </c>
+      <c r="J47" s="1384">
+        <f>D47*$L$14*G47</f>
+        <v/>
+      </c>
+      <c r="K47" s="609" t="n"/>
+      <c r="L47" s="609" t="n"/>
+      <c r="M47" s="609" t="n"/>
+      <c r="N47" s="1078" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="550">
-      <c r="A48" s="1101" t="inlineStr">
-        <is>
-          <t>UBICACIÓN</t>
-        </is>
-      </c>
-      <c r="B48" s="609" t="n"/>
-      <c r="C48" s="1106" t="inlineStr">
-        <is>
-          <t>DESCRIPCIÓN DE LA ACTIVIDAD</t>
-        </is>
-      </c>
-      <c r="D48" s="609" t="n"/>
-      <c r="E48" s="609" t="n"/>
-      <c r="F48" s="609" t="n"/>
-      <c r="G48" s="1106" t="inlineStr">
-        <is>
-          <t>AVANCE DEL PERÍODO</t>
-        </is>
-      </c>
-      <c r="H48" s="609" t="n"/>
-      <c r="I48" s="1106" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="J48" s="609" t="n"/>
-      <c r="K48" s="1057" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES</t>
-        </is>
-      </c>
+      <c r="A48" s="1058" t="n"/>
+      <c r="B48" s="567" t="n"/>
+      <c r="C48" s="682" t="n"/>
+      <c r="D48" s="1379" t="n"/>
+      <c r="E48" s="1380" t="n"/>
+      <c r="F48" s="1380" t="n"/>
+      <c r="G48" s="1376">
+        <f>F48-E48</f>
+        <v/>
+      </c>
+      <c r="H48" s="1381">
+        <f>D48*E48</f>
+        <v/>
+      </c>
+      <c r="I48" s="1381">
+        <f>D48*F48</f>
+        <v/>
+      </c>
+      <c r="J48" s="1384">
+        <f>D48*$L$14*G48</f>
+        <v/>
+      </c>
+      <c r="K48" s="609" t="n"/>
       <c r="L48" s="609" t="n"/>
       <c r="M48" s="609" t="n"/>
-      <c r="N48" s="610" t="n"/>
-    </row>
-    <row r="49" ht="14.4" customHeight="1" s="550">
-      <c r="A49" s="1077" t="n"/>
-      <c r="B49" s="609" t="n"/>
-      <c r="C49" s="1164" t="n"/>
-      <c r="D49" s="609" t="n"/>
-      <c r="E49" s="609" t="n"/>
-      <c r="F49" s="609" t="n"/>
-      <c r="G49" s="1388" t="n"/>
-      <c r="H49" s="609" t="n"/>
-      <c r="I49" s="609" t="n"/>
-      <c r="J49" s="609" t="n"/>
-      <c r="K49" s="1389" t="n"/>
+      <c r="N48" s="1078" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="550">
+      <c r="A49" s="1058" t="n"/>
+      <c r="B49" s="567" t="n"/>
+      <c r="C49" s="682" t="n"/>
+      <c r="D49" s="1379" t="n"/>
+      <c r="E49" s="1380" t="n"/>
+      <c r="F49" s="1380" t="n"/>
+      <c r="G49" s="1376">
+        <f>F49-E49</f>
+        <v/>
+      </c>
+      <c r="H49" s="1381">
+        <f>D49*E49</f>
+        <v/>
+      </c>
+      <c r="I49" s="1381">
+        <f>D49*F49</f>
+        <v/>
+      </c>
+      <c r="J49" s="1384">
+        <f>D49*$L$14*G49</f>
+        <v/>
+      </c>
+      <c r="K49" s="609" t="n"/>
       <c r="L49" s="609" t="n"/>
       <c r="M49" s="609" t="n"/>
-      <c r="N49" s="610" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1061" t="n"/>
+      <c r="N49" s="1078" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="550">
+      <c r="A50" s="1058" t="n"/>
       <c r="B50" s="567" t="n"/>
-      <c r="C50" s="1056" t="n"/>
-      <c r="D50" s="567" t="n"/>
-      <c r="E50" s="567" t="n"/>
-      <c r="F50" s="567" t="n"/>
-      <c r="G50" s="1081" t="n"/>
-      <c r="H50" s="567" t="n"/>
-      <c r="I50" s="1091" t="n"/>
-      <c r="J50" s="567" t="n"/>
-      <c r="K50" s="1390" t="n"/>
-      <c r="L50" s="567" t="n"/>
-      <c r="M50" s="567" t="n"/>
-      <c r="N50" s="607" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1061" t="n"/>
+      <c r="C50" s="682" t="n"/>
+      <c r="D50" s="1379" t="n"/>
+      <c r="E50" s="1380" t="n"/>
+      <c r="F50" s="1380" t="n"/>
+      <c r="G50" s="1376">
+        <f>F50-E50</f>
+        <v/>
+      </c>
+      <c r="H50" s="1381">
+        <f>D50*E50</f>
+        <v/>
+      </c>
+      <c r="I50" s="1381">
+        <f>D50*F50</f>
+        <v/>
+      </c>
+      <c r="J50" s="1384">
+        <f>D50*$L$14*G50</f>
+        <v/>
+      </c>
+      <c r="K50" s="609" t="n"/>
+      <c r="L50" s="609" t="n"/>
+      <c r="M50" s="609" t="n"/>
+      <c r="N50" s="1078" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="550">
+      <c r="A51" s="1058" t="n"/>
       <c r="B51" s="567" t="n"/>
-      <c r="C51" s="1056" t="n"/>
-      <c r="D51" s="567" t="n"/>
-      <c r="E51" s="567" t="n"/>
-      <c r="F51" s="567" t="n"/>
-      <c r="G51" s="1081" t="n"/>
-      <c r="H51" s="567" t="n"/>
-      <c r="I51" s="1091" t="n"/>
-      <c r="J51" s="567" t="n"/>
-      <c r="K51" s="1390" t="n"/>
-      <c r="L51" s="567" t="n"/>
-      <c r="M51" s="567" t="n"/>
-      <c r="N51" s="607" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1061" t="n"/>
+      <c r="C51" s="682" t="n"/>
+      <c r="D51" s="1379" t="n"/>
+      <c r="E51" s="1380" t="n"/>
+      <c r="F51" s="1380" t="n"/>
+      <c r="G51" s="1376">
+        <f>F51-E51</f>
+        <v/>
+      </c>
+      <c r="H51" s="1381">
+        <f>D51*E51</f>
+        <v/>
+      </c>
+      <c r="I51" s="1381">
+        <f>D51*F51</f>
+        <v/>
+      </c>
+      <c r="J51" s="1384">
+        <f>D51*$L$14*G51</f>
+        <v/>
+      </c>
+      <c r="K51" s="609" t="n"/>
+      <c r="L51" s="609" t="n"/>
+      <c r="M51" s="609" t="n"/>
+      <c r="N51" s="1078" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="550">
+      <c r="A52" s="1058" t="n"/>
       <c r="B52" s="567" t="n"/>
-      <c r="C52" s="1056" t="n"/>
-      <c r="D52" s="567" t="n"/>
-      <c r="E52" s="567" t="n"/>
-      <c r="F52" s="567" t="n"/>
-      <c r="G52" s="1081" t="n"/>
-      <c r="H52" s="567" t="n"/>
-      <c r="I52" s="1091" t="n"/>
-      <c r="J52" s="567" t="n"/>
-      <c r="K52" s="1390" t="n"/>
-      <c r="L52" s="567" t="n"/>
-      <c r="M52" s="567" t="n"/>
-      <c r="N52" s="607" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1072" t="n"/>
+      <c r="C52" s="682" t="n"/>
+      <c r="D52" s="1379" t="n"/>
+      <c r="E52" s="1380" t="n"/>
+      <c r="F52" s="1380" t="n"/>
+      <c r="G52" s="1376">
+        <f>F52-E52</f>
+        <v/>
+      </c>
+      <c r="H52" s="1381">
+        <f>D52*E52</f>
+        <v/>
+      </c>
+      <c r="I52" s="1381">
+        <f>D52*F52</f>
+        <v/>
+      </c>
+      <c r="J52" s="1384">
+        <f>D52*$L$14*G52</f>
+        <v/>
+      </c>
+      <c r="K52" s="609" t="n"/>
+      <c r="L52" s="609" t="n"/>
+      <c r="M52" s="609" t="n"/>
+      <c r="N52" s="1078" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="550">
+      <c r="A53" s="1058" t="n"/>
       <c r="B53" s="567" t="n"/>
-      <c r="C53" s="1088" t="n"/>
-      <c r="D53" s="567" t="n"/>
-      <c r="E53" s="567" t="n"/>
-      <c r="F53" s="567" t="n"/>
-      <c r="G53" s="1081" t="n"/>
-      <c r="H53" s="567" t="n"/>
-      <c r="I53" s="567" t="n"/>
-      <c r="J53" s="567" t="n"/>
-      <c r="K53" s="1390" t="n"/>
-      <c r="L53" s="567" t="n"/>
-      <c r="M53" s="567" t="n"/>
-      <c r="N53" s="607" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1072" t="n"/>
+      <c r="C53" s="682" t="n"/>
+      <c r="D53" s="1379" t="n"/>
+      <c r="E53" s="1380" t="n"/>
+      <c r="F53" s="1380" t="n"/>
+      <c r="G53" s="1376">
+        <f>F53-E53</f>
+        <v/>
+      </c>
+      <c r="H53" s="1381">
+        <f>D53*E53</f>
+        <v/>
+      </c>
+      <c r="I53" s="1381">
+        <f>D53*F53</f>
+        <v/>
+      </c>
+      <c r="J53" s="1384">
+        <f>D53*$L$14*G53</f>
+        <v/>
+      </c>
+      <c r="K53" s="609" t="n"/>
+      <c r="L53" s="609" t="n"/>
+      <c r="M53" s="609" t="n"/>
+      <c r="N53" s="1078" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="550">
+      <c r="A54" s="1058" t="n"/>
       <c r="B54" s="567" t="n"/>
-      <c r="C54" s="1088" t="n"/>
-      <c r="D54" s="567" t="n"/>
-      <c r="E54" s="567" t="n"/>
-      <c r="F54" s="567" t="n"/>
-      <c r="G54" s="1081" t="n"/>
-      <c r="H54" s="567" t="n"/>
-      <c r="I54" s="567" t="n"/>
-      <c r="J54" s="567" t="n"/>
-      <c r="K54" s="1390" t="n"/>
-      <c r="L54" s="567" t="n"/>
-      <c r="M54" s="567" t="n"/>
-      <c r="N54" s="607" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1072" t="n"/>
+      <c r="C54" s="682" t="n"/>
+      <c r="D54" s="1379" t="n"/>
+      <c r="E54" s="1380" t="n"/>
+      <c r="F54" s="1380" t="n"/>
+      <c r="G54" s="1376">
+        <f>F54-E54</f>
+        <v/>
+      </c>
+      <c r="H54" s="1381">
+        <f>D54*E54</f>
+        <v/>
+      </c>
+      <c r="I54" s="1381">
+        <f>D54*F54</f>
+        <v/>
+      </c>
+      <c r="J54" s="1384">
+        <f>D54*$L$14*G54</f>
+        <v/>
+      </c>
+      <c r="K54" s="609" t="n"/>
+      <c r="L54" s="609" t="n"/>
+      <c r="M54" s="609" t="n"/>
+      <c r="N54" s="1078" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="550">
+      <c r="A55" s="1058" t="n"/>
       <c r="B55" s="567" t="n"/>
-      <c r="C55" s="1088" t="n"/>
-      <c r="D55" s="567" t="n"/>
-      <c r="E55" s="567" t="n"/>
-      <c r="F55" s="567" t="n"/>
-      <c r="G55" s="1081" t="n"/>
-      <c r="H55" s="567" t="n"/>
-      <c r="I55" s="567" t="n"/>
-      <c r="J55" s="567" t="n"/>
-      <c r="K55" s="1390" t="n"/>
-      <c r="L55" s="567" t="n"/>
-      <c r="M55" s="567" t="n"/>
-      <c r="N55" s="607" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1072" t="n"/>
+      <c r="C55" s="682" t="n"/>
+      <c r="D55" s="1379" t="n"/>
+      <c r="E55" s="1380" t="n"/>
+      <c r="F55" s="1380" t="n"/>
+      <c r="G55" s="1376">
+        <f>F55-E55</f>
+        <v/>
+      </c>
+      <c r="H55" s="1381">
+        <f>D55*E55</f>
+        <v/>
+      </c>
+      <c r="I55" s="1381">
+        <f>D55*F55</f>
+        <v/>
+      </c>
+      <c r="J55" s="1384">
+        <f>D55*$L$14*G55</f>
+        <v/>
+      </c>
+      <c r="K55" s="609" t="n"/>
+      <c r="L55" s="609" t="n"/>
+      <c r="M55" s="609" t="n"/>
+      <c r="N55" s="1078" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="550">
+      <c r="A56" s="1058" t="n"/>
       <c r="B56" s="567" t="n"/>
-      <c r="C56" s="1088" t="n"/>
-      <c r="D56" s="567" t="n"/>
-      <c r="E56" s="567" t="n"/>
-      <c r="F56" s="567" t="n"/>
-      <c r="G56" s="1081" t="n"/>
-      <c r="H56" s="567" t="n"/>
-      <c r="I56" s="567" t="n"/>
-      <c r="J56" s="567" t="n"/>
-      <c r="K56" s="1390" t="n"/>
-      <c r="L56" s="567" t="n"/>
-      <c r="M56" s="567" t="n"/>
-      <c r="N56" s="607" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1072" t="n"/>
+      <c r="C56" s="682" t="n"/>
+      <c r="D56" s="1379" t="n"/>
+      <c r="E56" s="1380" t="n"/>
+      <c r="F56" s="1380" t="n"/>
+      <c r="G56" s="1376">
+        <f>F56-E56</f>
+        <v/>
+      </c>
+      <c r="H56" s="1381">
+        <f>D56*E56</f>
+        <v/>
+      </c>
+      <c r="I56" s="1381">
+        <f>D56*F56</f>
+        <v/>
+      </c>
+      <c r="J56" s="1384">
+        <f>D56*$L$14*G56</f>
+        <v/>
+      </c>
+      <c r="K56" s="609" t="n"/>
+      <c r="L56" s="609" t="n"/>
+      <c r="M56" s="609" t="n"/>
+      <c r="N56" s="1078" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="550">
+      <c r="A57" s="1058" t="n"/>
       <c r="B57" s="567" t="n"/>
-      <c r="C57" s="1088" t="n"/>
-      <c r="D57" s="567" t="n"/>
-      <c r="E57" s="567" t="n"/>
-      <c r="F57" s="567" t="n"/>
-      <c r="G57" s="1081" t="n"/>
-      <c r="H57" s="567" t="n"/>
-      <c r="I57" s="567" t="n"/>
-      <c r="J57" s="567" t="n"/>
-      <c r="K57" s="1390" t="n"/>
-      <c r="L57" s="567" t="n"/>
-      <c r="M57" s="567" t="n"/>
-      <c r="N57" s="607" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" s="550">
-      <c r="A58" s="1131" t="inlineStr">
+      <c r="C57" s="682" t="n"/>
+      <c r="D57" s="1379" t="n"/>
+      <c r="E57" s="1380" t="n"/>
+      <c r="F57" s="1380" t="n"/>
+      <c r="G57" s="1376">
+        <f>F57-E57</f>
+        <v/>
+      </c>
+      <c r="H57" s="1381">
+        <f>D57*E57</f>
+        <v/>
+      </c>
+      <c r="I57" s="1381">
+        <f>D57*F57</f>
+        <v/>
+      </c>
+      <c r="J57" s="1384">
+        <f>D57*$L$14*G57</f>
+        <v/>
+      </c>
+      <c r="K57" s="609" t="n"/>
+      <c r="L57" s="609" t="n"/>
+      <c r="M57" s="609" t="n"/>
+      <c r="N57" s="1078" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="550">
+      <c r="A58" s="1058" t="n"/>
+      <c r="B58" s="567" t="n"/>
+      <c r="C58" s="682" t="n"/>
+      <c r="D58" s="1379" t="n"/>
+      <c r="E58" s="1380" t="n"/>
+      <c r="F58" s="1380" t="n"/>
+      <c r="G58" s="1376">
+        <f>F58-E58</f>
+        <v/>
+      </c>
+      <c r="H58" s="1381">
+        <f>D58*E58</f>
+        <v/>
+      </c>
+      <c r="I58" s="1381">
+        <f>D58*F58</f>
+        <v/>
+      </c>
+      <c r="J58" s="1384">
+        <f>D58*$L$14*G58</f>
+        <v/>
+      </c>
+      <c r="K58" s="609" t="n"/>
+      <c r="L58" s="609" t="n"/>
+      <c r="M58" s="609" t="n"/>
+      <c r="N58" s="1078" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="550">
+      <c r="A59" s="1058" t="n"/>
+      <c r="B59" s="567" t="n"/>
+      <c r="C59" s="682" t="n"/>
+      <c r="D59" s="1379" t="n"/>
+      <c r="E59" s="1380" t="n"/>
+      <c r="F59" s="1380" t="n"/>
+      <c r="G59" s="1376">
+        <f>F59-E59</f>
+        <v/>
+      </c>
+      <c r="H59" s="1381">
+        <f>D59*E59</f>
+        <v/>
+      </c>
+      <c r="I59" s="1381">
+        <f>D59*F59</f>
+        <v/>
+      </c>
+      <c r="J59" s="1384">
+        <f>D59*$L$14*G59</f>
+        <v/>
+      </c>
+      <c r="K59" s="609" t="n"/>
+      <c r="L59" s="609" t="n"/>
+      <c r="M59" s="609" t="n"/>
+      <c r="N59" s="1078" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="550">
+      <c r="A60" s="1058" t="n"/>
+      <c r="B60" s="567" t="n"/>
+      <c r="C60" s="682" t="n"/>
+      <c r="D60" s="1379" t="n"/>
+      <c r="E60" s="1380" t="n"/>
+      <c r="F60" s="1380" t="n"/>
+      <c r="G60" s="1376">
+        <f>F60-E60</f>
+        <v/>
+      </c>
+      <c r="H60" s="1381">
+        <f>D60*E60</f>
+        <v/>
+      </c>
+      <c r="I60" s="1381">
+        <f>D60*F60</f>
+        <v/>
+      </c>
+      <c r="J60" s="1384">
+        <f>D60*$L$14*G60</f>
+        <v/>
+      </c>
+      <c r="K60" s="609" t="n"/>
+      <c r="L60" s="609" t="n"/>
+      <c r="M60" s="609" t="n"/>
+      <c r="N60" s="1078" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1059" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B61" s="567" t="n"/>
+      <c r="C61" s="682" t="n"/>
+      <c r="D61" s="1385">
+        <f>SUM(D24:D60)</f>
+        <v/>
+      </c>
+      <c r="E61" s="261" t="n"/>
+      <c r="F61" s="261" t="n"/>
+      <c r="G61" s="262" t="n"/>
+      <c r="H61" s="1386">
+        <f>SUM(H24:H60)</f>
+        <v/>
+      </c>
+      <c r="I61" s="1386">
+        <f>SUM(I24:I60)</f>
+        <v/>
+      </c>
+      <c r="J61" s="1387">
+        <f>SUM(J24:J60)</f>
+        <v/>
+      </c>
+      <c r="K61" s="1064" t="n"/>
+      <c r="L61" s="1064" t="n"/>
+      <c r="M61" s="1064" t="n"/>
+      <c r="N61" s="1076" t="n"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="550">
+      <c r="A62" s="1111" t="inlineStr">
+        <is>
+          <t>ACTIVIDADES MÁS RELEVANTES DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="N62" s="562" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="550">
+      <c r="A63" s="1101" t="inlineStr">
+        <is>
+          <t>UBICACIÓN</t>
+        </is>
+      </c>
+      <c r="B63" s="609" t="n"/>
+      <c r="C63" s="1106" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN DE LA ACTIVIDAD</t>
+        </is>
+      </c>
+      <c r="D63" s="609" t="n"/>
+      <c r="E63" s="609" t="n"/>
+      <c r="F63" s="609" t="n"/>
+      <c r="G63" s="1106" t="inlineStr">
+        <is>
+          <t>AVANCE DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="H63" s="609" t="n"/>
+      <c r="I63" s="1106" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="J63" s="609" t="n"/>
+      <c r="K63" s="1057" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES</t>
+        </is>
+      </c>
+      <c r="L63" s="609" t="n"/>
+      <c r="M63" s="609" t="n"/>
+      <c r="N63" s="610" t="n"/>
+    </row>
+    <row r="64" ht="14.4" customHeight="1" s="550">
+      <c r="A64" s="1077" t="n"/>
+      <c r="B64" s="609" t="n"/>
+      <c r="C64" s="1164" t="n"/>
+      <c r="D64" s="609" t="n"/>
+      <c r="E64" s="609" t="n"/>
+      <c r="F64" s="609" t="n"/>
+      <c r="G64" s="1388" t="n"/>
+      <c r="H64" s="609" t="n"/>
+      <c r="I64" s="609" t="n"/>
+      <c r="J64" s="609" t="n"/>
+      <c r="K64" s="1389" t="n"/>
+      <c r="L64" s="609" t="n"/>
+      <c r="M64" s="609" t="n"/>
+      <c r="N64" s="610" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="1061" t="n"/>
+      <c r="B65" s="567" t="n"/>
+      <c r="C65" s="1056" t="n"/>
+      <c r="D65" s="567" t="n"/>
+      <c r="E65" s="567" t="n"/>
+      <c r="F65" s="567" t="n"/>
+      <c r="G65" s="1081" t="n"/>
+      <c r="H65" s="567" t="n"/>
+      <c r="I65" s="1091" t="n"/>
+      <c r="J65" s="567" t="n"/>
+      <c r="K65" s="1390" t="n"/>
+      <c r="L65" s="567" t="n"/>
+      <c r="M65" s="567" t="n"/>
+      <c r="N65" s="607" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="550">
+      <c r="A66" s="1061" t="n"/>
+      <c r="B66" s="567" t="n"/>
+      <c r="C66" s="1056" t="n"/>
+      <c r="D66" s="567" t="n"/>
+      <c r="E66" s="567" t="n"/>
+      <c r="F66" s="567" t="n"/>
+      <c r="G66" s="1081" t="n"/>
+      <c r="H66" s="567" t="n"/>
+      <c r="I66" s="1091" t="n"/>
+      <c r="J66" s="567" t="n"/>
+      <c r="K66" s="1390" t="n"/>
+      <c r="L66" s="567" t="n"/>
+      <c r="M66" s="567" t="n"/>
+      <c r="N66" s="607" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="550">
+      <c r="A67" s="1061" t="n"/>
+      <c r="B67" s="567" t="n"/>
+      <c r="C67" s="1056" t="n"/>
+      <c r="D67" s="567" t="n"/>
+      <c r="E67" s="567" t="n"/>
+      <c r="F67" s="567" t="n"/>
+      <c r="G67" s="1081" t="n"/>
+      <c r="H67" s="567" t="n"/>
+      <c r="I67" s="1091" t="n"/>
+      <c r="J67" s="567" t="n"/>
+      <c r="K67" s="1390" t="n"/>
+      <c r="L67" s="567" t="n"/>
+      <c r="M67" s="567" t="n"/>
+      <c r="N67" s="607" t="n"/>
+    </row>
+    <row r="68" ht="25.05" customHeight="1" s="550">
+      <c r="A68" s="1072" t="n"/>
+      <c r="B68" s="567" t="n"/>
+      <c r="C68" s="1088" t="n"/>
+      <c r="D68" s="567" t="n"/>
+      <c r="E68" s="567" t="n"/>
+      <c r="F68" s="567" t="n"/>
+      <c r="G68" s="1081" t="n"/>
+      <c r="H68" s="567" t="n"/>
+      <c r="I68" s="567" t="n"/>
+      <c r="J68" s="567" t="n"/>
+      <c r="K68" s="1390" t="n"/>
+      <c r="L68" s="567" t="n"/>
+      <c r="M68" s="567" t="n"/>
+      <c r="N68" s="607" t="n"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" s="550">
+      <c r="A69" s="1072" t="n"/>
+      <c r="B69" s="567" t="n"/>
+      <c r="C69" s="1088" t="n"/>
+      <c r="D69" s="567" t="n"/>
+      <c r="E69" s="567" t="n"/>
+      <c r="F69" s="567" t="n"/>
+      <c r="G69" s="1081" t="n"/>
+      <c r="H69" s="567" t="n"/>
+      <c r="I69" s="567" t="n"/>
+      <c r="J69" s="567" t="n"/>
+      <c r="K69" s="1390" t="n"/>
+      <c r="L69" s="567" t="n"/>
+      <c r="M69" s="567" t="n"/>
+      <c r="N69" s="607" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="550">
+      <c r="A70" s="1072" t="n"/>
+      <c r="B70" s="567" t="n"/>
+      <c r="C70" s="1088" t="n"/>
+      <c r="D70" s="567" t="n"/>
+      <c r="E70" s="567" t="n"/>
+      <c r="F70" s="567" t="n"/>
+      <c r="G70" s="1081" t="n"/>
+      <c r="H70" s="567" t="n"/>
+      <c r="I70" s="567" t="n"/>
+      <c r="J70" s="567" t="n"/>
+      <c r="K70" s="1390" t="n"/>
+      <c r="L70" s="567" t="n"/>
+      <c r="M70" s="567" t="n"/>
+      <c r="N70" s="607" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1072" t="n"/>
+      <c r="B71" s="567" t="n"/>
+      <c r="C71" s="1088" t="n"/>
+      <c r="D71" s="567" t="n"/>
+      <c r="E71" s="567" t="n"/>
+      <c r="F71" s="567" t="n"/>
+      <c r="G71" s="1081" t="n"/>
+      <c r="H71" s="567" t="n"/>
+      <c r="I71" s="567" t="n"/>
+      <c r="J71" s="567" t="n"/>
+      <c r="K71" s="1390" t="n"/>
+      <c r="L71" s="567" t="n"/>
+      <c r="M71" s="567" t="n"/>
+      <c r="N71" s="607" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="550">
+      <c r="A72" s="1072" t="n"/>
+      <c r="B72" s="567" t="n"/>
+      <c r="C72" s="1088" t="n"/>
+      <c r="D72" s="567" t="n"/>
+      <c r="E72" s="567" t="n"/>
+      <c r="F72" s="567" t="n"/>
+      <c r="G72" s="1081" t="n"/>
+      <c r="H72" s="567" t="n"/>
+      <c r="I72" s="567" t="n"/>
+      <c r="J72" s="567" t="n"/>
+      <c r="K72" s="1390" t="n"/>
+      <c r="L72" s="567" t="n"/>
+      <c r="M72" s="567" t="n"/>
+      <c r="N72" s="607" t="n"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="550">
+      <c r="A73" s="1131" t="inlineStr">
         <is>
           <t>AVANCE FINANCIERO Y ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="N58" s="1100" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="550">
-      <c r="A59" s="1123" t="inlineStr">
+      <c r="N73" s="1100" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="550">
+      <c r="A74" s="1123" t="inlineStr">
         <is>
           <t>INGRESOS DEL PERÍODO</t>
         </is>
       </c>
-      <c r="B59" s="567" t="n"/>
-      <c r="C59" s="567" t="n"/>
-      <c r="D59" s="567" t="n"/>
-      <c r="E59" s="567" t="n"/>
-      <c r="F59" s="567" t="n"/>
-      <c r="G59" s="268" t="n"/>
-      <c r="H59" s="1151" t="inlineStr">
-        <is>
-          <t>EGRESOS / GASTOS DEL PERÍODO</t>
-        </is>
-      </c>
-      <c r="N59" s="562" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="550">
-      <c r="A60" s="1125" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
-      <c r="B60" s="1126" t="n"/>
-      <c r="C60" s="1126" t="n"/>
-      <c r="D60" s="1391" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="E60" s="1167" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
-      <c r="F60" s="1126" t="n"/>
-      <c r="G60" s="267" t="n"/>
-      <c r="H60" s="1103" t="inlineStr">
-        <is>
-          <t>CONCEPTO</t>
-        </is>
-      </c>
-      <c r="I60" s="652" t="n"/>
-      <c r="J60" s="652" t="n"/>
-      <c r="K60" s="1103" t="inlineStr">
-        <is>
-          <t>FECHA</t>
-        </is>
-      </c>
-      <c r="L60" s="652" t="n"/>
-      <c r="M60" s="1073" t="inlineStr">
-        <is>
-          <t>VALOR ($)</t>
-        </is>
-      </c>
-      <c r="N60" s="1074" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1135" t="n"/>
-      <c r="B61" s="1136" t="n"/>
-      <c r="C61" s="1137" t="n"/>
-      <c r="D61" s="1392" t="n"/>
-      <c r="E61" s="1393" t="n"/>
-      <c r="F61" s="1137" t="n"/>
-      <c r="G61" s="265" t="n"/>
-      <c r="H61" s="1135" t="n"/>
-      <c r="I61" s="1136" t="n"/>
-      <c r="J61" s="1137" t="n"/>
-      <c r="K61" s="1169" t="n"/>
-      <c r="L61" s="1137" t="n"/>
-      <c r="M61" s="1393" t="n"/>
-      <c r="N61" s="1137" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1084" t="n"/>
-      <c r="B62" s="567" t="n"/>
-      <c r="C62" s="682" t="n"/>
-      <c r="D62" s="1394" t="n"/>
-      <c r="E62" s="1395" t="n"/>
-      <c r="F62" s="682" t="n"/>
-      <c r="G62" s="263" t="n"/>
-      <c r="H62" s="1084" t="n"/>
-      <c r="I62" s="567" t="n"/>
-      <c r="J62" s="682" t="n"/>
-      <c r="K62" s="1107" t="n"/>
-      <c r="L62" s="682" t="n"/>
-      <c r="M62" s="1395" t="n"/>
-      <c r="N62" s="682" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1084" t="n"/>
-      <c r="B63" s="567" t="n"/>
-      <c r="C63" s="682" t="n"/>
-      <c r="D63" s="1394" t="n"/>
-      <c r="E63" s="1395" t="n"/>
-      <c r="F63" s="682" t="n"/>
-      <c r="G63" s="263" t="n"/>
-      <c r="H63" s="1084" t="n"/>
-      <c r="I63" s="567" t="n"/>
-      <c r="J63" s="682" t="n"/>
-      <c r="K63" s="1107" t="n"/>
-      <c r="L63" s="682" t="n"/>
-      <c r="M63" s="1395" t="n"/>
-      <c r="N63" s="682" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1084" t="n"/>
-      <c r="B64" s="567" t="n"/>
-      <c r="C64" s="682" t="n"/>
-      <c r="D64" s="1394" t="n"/>
-      <c r="E64" s="1395" t="n"/>
-      <c r="F64" s="682" t="n"/>
-      <c r="G64" s="263" t="n"/>
-      <c r="H64" s="1084" t="n"/>
-      <c r="I64" s="567" t="n"/>
-      <c r="J64" s="682" t="n"/>
-      <c r="K64" s="1107" t="n"/>
-      <c r="L64" s="682" t="n"/>
-      <c r="M64" s="1395" t="n"/>
-      <c r="N64" s="682" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1084" t="n"/>
-      <c r="B65" s="567" t="n"/>
-      <c r="C65" s="682" t="n"/>
-      <c r="D65" s="1394" t="n"/>
-      <c r="E65" s="1395" t="n"/>
-      <c r="F65" s="682" t="n"/>
-      <c r="G65" s="263" t="n"/>
-      <c r="H65" s="1084" t="n"/>
-      <c r="I65" s="567" t="n"/>
-      <c r="J65" s="682" t="n"/>
-      <c r="K65" s="1153" t="n"/>
-      <c r="L65" s="1076" t="n"/>
-      <c r="M65" s="1396" t="n"/>
-      <c r="N65" s="1076" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="550">
-      <c r="A66" s="1171" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
-      <c r="B66" s="567" t="n"/>
-      <c r="C66" s="567" t="n"/>
-      <c r="D66" s="567" t="n"/>
-      <c r="E66" s="1397">
-        <f>SUM(E61:F65)</f>
-        <v/>
-      </c>
-      <c r="F66" s="567" t="n"/>
-      <c r="G66" s="260" t="n"/>
-      <c r="H66" s="1090" t="inlineStr">
-        <is>
-          <t>TOTAL EGRESOS</t>
-        </is>
-      </c>
-      <c r="M66" s="1398">
-        <f>SUM(M61:N65)</f>
-        <v/>
-      </c>
-      <c r="N66" s="562" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="550">
-      <c r="A67" s="1122" t="inlineStr">
-        <is>
-          <t>BALANCE DEL PERÍODO (INGRESOS - EGRESOS)</t>
-        </is>
-      </c>
-      <c r="B67" s="609" t="n"/>
-      <c r="C67" s="609" t="n"/>
-      <c r="D67" s="609" t="n"/>
-      <c r="E67" s="609" t="n"/>
-      <c r="F67" s="609" t="n"/>
-      <c r="G67" s="609" t="n"/>
-      <c r="H67" s="609" t="n"/>
-      <c r="I67" s="609" t="n"/>
-      <c r="J67" s="609" t="n"/>
-      <c r="K67" s="609" t="n"/>
-      <c r="L67" s="609" t="n"/>
-      <c r="M67" s="1399">
-        <f>E66-M66</f>
-        <v/>
-      </c>
-      <c r="N67" s="610" t="n"/>
-    </row>
-    <row r="68" ht="25.05" customHeight="1" s="550">
-      <c r="A68" s="1150" t="inlineStr">
-        <is>
-          <t>PRESUPUESTO EJECUTADO ACUMULADO ($)</t>
-        </is>
-      </c>
-      <c r="B68" s="1140" t="n"/>
-      <c r="C68" s="1140" t="n"/>
-      <c r="D68" s="1140" t="n"/>
-      <c r="E68" s="1140" t="n"/>
-      <c r="F68" s="1140" t="n"/>
-      <c r="G68" s="1400">
-        <f>J46</f>
-        <v/>
-      </c>
-      <c r="H68" s="1140" t="n"/>
-      <c r="I68" s="1140" t="n"/>
-      <c r="J68" s="1156" t="inlineStr">
-        <is>
-          <t>% EJECUTADO vs PRESUPUESTO</t>
-        </is>
-      </c>
-      <c r="K68" s="1140" t="n"/>
-      <c r="L68" s="1157" t="n"/>
-      <c r="M68" s="1401">
-        <f>IFERROR(J46/$L$14,0)</f>
-        <v/>
-      </c>
-      <c r="N68" s="1133" t="n"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" s="550">
-      <c r="A69" s="1111" t="inlineStr">
-        <is>
-          <t>ASPECTOS HSE Y AMBIENTALES</t>
-        </is>
-      </c>
-      <c r="N69" s="562" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="550">
-      <c r="A70" s="1162" t="inlineStr">
-        <is>
-          <t>HORAS HOMBRE TRABAJADAS</t>
-        </is>
-      </c>
-      <c r="B70" s="1126" t="n"/>
-      <c r="C70" s="1126" t="n"/>
-      <c r="D70" s="1126" t="n"/>
-      <c r="E70" s="1126" t="n"/>
-      <c r="F70" s="1126" t="n"/>
-      <c r="G70" s="1126" t="n"/>
-      <c r="H70" s="1126" t="n"/>
-      <c r="I70" s="1126" t="n"/>
-      <c r="J70" s="1126" t="n"/>
-      <c r="K70" s="1126" t="n"/>
-      <c r="L70" s="1126" t="n"/>
-      <c r="M70" s="1126" t="n"/>
-      <c r="N70" s="1163" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1089" t="n"/>
-      <c r="N71" s="562" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="550">
-      <c r="A72" s="1154" t="inlineStr">
-        <is>
-          <t>OBSERVACIONES HSE</t>
-        </is>
-      </c>
-      <c r="B72" s="565" t="n"/>
-      <c r="C72" s="565" t="n"/>
-      <c r="D72" s="565" t="n"/>
-      <c r="E72" s="565" t="n"/>
-      <c r="F72" s="565" t="n"/>
-      <c r="G72" s="565" t="n"/>
-      <c r="H72" s="565" t="n"/>
-      <c r="I72" s="565" t="n"/>
-      <c r="J72" s="565" t="n"/>
-      <c r="K72" s="565" t="n"/>
-      <c r="L72" s="565" t="n"/>
-      <c r="M72" s="565" t="n"/>
-      <c r="N72" s="593" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1402" t="n"/>
-      <c r="B73" s="710" t="n"/>
-      <c r="C73" s="710" t="n"/>
-      <c r="D73" s="710" t="n"/>
-      <c r="E73" s="710" t="n"/>
-      <c r="F73" s="710" t="n"/>
-      <c r="G73" s="710" t="n"/>
-      <c r="H73" s="710" t="n"/>
-      <c r="I73" s="710" t="n"/>
-      <c r="J73" s="710" t="n"/>
-      <c r="K73" s="710" t="n"/>
-      <c r="L73" s="710" t="n"/>
-      <c r="M73" s="710" t="n"/>
-      <c r="N73" s="1160" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1403" t="n"/>
       <c r="B74" s="567" t="n"/>
       <c r="C74" s="567" t="n"/>
       <c r="D74" s="567" t="n"/>
       <c r="E74" s="567" t="n"/>
       <c r="F74" s="567" t="n"/>
-      <c r="G74" s="567" t="n"/>
-      <c r="H74" s="567" t="n"/>
-      <c r="I74" s="567" t="n"/>
-      <c r="J74" s="567" t="n"/>
-      <c r="K74" s="567" t="n"/>
-      <c r="L74" s="567" t="n"/>
-      <c r="M74" s="567" t="n"/>
-      <c r="N74" s="607" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1403" t="n"/>
-      <c r="B75" s="567" t="n"/>
-      <c r="C75" s="567" t="n"/>
-      <c r="D75" s="567" t="n"/>
-      <c r="E75" s="567" t="n"/>
-      <c r="F75" s="567" t="n"/>
-      <c r="G75" s="567" t="n"/>
-      <c r="H75" s="567" t="n"/>
-      <c r="I75" s="567" t="n"/>
-      <c r="J75" s="567" t="n"/>
-      <c r="K75" s="567" t="n"/>
-      <c r="L75" s="567" t="n"/>
-      <c r="M75" s="567" t="n"/>
-      <c r="N75" s="607" t="n"/>
+      <c r="G74" s="268" t="n"/>
+      <c r="H74" s="1151" t="inlineStr">
+        <is>
+          <t>EGRESOS / GASTOS DEL PERÍODO</t>
+        </is>
+      </c>
+      <c r="N74" s="562" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="550">
+      <c r="A75" s="1125" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="B75" s="1126" t="n"/>
+      <c r="C75" s="1126" t="n"/>
+      <c r="D75" s="1391" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E75" s="1167" t="inlineStr">
+        <is>
+          <t>VALOR ($)</t>
+        </is>
+      </c>
+      <c r="F75" s="1126" t="n"/>
+      <c r="G75" s="267" t="n"/>
+      <c r="H75" s="1103" t="inlineStr">
+        <is>
+          <t>CONCEPTO</t>
+        </is>
+      </c>
+      <c r="I75" s="652" t="n"/>
+      <c r="J75" s="652" t="n"/>
+      <c r="K75" s="1103" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="L75" s="652" t="n"/>
+      <c r="M75" s="1073" t="inlineStr">
+        <is>
+          <t>VALOR ($)</t>
+        </is>
+      </c>
+      <c r="N75" s="1074" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="1403" t="n"/>
-      <c r="B76" s="567" t="n"/>
-      <c r="C76" s="567" t="n"/>
-      <c r="D76" s="567" t="n"/>
-      <c r="E76" s="567" t="n"/>
-      <c r="F76" s="567" t="n"/>
-      <c r="G76" s="567" t="n"/>
-      <c r="H76" s="567" t="n"/>
-      <c r="I76" s="567" t="n"/>
-      <c r="J76" s="567" t="n"/>
-      <c r="K76" s="567" t="n"/>
-      <c r="L76" s="567" t="n"/>
-      <c r="M76" s="567" t="n"/>
-      <c r="N76" s="607" t="n"/>
+      <c r="A76" s="1135" t="n"/>
+      <c r="B76" s="1136" t="n"/>
+      <c r="C76" s="1137" t="n"/>
+      <c r="D76" s="1392" t="n"/>
+      <c r="E76" s="1393" t="n"/>
+      <c r="F76" s="1137" t="n"/>
+      <c r="G76" s="265" t="n"/>
+      <c r="H76" s="1135" t="n"/>
+      <c r="I76" s="1136" t="n"/>
+      <c r="J76" s="1137" t="n"/>
+      <c r="K76" s="1169" t="n"/>
+      <c r="L76" s="1137" t="n"/>
+      <c r="M76" s="1393" t="n"/>
+      <c r="N76" s="1137" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1" s="550">
-      <c r="A77" s="1104" t="inlineStr">
+      <c r="A77" s="1084" t="n"/>
+      <c r="B77" s="567" t="n"/>
+      <c r="C77" s="682" t="n"/>
+      <c r="D77" s="1394" t="n"/>
+      <c r="E77" s="1395" t="n"/>
+      <c r="F77" s="682" t="n"/>
+      <c r="G77" s="263" t="n"/>
+      <c r="H77" s="1084" t="n"/>
+      <c r="I77" s="567" t="n"/>
+      <c r="J77" s="682" t="n"/>
+      <c r="K77" s="1107" t="n"/>
+      <c r="L77" s="682" t="n"/>
+      <c r="M77" s="1395" t="n"/>
+      <c r="N77" s="682" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1084" t="n"/>
+      <c r="B78" s="567" t="n"/>
+      <c r="C78" s="682" t="n"/>
+      <c r="D78" s="1394" t="n"/>
+      <c r="E78" s="1395" t="n"/>
+      <c r="F78" s="682" t="n"/>
+      <c r="G78" s="263" t="n"/>
+      <c r="H78" s="1084" t="n"/>
+      <c r="I78" s="567" t="n"/>
+      <c r="J78" s="682" t="n"/>
+      <c r="K78" s="1107" t="n"/>
+      <c r="L78" s="682" t="n"/>
+      <c r="M78" s="1395" t="n"/>
+      <c r="N78" s="682" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1084" t="n"/>
+      <c r="B79" s="567" t="n"/>
+      <c r="C79" s="682" t="n"/>
+      <c r="D79" s="1394" t="n"/>
+      <c r="E79" s="1395" t="n"/>
+      <c r="F79" s="682" t="n"/>
+      <c r="G79" s="263" t="n"/>
+      <c r="H79" s="1084" t="n"/>
+      <c r="I79" s="567" t="n"/>
+      <c r="J79" s="682" t="n"/>
+      <c r="K79" s="1107" t="n"/>
+      <c r="L79" s="682" t="n"/>
+      <c r="M79" s="1395" t="n"/>
+      <c r="N79" s="682" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1084" t="n"/>
+      <c r="B80" s="567" t="n"/>
+      <c r="C80" s="682" t="n"/>
+      <c r="D80" s="1394" t="n"/>
+      <c r="E80" s="1395" t="n"/>
+      <c r="F80" s="682" t="n"/>
+      <c r="G80" s="263" t="n"/>
+      <c r="H80" s="1084" t="n"/>
+      <c r="I80" s="567" t="n"/>
+      <c r="J80" s="682" t="n"/>
+      <c r="K80" s="1153" t="n"/>
+      <c r="L80" s="1076" t="n"/>
+      <c r="M80" s="1396" t="n"/>
+      <c r="N80" s="1076" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="550">
+      <c r="A81" s="1171" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="B81" s="567" t="n"/>
+      <c r="C81" s="567" t="n"/>
+      <c r="D81" s="567" t="n"/>
+      <c r="E81" s="1397">
+        <f>SUM(E76:F80)</f>
+        <v/>
+      </c>
+      <c r="F81" s="567" t="n"/>
+      <c r="G81" s="260" t="n"/>
+      <c r="H81" s="1090" t="inlineStr">
+        <is>
+          <t>TOTAL EGRESOS</t>
+        </is>
+      </c>
+      <c r="M81" s="1398">
+        <f>SUM(M76:N80)</f>
+        <v/>
+      </c>
+      <c r="N81" s="562" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="550">
+      <c r="A82" s="1122" t="inlineStr">
+        <is>
+          <t>BALANCE DEL PERÍODO (INGRESOS - EGRESOS)</t>
+        </is>
+      </c>
+      <c r="B82" s="609" t="n"/>
+      <c r="C82" s="609" t="n"/>
+      <c r="D82" s="609" t="n"/>
+      <c r="E82" s="609" t="n"/>
+      <c r="F82" s="609" t="n"/>
+      <c r="G82" s="609" t="n"/>
+      <c r="H82" s="609" t="n"/>
+      <c r="I82" s="609" t="n"/>
+      <c r="J82" s="609" t="n"/>
+      <c r="K82" s="609" t="n"/>
+      <c r="L82" s="609" t="n"/>
+      <c r="M82" s="1399">
+        <f>E81-M81</f>
+        <v/>
+      </c>
+      <c r="N82" s="610" t="n"/>
+    </row>
+    <row r="83" ht="25.05" customHeight="1" s="550">
+      <c r="A83" s="1150" t="inlineStr">
+        <is>
+          <t>PRESUPUESTO EJECUTADO ACUMULADO ($)</t>
+        </is>
+      </c>
+      <c r="B83" s="1140" t="n"/>
+      <c r="C83" s="1140" t="n"/>
+      <c r="D83" s="1140" t="n"/>
+      <c r="E83" s="1140" t="n"/>
+      <c r="F83" s="1140" t="n"/>
+      <c r="G83" s="1400">
+        <f>J61</f>
+        <v/>
+      </c>
+      <c r="H83" s="1140" t="n"/>
+      <c r="I83" s="1140" t="n"/>
+      <c r="J83" s="1156" t="inlineStr">
+        <is>
+          <t>% EJECUTADO vs PRESUPUESTO</t>
+        </is>
+      </c>
+      <c r="K83" s="1140" t="n"/>
+      <c r="L83" s="1157" t="n"/>
+      <c r="M83" s="1401">
+        <f>IFERROR(J61/$L$14,0)</f>
+        <v/>
+      </c>
+      <c r="N83" s="1133" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="550">
+      <c r="A84" s="1111" t="inlineStr">
+        <is>
+          <t>ASPECTOS HSE Y AMBIENTALES</t>
+        </is>
+      </c>
+      <c r="N84" s="562" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="550">
+      <c r="A85" s="1162" t="inlineStr">
+        <is>
+          <t>HORAS HOMBRE TRABAJADAS</t>
+        </is>
+      </c>
+      <c r="B85" s="1126" t="n"/>
+      <c r="C85" s="1126" t="n"/>
+      <c r="D85" s="1126" t="n"/>
+      <c r="E85" s="1126" t="n"/>
+      <c r="F85" s="1126" t="n"/>
+      <c r="G85" s="1126" t="n"/>
+      <c r="H85" s="1126" t="n"/>
+      <c r="I85" s="1126" t="n"/>
+      <c r="J85" s="1126" t="n"/>
+      <c r="K85" s="1126" t="n"/>
+      <c r="L85" s="1126" t="n"/>
+      <c r="M85" s="1126" t="n"/>
+      <c r="N85" s="1163" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1089" t="n"/>
+      <c r="N86" s="562" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="550">
+      <c r="A87" s="1154" t="inlineStr">
+        <is>
+          <t>OBSERVACIONES HSE</t>
+        </is>
+      </c>
+      <c r="B87" s="565" t="n"/>
+      <c r="C87" s="565" t="n"/>
+      <c r="D87" s="565" t="n"/>
+      <c r="E87" s="565" t="n"/>
+      <c r="F87" s="565" t="n"/>
+      <c r="G87" s="565" t="n"/>
+      <c r="H87" s="565" t="n"/>
+      <c r="I87" s="565" t="n"/>
+      <c r="J87" s="565" t="n"/>
+      <c r="K87" s="565" t="n"/>
+      <c r="L87" s="565" t="n"/>
+      <c r="M87" s="565" t="n"/>
+      <c r="N87" s="593" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="1402" t="n"/>
+      <c r="B88" s="710" t="n"/>
+      <c r="C88" s="710" t="n"/>
+      <c r="D88" s="710" t="n"/>
+      <c r="E88" s="710" t="n"/>
+      <c r="F88" s="710" t="n"/>
+      <c r="G88" s="710" t="n"/>
+      <c r="H88" s="710" t="n"/>
+      <c r="I88" s="710" t="n"/>
+      <c r="J88" s="710" t="n"/>
+      <c r="K88" s="710" t="n"/>
+      <c r="L88" s="710" t="n"/>
+      <c r="M88" s="710" t="n"/>
+      <c r="N88" s="1160" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="1403" t="n"/>
+      <c r="B89" s="567" t="n"/>
+      <c r="C89" s="567" t="n"/>
+      <c r="D89" s="567" t="n"/>
+      <c r="E89" s="567" t="n"/>
+      <c r="F89" s="567" t="n"/>
+      <c r="G89" s="567" t="n"/>
+      <c r="H89" s="567" t="n"/>
+      <c r="I89" s="567" t="n"/>
+      <c r="J89" s="567" t="n"/>
+      <c r="K89" s="567" t="n"/>
+      <c r="L89" s="567" t="n"/>
+      <c r="M89" s="567" t="n"/>
+      <c r="N89" s="607" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="1403" t="n"/>
+      <c r="B90" s="567" t="n"/>
+      <c r="C90" s="567" t="n"/>
+      <c r="D90" s="567" t="n"/>
+      <c r="E90" s="567" t="n"/>
+      <c r="F90" s="567" t="n"/>
+      <c r="G90" s="567" t="n"/>
+      <c r="H90" s="567" t="n"/>
+      <c r="I90" s="567" t="n"/>
+      <c r="J90" s="567" t="n"/>
+      <c r="K90" s="567" t="n"/>
+      <c r="L90" s="567" t="n"/>
+      <c r="M90" s="567" t="n"/>
+      <c r="N90" s="607" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="1403" t="n"/>
+      <c r="B91" s="567" t="n"/>
+      <c r="C91" s="567" t="n"/>
+      <c r="D91" s="567" t="n"/>
+      <c r="E91" s="567" t="n"/>
+      <c r="F91" s="567" t="n"/>
+      <c r="G91" s="567" t="n"/>
+      <c r="H91" s="567" t="n"/>
+      <c r="I91" s="567" t="n"/>
+      <c r="J91" s="567" t="n"/>
+      <c r="K91" s="567" t="n"/>
+      <c r="L91" s="567" t="n"/>
+      <c r="M91" s="567" t="n"/>
+      <c r="N91" s="607" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="550">
+      <c r="A92" s="1104" t="inlineStr">
         <is>
           <t>ASPECTOS AMBIENTALES / NO CONFORMIDADES</t>
         </is>
       </c>
-      <c r="B77" s="567" t="n"/>
-      <c r="C77" s="567" t="n"/>
-      <c r="D77" s="567" t="n"/>
-      <c r="E77" s="567" t="n"/>
-      <c r="F77" s="567" t="n"/>
-      <c r="G77" s="567" t="n"/>
-      <c r="H77" s="567" t="n"/>
-      <c r="I77" s="567" t="n"/>
-      <c r="J77" s="567" t="n"/>
-      <c r="K77" s="567" t="n"/>
-      <c r="L77" s="567" t="n"/>
-      <c r="M77" s="567" t="n"/>
-      <c r="N77" s="607" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1071" t="n"/>
-      <c r="B78" s="567" t="n"/>
-      <c r="C78" s="567" t="n"/>
-      <c r="D78" s="567" t="n"/>
-      <c r="E78" s="567" t="n"/>
-      <c r="F78" s="567" t="n"/>
-      <c r="G78" s="567" t="n"/>
-      <c r="H78" s="567" t="n"/>
-      <c r="I78" s="567" t="n"/>
-      <c r="J78" s="567" t="n"/>
-      <c r="K78" s="567" t="n"/>
-      <c r="L78" s="567" t="n"/>
-      <c r="M78" s="567" t="n"/>
-      <c r="N78" s="607" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1071" t="n"/>
-      <c r="B79" s="567" t="n"/>
-      <c r="C79" s="567" t="n"/>
-      <c r="D79" s="567" t="n"/>
-      <c r="E79" s="567" t="n"/>
-      <c r="F79" s="567" t="n"/>
-      <c r="G79" s="567" t="n"/>
-      <c r="H79" s="567" t="n"/>
-      <c r="I79" s="567" t="n"/>
-      <c r="J79" s="567" t="n"/>
-      <c r="K79" s="567" t="n"/>
-      <c r="L79" s="567" t="n"/>
-      <c r="M79" s="567" t="n"/>
-      <c r="N79" s="607" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1158" t="inlineStr">
+      <c r="B92" s="567" t="n"/>
+      <c r="C92" s="567" t="n"/>
+      <c r="D92" s="567" t="n"/>
+      <c r="E92" s="567" t="n"/>
+      <c r="F92" s="567" t="n"/>
+      <c r="G92" s="567" t="n"/>
+      <c r="H92" s="567" t="n"/>
+      <c r="I92" s="567" t="n"/>
+      <c r="J92" s="567" t="n"/>
+      <c r="K92" s="567" t="n"/>
+      <c r="L92" s="567" t="n"/>
+      <c r="M92" s="567" t="n"/>
+      <c r="N92" s="607" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="1071" t="n"/>
+      <c r="B93" s="567" t="n"/>
+      <c r="C93" s="567" t="n"/>
+      <c r="D93" s="567" t="n"/>
+      <c r="E93" s="567" t="n"/>
+      <c r="F93" s="567" t="n"/>
+      <c r="G93" s="567" t="n"/>
+      <c r="H93" s="567" t="n"/>
+      <c r="I93" s="567" t="n"/>
+      <c r="J93" s="567" t="n"/>
+      <c r="K93" s="567" t="n"/>
+      <c r="L93" s="567" t="n"/>
+      <c r="M93" s="567" t="n"/>
+      <c r="N93" s="607" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1071" t="n"/>
+      <c r="B94" s="567" t="n"/>
+      <c r="C94" s="567" t="n"/>
+      <c r="D94" s="567" t="n"/>
+      <c r="E94" s="567" t="n"/>
+      <c r="F94" s="567" t="n"/>
+      <c r="G94" s="567" t="n"/>
+      <c r="H94" s="567" t="n"/>
+      <c r="I94" s="567" t="n"/>
+      <c r="J94" s="567" t="n"/>
+      <c r="K94" s="567" t="n"/>
+      <c r="L94" s="567" t="n"/>
+      <c r="M94" s="567" t="n"/>
+      <c r="N94" s="607" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="1158" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="B80" s="1064" t="n"/>
-      <c r="C80" s="1064" t="n"/>
-      <c r="D80" s="1064" t="n"/>
-      <c r="E80" s="1064" t="n"/>
-      <c r="F80" s="1064" t="n"/>
-      <c r="G80" s="1076" t="n"/>
-      <c r="H80" s="1108" t="inlineStr">
+      <c r="B95" s="1064" t="n"/>
+      <c r="C95" s="1064" t="n"/>
+      <c r="D95" s="1064" t="n"/>
+      <c r="E95" s="1064" t="n"/>
+      <c r="F95" s="1064" t="n"/>
+      <c r="G95" s="1076" t="n"/>
+      <c r="H95" s="1108" t="inlineStr">
         <is>
           <t>INSERTAR FOTOGRAFÍA</t>
         </is>
       </c>
-      <c r="I80" s="1064" t="n"/>
-      <c r="J80" s="1064" t="n"/>
-      <c r="K80" s="1064" t="n"/>
-      <c r="L80" s="1064" t="n"/>
-      <c r="M80" s="1064" t="n"/>
-      <c r="N80" s="1065" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1066" t="n"/>
-      <c r="G81" s="1100" t="n"/>
-      <c r="H81" s="1066" t="n"/>
-      <c r="N81" s="562" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="550">
-      <c r="A82" s="1066" t="n"/>
-      <c r="G82" s="1100" t="n"/>
-      <c r="H82" s="1066" t="n"/>
-      <c r="N82" s="562" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1066" t="n"/>
-      <c r="G83" s="1100" t="n"/>
-      <c r="H83" s="1066" t="n"/>
-      <c r="N83" s="562" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1066" t="n"/>
-      <c r="G84" s="1100" t="n"/>
-      <c r="H84" s="1066" t="n"/>
-      <c r="N84" s="562" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1066" t="n"/>
-      <c r="G85" s="1100" t="n"/>
-      <c r="H85" s="1066" t="n"/>
-      <c r="N85" s="562" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1066" t="n"/>
-      <c r="G86" s="1100" t="n"/>
-      <c r="H86" s="1066" t="n"/>
-      <c r="N86" s="562" t="n"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="550">
-      <c r="A87" s="1066" t="n"/>
-      <c r="G87" s="1100" t="n"/>
-      <c r="H87" s="1066" t="n"/>
-      <c r="N87" s="562" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1066" t="n"/>
-      <c r="G88" s="1100" t="n"/>
-      <c r="H88" s="1066" t="n"/>
-      <c r="N88" s="562" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1066" t="n"/>
-      <c r="G89" s="1100" t="n"/>
-      <c r="H89" s="1066" t="n"/>
-      <c r="N89" s="562" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1066" t="n"/>
-      <c r="G90" s="1100" t="n"/>
-      <c r="H90" s="1066" t="n"/>
-      <c r="N90" s="562" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1066" t="n"/>
-      <c r="G91" s="1100" t="n"/>
-      <c r="H91" s="1066" t="n"/>
-      <c r="N91" s="562" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1066" t="n"/>
-      <c r="G92" s="1100" t="n"/>
-      <c r="H92" s="1066" t="n"/>
-      <c r="N92" s="562" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1077" t="n"/>
-      <c r="B93" s="609" t="n"/>
-      <c r="C93" s="609" t="n"/>
-      <c r="D93" s="609" t="n"/>
-      <c r="E93" s="609" t="n"/>
-      <c r="F93" s="609" t="n"/>
-      <c r="G93" s="1078" t="n"/>
-      <c r="H93" s="1077" t="n"/>
-      <c r="I93" s="609" t="n"/>
-      <c r="J93" s="609" t="n"/>
-      <c r="K93" s="609" t="n"/>
-      <c r="L93" s="609" t="n"/>
-      <c r="M93" s="609" t="n"/>
-      <c r="N93" s="610" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="1404" t="n"/>
-      <c r="H94" s="1404" t="n"/>
-    </row>
-    <row r="95"/>
+      <c r="I95" s="1064" t="n"/>
+      <c r="J95" s="1064" t="n"/>
+      <c r="K95" s="1064" t="n"/>
+      <c r="L95" s="1064" t="n"/>
+      <c r="M95" s="1064" t="n"/>
+      <c r="N95" s="1065" t="n"/>
+    </row>
     <row r="96">
-      <c r="A96" s="1165" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="B96" s="1064" t="n"/>
-      <c r="C96" s="1064" t="n"/>
-      <c r="D96" s="1064" t="n"/>
-      <c r="E96" s="1064" t="n"/>
-      <c r="F96" s="1064" t="n"/>
-      <c r="G96" s="1076" t="n"/>
-      <c r="H96" s="1063" t="inlineStr">
-        <is>
-          <t>INSERTAR FOTOGRAFÍA</t>
-        </is>
-      </c>
-      <c r="I96" s="1064" t="n"/>
-      <c r="J96" s="1064" t="n"/>
-      <c r="K96" s="1064" t="n"/>
-      <c r="L96" s="1064" t="n"/>
-      <c r="M96" s="1064" t="n"/>
-      <c r="N96" s="1065" t="n"/>
-    </row>
-    <row r="97">
+      <c r="A96" s="1066" t="n"/>
+      <c r="G96" s="1100" t="n"/>
+      <c r="H96" s="1066" t="n"/>
+      <c r="N96" s="562" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="550">
       <c r="A97" s="1066" t="n"/>
       <c r="G97" s="1100" t="n"/>
       <c r="H97" s="1066" t="n"/>
@@ -18316,7 +18622,7 @@
       <c r="H101" s="1066" t="n"/>
       <c r="N101" s="562" t="n"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1" s="550">
       <c r="A102" s="1066" t="n"/>
       <c r="G102" s="1100" t="n"/>
       <c r="H102" s="1066" t="n"/>
@@ -18353,452 +18659,593 @@
       <c r="N107" s="562" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="1066" t="n"/>
-      <c r="G108" s="1100" t="n"/>
-      <c r="H108" s="1066" t="n"/>
-      <c r="N108" s="562" t="n"/>
+      <c r="A108" s="1077" t="n"/>
+      <c r="B108" s="609" t="n"/>
+      <c r="C108" s="609" t="n"/>
+      <c r="D108" s="609" t="n"/>
+      <c r="E108" s="609" t="n"/>
+      <c r="F108" s="609" t="n"/>
+      <c r="G108" s="1078" t="n"/>
+      <c r="H108" s="1077" t="n"/>
+      <c r="I108" s="609" t="n"/>
+      <c r="J108" s="609" t="n"/>
+      <c r="K108" s="609" t="n"/>
+      <c r="L108" s="609" t="n"/>
+      <c r="M108" s="609" t="n"/>
+      <c r="N108" s="610" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="1067" t="n"/>
-      <c r="B109" s="557" t="n"/>
-      <c r="C109" s="557" t="n"/>
-      <c r="D109" s="557" t="n"/>
-      <c r="E109" s="557" t="n"/>
-      <c r="F109" s="557" t="n"/>
-      <c r="G109" s="1166" t="n"/>
-      <c r="H109" s="1067" t="n"/>
-      <c r="I109" s="557" t="n"/>
-      <c r="J109" s="557" t="n"/>
-      <c r="K109" s="557" t="n"/>
-      <c r="L109" s="557" t="n"/>
-      <c r="M109" s="557" t="n"/>
-      <c r="N109" s="763" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1404" t="n"/>
-      <c r="H110" s="1404" t="n"/>
-    </row>
-    <row r="111"/>
+      <c r="A109" s="1404" t="n"/>
+      <c r="H109" s="1404" t="n"/>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="1165" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="B111" s="1064" t="n"/>
+      <c r="C111" s="1064" t="n"/>
+      <c r="D111" s="1064" t="n"/>
+      <c r="E111" s="1064" t="n"/>
+      <c r="F111" s="1064" t="n"/>
+      <c r="G111" s="1076" t="n"/>
+      <c r="H111" s="1063" t="inlineStr">
+        <is>
+          <t>INSERTAR FOTOGRAFÍA</t>
+        </is>
+      </c>
+      <c r="I111" s="1064" t="n"/>
+      <c r="J111" s="1064" t="n"/>
+      <c r="K111" s="1064" t="n"/>
+      <c r="L111" s="1064" t="n"/>
+      <c r="M111" s="1064" t="n"/>
+      <c r="N111" s="1065" t="n"/>
+    </row>
     <row r="112">
-      <c r="A112" s="1161" t="n"/>
-      <c r="H112" s="1147" t="n"/>
+      <c r="A112" s="1066" t="n"/>
+      <c r="G112" s="1100" t="n"/>
+      <c r="H112" s="1066" t="n"/>
       <c r="N112" s="562" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="1120" t="inlineStr">
+      <c r="A113" s="1066" t="n"/>
+      <c r="G113" s="1100" t="n"/>
+      <c r="H113" s="1066" t="n"/>
+      <c r="N113" s="562" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="1066" t="n"/>
+      <c r="G114" s="1100" t="n"/>
+      <c r="H114" s="1066" t="n"/>
+      <c r="N114" s="562" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="1066" t="n"/>
+      <c r="G115" s="1100" t="n"/>
+      <c r="H115" s="1066" t="n"/>
+      <c r="N115" s="562" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="1066" t="n"/>
+      <c r="G116" s="1100" t="n"/>
+      <c r="H116" s="1066" t="n"/>
+      <c r="N116" s="562" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="1066" t="n"/>
+      <c r="G117" s="1100" t="n"/>
+      <c r="H117" s="1066" t="n"/>
+      <c r="N117" s="562" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1066" t="n"/>
+      <c r="G118" s="1100" t="n"/>
+      <c r="H118" s="1066" t="n"/>
+      <c r="N118" s="562" t="n"/>
+    </row>
+    <row r="119" ht="14.4" customHeight="1" s="550">
+      <c r="A119" s="1066" t="n"/>
+      <c r="G119" s="1100" t="n"/>
+      <c r="H119" s="1066" t="n"/>
+      <c r="N119" s="562" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1066" t="n"/>
+      <c r="G120" s="1100" t="n"/>
+      <c r="H120" s="1066" t="n"/>
+      <c r="N120" s="562" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="1066" t="n"/>
+      <c r="G121" s="1100" t="n"/>
+      <c r="H121" s="1066" t="n"/>
+      <c r="N121" s="562" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1066" t="n"/>
+      <c r="G122" s="1100" t="n"/>
+      <c r="H122" s="1066" t="n"/>
+      <c r="N122" s="562" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1066" t="n"/>
+      <c r="G123" s="1100" t="n"/>
+      <c r="H123" s="1066" t="n"/>
+      <c r="N123" s="562" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1067" t="n"/>
+      <c r="B124" s="557" t="n"/>
+      <c r="C124" s="557" t="n"/>
+      <c r="D124" s="557" t="n"/>
+      <c r="E124" s="557" t="n"/>
+      <c r="F124" s="557" t="n"/>
+      <c r="G124" s="1166" t="n"/>
+      <c r="H124" s="1067" t="n"/>
+      <c r="I124" s="557" t="n"/>
+      <c r="J124" s="557" t="n"/>
+      <c r="K124" s="557" t="n"/>
+      <c r="L124" s="557" t="n"/>
+      <c r="M124" s="557" t="n"/>
+      <c r="N124" s="763" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1404" t="n"/>
+      <c r="H125" s="1404" t="n"/>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="1161" t="n"/>
+      <c r="H127" s="1147" t="n"/>
+      <c r="N127" s="562" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1120" t="inlineStr">
         <is>
           <t>FIRMAS</t>
         </is>
       </c>
-      <c r="B113" s="677" t="n"/>
-      <c r="C113" s="677" t="n"/>
-      <c r="D113" s="677" t="n"/>
-      <c r="E113" s="677" t="n"/>
-      <c r="F113" s="677" t="n"/>
-      <c r="G113" s="677" t="n"/>
-      <c r="H113" s="677" t="n"/>
-      <c r="I113" s="677" t="n"/>
-      <c r="J113" s="677" t="n"/>
-      <c r="K113" s="677" t="n"/>
-      <c r="L113" s="677" t="n"/>
-      <c r="M113" s="677" t="n"/>
-      <c r="N113" s="1121" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="1079" t="inlineStr">
+      <c r="B128" s="677" t="n"/>
+      <c r="C128" s="677" t="n"/>
+      <c r="D128" s="677" t="n"/>
+      <c r="E128" s="677" t="n"/>
+      <c r="F128" s="677" t="n"/>
+      <c r="G128" s="677" t="n"/>
+      <c r="H128" s="677" t="n"/>
+      <c r="I128" s="677" t="n"/>
+      <c r="J128" s="677" t="n"/>
+      <c r="K128" s="677" t="n"/>
+      <c r="L128" s="677" t="n"/>
+      <c r="M128" s="677" t="n"/>
+      <c r="N128" s="1121" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1079" t="inlineStr">
         <is>
           <t>ELABORADO POR</t>
         </is>
       </c>
-      <c r="D114" s="1080" t="n"/>
-      <c r="E114" s="1116" t="inlineStr">
+      <c r="D129" s="1080" t="n"/>
+      <c r="E129" s="1116" t="inlineStr">
         <is>
           <t>REVISADO POR</t>
         </is>
       </c>
-      <c r="I114" s="1080" t="n"/>
-      <c r="J114" s="1094" t="inlineStr">
+      <c r="I129" s="1080" t="n"/>
+      <c r="J129" s="1094" t="inlineStr">
         <is>
           <t>APROBADO POR</t>
         </is>
       </c>
-      <c r="N114" s="562" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="1068" t="inlineStr">
+      <c r="N129" s="562" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1068" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="B115" s="1075" t="n"/>
-      <c r="C115" s="1064" t="n"/>
-      <c r="D115" s="1076" t="n"/>
-      <c r="E115" s="1068" t="inlineStr">
+      <c r="B130" s="1075" t="n"/>
+      <c r="C130" s="1064" t="n"/>
+      <c r="D130" s="1076" t="n"/>
+      <c r="E130" s="1068" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="F115" s="1075" t="n"/>
-      <c r="G115" s="1064" t="n"/>
-      <c r="H115" s="1064" t="n"/>
-      <c r="I115" s="1076" t="n"/>
-      <c r="J115" s="1068" t="inlineStr">
+      <c r="F130" s="1075" t="n"/>
+      <c r="G130" s="1064" t="n"/>
+      <c r="H130" s="1064" t="n"/>
+      <c r="I130" s="1076" t="n"/>
+      <c r="J130" s="1068" t="inlineStr">
         <is>
           <t>FIRMA:</t>
         </is>
       </c>
-      <c r="K115" s="1141" t="n"/>
-      <c r="N115" s="562" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="1069" t="n"/>
-      <c r="B116" s="1077" t="n"/>
-      <c r="C116" s="609" t="n"/>
-      <c r="D116" s="1078" t="n"/>
-      <c r="E116" s="1069" t="n"/>
-      <c r="F116" s="1077" t="n"/>
-      <c r="G116" s="609" t="n"/>
-      <c r="H116" s="609" t="n"/>
-      <c r="I116" s="1078" t="n"/>
-      <c r="J116" s="1069" t="n"/>
-      <c r="K116" s="1066" t="n"/>
-      <c r="N116" s="562" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="1068" t="inlineStr">
+      <c r="K130" s="1141" t="n"/>
+      <c r="N130" s="562" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1069" t="n"/>
+      <c r="B131" s="1077" t="n"/>
+      <c r="C131" s="609" t="n"/>
+      <c r="D131" s="1078" t="n"/>
+      <c r="E131" s="1069" t="n"/>
+      <c r="F131" s="1077" t="n"/>
+      <c r="G131" s="609" t="n"/>
+      <c r="H131" s="609" t="n"/>
+      <c r="I131" s="1078" t="n"/>
+      <c r="J131" s="1069" t="n"/>
+      <c r="K131" s="1066" t="n"/>
+      <c r="N131" s="562" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1068" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="B117" s="1075" t="n"/>
-      <c r="C117" s="1064" t="n"/>
-      <c r="D117" s="1076" t="n"/>
-      <c r="E117" s="1068" t="inlineStr">
+      <c r="B132" s="1075" t="n"/>
+      <c r="C132" s="1064" t="n"/>
+      <c r="D132" s="1076" t="n"/>
+      <c r="E132" s="1068" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="F117" s="1075" t="n"/>
-      <c r="G117" s="1064" t="n"/>
-      <c r="H117" s="1064" t="n"/>
-      <c r="I117" s="1076" t="n"/>
-      <c r="J117" s="1068" t="inlineStr">
+      <c r="F132" s="1075" t="n"/>
+      <c r="G132" s="1064" t="n"/>
+      <c r="H132" s="1064" t="n"/>
+      <c r="I132" s="1076" t="n"/>
+      <c r="J132" s="1068" t="inlineStr">
         <is>
           <t>NOMBRE:</t>
         </is>
       </c>
-      <c r="K117" s="1141" t="n"/>
-      <c r="N117" s="562" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="1069" t="n"/>
-      <c r="B118" s="1077" t="n"/>
-      <c r="C118" s="609" t="n"/>
-      <c r="D118" s="1078" t="n"/>
-      <c r="E118" s="1069" t="n"/>
-      <c r="F118" s="1077" t="n"/>
-      <c r="G118" s="609" t="n"/>
-      <c r="H118" s="609" t="n"/>
-      <c r="I118" s="1078" t="n"/>
-      <c r="J118" s="1069" t="n"/>
-      <c r="K118" s="1066" t="n"/>
-      <c r="N118" s="562" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1068" t="inlineStr">
+      <c r="K132" s="1141" t="n"/>
+      <c r="N132" s="562" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1069" t="n"/>
+      <c r="B133" s="1077" t="n"/>
+      <c r="C133" s="609" t="n"/>
+      <c r="D133" s="1078" t="n"/>
+      <c r="E133" s="1069" t="n"/>
+      <c r="F133" s="1077" t="n"/>
+      <c r="G133" s="609" t="n"/>
+      <c r="H133" s="609" t="n"/>
+      <c r="I133" s="1078" t="n"/>
+      <c r="J133" s="1069" t="n"/>
+      <c r="K133" s="1066" t="n"/>
+      <c r="N133" s="562" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1068" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="B119" s="1075" t="n"/>
-      <c r="C119" s="1064" t="n"/>
-      <c r="D119" s="1076" t="n"/>
-      <c r="E119" s="1068" t="inlineStr">
+      <c r="B134" s="1075" t="n"/>
+      <c r="C134" s="1064" t="n"/>
+      <c r="D134" s="1076" t="n"/>
+      <c r="E134" s="1068" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="F119" s="1075" t="n"/>
-      <c r="G119" s="1064" t="n"/>
-      <c r="H119" s="1064" t="n"/>
-      <c r="I119" s="1076" t="n"/>
-      <c r="J119" s="1068" t="inlineStr">
+      <c r="F134" s="1075" t="n"/>
+      <c r="G134" s="1064" t="n"/>
+      <c r="H134" s="1064" t="n"/>
+      <c r="I134" s="1076" t="n"/>
+      <c r="J134" s="1068" t="inlineStr">
         <is>
           <t>CARGO:</t>
         </is>
       </c>
-      <c r="K119" s="1109" t="n"/>
-      <c r="N119" s="562" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="1069" t="n"/>
-      <c r="B120" s="1077" t="n"/>
-      <c r="C120" s="609" t="n"/>
-      <c r="D120" s="1078" t="n"/>
-      <c r="E120" s="1069" t="n"/>
-      <c r="F120" s="1077" t="n"/>
-      <c r="G120" s="609" t="n"/>
-      <c r="H120" s="609" t="n"/>
-      <c r="I120" s="1078" t="n"/>
-      <c r="J120" s="1069" t="n"/>
-      <c r="K120" s="1067" t="n"/>
-      <c r="L120" s="557" t="n"/>
-      <c r="M120" s="557" t="n"/>
-      <c r="N120" s="763" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="205" t="inlineStr">
+      <c r="K134" s="1109" t="n"/>
+      <c r="N134" s="562" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1069" t="n"/>
+      <c r="B135" s="1077" t="n"/>
+      <c r="C135" s="609" t="n"/>
+      <c r="D135" s="1078" t="n"/>
+      <c r="E135" s="1069" t="n"/>
+      <c r="F135" s="1077" t="n"/>
+      <c r="G135" s="609" t="n"/>
+      <c r="H135" s="609" t="n"/>
+      <c r="I135" s="1078" t="n"/>
+      <c r="J135" s="1069" t="n"/>
+      <c r="K135" s="1067" t="n"/>
+      <c r="L135" s="557" t="n"/>
+      <c r="M135" s="557" t="n"/>
+      <c r="N135" s="763" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="205" t="inlineStr">
         <is>
           <t>REV. 10/09/2026</t>
         </is>
       </c>
-      <c r="B121" s="26" t="n"/>
-      <c r="C121" s="26" t="n"/>
-      <c r="D121" s="26" t="n"/>
-      <c r="E121" s="26" t="n"/>
-      <c r="F121" s="26" t="n"/>
-      <c r="G121" s="26" t="n"/>
-      <c r="H121" s="26" t="n"/>
-      <c r="I121" s="26" t="n"/>
-      <c r="J121" s="26" t="n"/>
-      <c r="K121" s="26" t="n"/>
-      <c r="L121" s="26" t="n"/>
-      <c r="M121" s="26" t="n"/>
-      <c r="N121" s="335">
+      <c r="B136" s="26" t="n"/>
+      <c r="C136" s="26" t="n"/>
+      <c r="D136" s="26" t="n"/>
+      <c r="E136" s="26" t="n"/>
+      <c r="F136" s="26" t="n"/>
+      <c r="G136" s="26" t="n"/>
+      <c r="H136" s="26" t="n"/>
+      <c r="I136" s="26" t="n"/>
+      <c r="J136" s="26" t="n"/>
+      <c r="K136" s="26" t="n"/>
+      <c r="L136" s="26" t="n"/>
+      <c r="M136" s="26" t="n"/>
+      <c r="N136" s="335">
         <f>M8</f>
         <v/>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="7" t="n"/>
+    <row r="137">
+      <c r="A137" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="225">
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="K48:N48"/>
-    <mergeCell ref="A46:C46"/>
+  <mergeCells count="255">
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A37:C37"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A94:G95"/>
+    <mergeCell ref="G71:H71"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="J117:J118"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="J57:N57"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A79:N79"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="B115:D116"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="K49:N49"/>
-    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="K134:N135"/>
+    <mergeCell ref="M82:N82"/>
     <mergeCell ref="M10:N10"/>
-    <mergeCell ref="G57:H57"/>
+    <mergeCell ref="H75:J75"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="J27:N27"/>
+    <mergeCell ref="A128:N128"/>
+    <mergeCell ref="G66:H66"/>
+    <mergeCell ref="I66:J66"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="E65:F65"/>
     <mergeCell ref="J35:N35"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="J20:N20"/>
-    <mergeCell ref="J25:N25"/>
-    <mergeCell ref="B117:D118"/>
-    <mergeCell ref="C54:F54"/>
-    <mergeCell ref="A71:N71"/>
-    <mergeCell ref="H66:L66"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="C64:F64"/>
+    <mergeCell ref="G68:H68"/>
     <mergeCell ref="A34:C34"/>
-    <mergeCell ref="F117:I118"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="E115:E116"/>
-    <mergeCell ref="C50:F50"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="J114:N114"/>
-    <mergeCell ref="B119:D120"/>
-    <mergeCell ref="C56:F56"/>
-    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="J46:N46"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A22:C23"/>
-    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="J52:N52"/>
+    <mergeCell ref="H125:N126"/>
+    <mergeCell ref="J61:N61"/>
     <mergeCell ref="J39:N39"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="A119:A120"/>
-    <mergeCell ref="H60:J60"/>
-    <mergeCell ref="A77:N77"/>
-    <mergeCell ref="E117:E118"/>
+    <mergeCell ref="J48:N48"/>
     <mergeCell ref="E8:K9"/>
-    <mergeCell ref="J29:N29"/>
-    <mergeCell ref="K53:N53"/>
-    <mergeCell ref="J38:N38"/>
-    <mergeCell ref="H96:N109"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="K64:L64"/>
-    <mergeCell ref="H80:N93"/>
-    <mergeCell ref="K119:N120"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="J40:N40"/>
-    <mergeCell ref="M64:N64"/>
-    <mergeCell ref="A69:N69"/>
-    <mergeCell ref="I54:J54"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A78:N78"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="J24:N24"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="A92:N92"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="A94:N94"/>
     <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A75:N75"/>
-    <mergeCell ref="I56:J56"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="J119:J120"/>
-    <mergeCell ref="G49:H49"/>
     <mergeCell ref="E14:H14"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="F115:I116"/>
-    <mergeCell ref="E114:I114"/>
-    <mergeCell ref="J26:N26"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A12:N12"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="K51:N51"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A113:N113"/>
-    <mergeCell ref="A67:L67"/>
-    <mergeCell ref="A115:A116"/>
+    <mergeCell ref="G65:H65"/>
+    <mergeCell ref="K63:N63"/>
     <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="K50:N50"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="E1:N5"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="K56:N56"/>
-    <mergeCell ref="M66:N66"/>
-    <mergeCell ref="J42:N42"/>
-    <mergeCell ref="K52:N52"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A82:L82"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A129:D129"/>
     <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A58:N58"/>
-    <mergeCell ref="F119:I120"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="M68:N68"/>
-    <mergeCell ref="J44:N44"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="H61:J61"/>
     <mergeCell ref="E16:H16"/>
-    <mergeCell ref="M67:N67"/>
-    <mergeCell ref="J28:N28"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="M9:N9"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="C57:F57"/>
-    <mergeCell ref="G68:I68"/>
-    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="G83:I83"/>
+    <mergeCell ref="A69:B69"/>
     <mergeCell ref="A42:C42"/>
-    <mergeCell ref="C53:F53"/>
-    <mergeCell ref="J30:N30"/>
-    <mergeCell ref="K115:N116"/>
+    <mergeCell ref="J132:J133"/>
     <mergeCell ref="M11:N11"/>
-    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="J53:N53"/>
     <mergeCell ref="J22:N23"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H112:N112"/>
-    <mergeCell ref="H94:N95"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="G69:H69"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A84:N84"/>
+    <mergeCell ref="J55:N55"/>
     <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A18:N18"/>
-    <mergeCell ref="K54:N54"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="K55:N55"/>
-    <mergeCell ref="J32:N32"/>
-    <mergeCell ref="K117:N118"/>
-    <mergeCell ref="H59:N59"/>
-    <mergeCell ref="J41:N41"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="H127:N127"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A86:N86"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="C65:F65"/>
     <mergeCell ref="E10:K10"/>
-    <mergeCell ref="J115:J116"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="D20:F20"/>
-    <mergeCell ref="I15:K15"/>
     <mergeCell ref="G21:I21"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="H63:J63"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="J43:N43"/>
-    <mergeCell ref="K65:L65"/>
-    <mergeCell ref="A80:G93"/>
+    <mergeCell ref="G64:H64"/>
+    <mergeCell ref="I64:J64"/>
+    <mergeCell ref="A79:C79"/>
     <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A72:N72"/>
+    <mergeCell ref="E81:F81"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="C51:F51"/>
+    <mergeCell ref="J58:N58"/>
     <mergeCell ref="J33:N33"/>
-    <mergeCell ref="J68:L68"/>
-    <mergeCell ref="G56:H56"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A95:G108"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="K71:N71"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="I65:J65"/>
     <mergeCell ref="I16:K16"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G52:H52"/>
-    <mergeCell ref="A110:G111"/>
-    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="A56:C56"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A73:N73"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="A96:G109"/>
-    <mergeCell ref="K57:N57"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="A70:N70"/>
-    <mergeCell ref="J34:N34"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="C49:F49"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="I53:J53"/>
-    <mergeCell ref="J36:N36"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="J45:N45"/>
-    <mergeCell ref="A74:N74"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="H110:N111"/>
-    <mergeCell ref="H62:J62"/>
-    <mergeCell ref="E119:E120"/>
-    <mergeCell ref="I55:J55"/>
-    <mergeCell ref="A76:N76"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="J31:N31"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="M61:N61"/>
-    <mergeCell ref="C55:F55"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A88:N88"/>
+    <mergeCell ref="K66:N66"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="B134:D135"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A90:N90"/>
+    <mergeCell ref="K68:N68"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="I68:J68"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="A85:N85"/>
     <mergeCell ref="L7:N7"/>
     <mergeCell ref="E13:N13"/>
-    <mergeCell ref="A17:N17"/>
-    <mergeCell ref="G55:H55"/>
     <mergeCell ref="L16:N16"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="J21:N21"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="E22:E23"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="G72:H72"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="K70:N70"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="J83:L83"/>
+    <mergeCell ref="C72:F72"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="K65:N65"/>
+    <mergeCell ref="A87:N87"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="J49:N49"/>
+    <mergeCell ref="A111:G124"/>
+    <mergeCell ref="J27:N27"/>
+    <mergeCell ref="A89:N89"/>
+    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="J25:N25"/>
+    <mergeCell ref="H74:N74"/>
+    <mergeCell ref="A109:G110"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="C63:F63"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="A91:N91"/>
+    <mergeCell ref="K67:N67"/>
+    <mergeCell ref="A22:C23"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="A93:N93"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="J29:N29"/>
+    <mergeCell ref="J38:N38"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="C67:F67"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="H111:N124"/>
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="K69:N69"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="H95:N108"/>
+    <mergeCell ref="J24:N24"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="B130:D131"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="J26:N26"/>
+    <mergeCell ref="A12:N12"/>
+    <mergeCell ref="K64:N64"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="B132:D133"/>
+    <mergeCell ref="A125:G126"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="K72:N72"/>
+    <mergeCell ref="E130:E131"/>
+    <mergeCell ref="J42:N42"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="E132:E133"/>
+    <mergeCell ref="J44:N44"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="E129:I129"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="J28:N28"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="C66:F66"/>
+    <mergeCell ref="J30:N30"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="C68:F68"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A18:N18"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="H109:N110"/>
+    <mergeCell ref="H81:L81"/>
+    <mergeCell ref="J54:N54"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="J41:N41"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="F130:I131"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="J47:N47"/>
+    <mergeCell ref="J56:N56"/>
+    <mergeCell ref="J43:N43"/>
+    <mergeCell ref="F132:I133"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="J129:N129"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="A73:N73"/>
+    <mergeCell ref="J59:N59"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="J60:N60"/>
+    <mergeCell ref="J34:N34"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A127:G127"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="J36:N36"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="J45:N45"/>
+    <mergeCell ref="J134:J135"/>
+    <mergeCell ref="F134:I135"/>
+    <mergeCell ref="K130:N131"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="K132:N133"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="J31:N31"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A17:N17"/>
+    <mergeCell ref="A62:N62"/>
+    <mergeCell ref="J51:N51"/>
     <mergeCell ref="A19:N19"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <pageMargins left="0.3149606299212598" right="0.3149606299212598" top="0.1968503937007874" bottom="0.1968503937007874" header="0.5118110236220472" footer="0.5118110236220472"/>
   <pageSetup orientation="portrait" scale="65" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
